--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:57</v>
@@ -477,7 +477,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:10</v>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:10</v>
@@ -553,7 +553,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:52</v>
@@ -591,7 +591,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:50</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>I Played "How Music Works" LIVE To 1500 People</v>
       </c>
       <c r="B7" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:32</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:27</v>
@@ -781,7 +781,7 @@
         <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:34</v>
@@ -1807,7 +1807,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:34</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:57</v>
@@ -477,7 +477,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:10</v>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:10</v>
@@ -553,7 +553,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:52</v>
@@ -591,7 +591,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:50</v>
@@ -629,7 +629,7 @@
         <v>I Played "How Music Works" LIVE To 1500 People</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:32</v>
@@ -667,7 +667,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:27</v>
@@ -1123,7 +1123,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>4:37</v>
@@ -1161,7 +1161,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>4:06</v>
@@ -1199,7 +1199,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:54</v>
@@ -1237,7 +1237,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:10</v>
@@ -1275,7 +1275,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:26</v>
@@ -1351,7 +1351,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:56</v>
@@ -1389,7 +1389,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:01</v>
@@ -1427,7 +1427,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>3:05</v>
@@ -1465,7 +1465,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:27</v>
@@ -1503,7 +1503,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:34</v>
@@ -1541,7 +1541,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:13</v>
@@ -1579,7 +1579,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:13</v>
@@ -1617,7 +1617,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:08</v>
@@ -1921,7 +1921,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:06</v>
@@ -1959,7 +1959,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:21</v>
@@ -2377,7 +2377,7 @@
         <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:25</v>
@@ -2415,7 +2415,7 @@
         <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>1:14</v>
@@ -2453,7 +2453,7 @@
         <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>2:59</v>
@@ -2491,7 +2491,7 @@
         <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:29</v>
@@ -2529,7 +2529,7 @@
         <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>2:34</v>
@@ -2567,7 +2567,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:48</v>
@@ -2605,7 +2605,7 @@
         <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:32</v>
@@ -2643,7 +2643,7 @@
         <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:49</v>
@@ -2681,7 +2681,7 @@
         <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:28</v>
@@ -2719,7 +2719,7 @@
         <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:37</v>
@@ -2757,7 +2757,7 @@
         <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:35</v>
@@ -2947,7 +2947,7 @@
         <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:11</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:57</v>
@@ -477,7 +477,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:10</v>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:10</v>
@@ -553,7 +553,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:52</v>
@@ -591,7 +591,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:50</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:32</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:27</v>
@@ -968,7 +968,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
@@ -2909,7 +2909,7 @@
         <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:11</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>מרסדס בנד – טינדר גירל</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a8%d7%a1%d7%93%d7%a1-%d7%91%d7%a0%d7%93-%d7%98%d7%99%d7%a0%d7%93%d7%a8-%d7%92%d7%99%d7%a8%d7%9c/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>השיר "טינדר גירל" של מרסדס בנד מציג באופן אירוני, מלודי ולעיתים גם משעשע – אך בו־זמנית כואב – דיוקן של בדידות אנושית בעידן הדיגיטלי. מאחורי ההומור והקלילות המוזיקלית מסתתרת ביקורת חברתית עדינה על הדרך שבה טכנולוגיה, אפליקציות ואלגוריתמים מחליפים קשרים</v>
       </c>
       <c r="G2" t="str">
-        <v>2:57</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>The Offspring</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>מרסדס בנד – טינדר גירל</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B3" t="str">
         <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -492,10 +492,10 @@
         <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:10</v>
+        <v>2:57</v>
       </c>
       <c r="H3" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B4" t="str">
         <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -530,10 +530,10 @@
         <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:10</v>
+        <v>4:10</v>
       </c>
       <c r="H4" t="str">
-        <v>Jason Derulo</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:52</v>
+        <v>2:10</v>
       </c>
       <c r="H5" t="str">
-        <v>lights</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B6" t="str">
-        <v>17 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>17 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H6" t="str">
-        <v>Telenova</v>
+        <v>lights</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>5:32</v>
+        <v>3:50</v>
       </c>
       <c r="H7" t="str">
-        <v>Marcin</v>
+        <v>Telenova</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B8" t="str">
-        <v>22 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>22 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:27</v>
+        <v>5:32</v>
       </c>
       <c r="H8" t="str">
-        <v>We Three</v>
+        <v>Marcin</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H9" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H10" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H11" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -834,10 +834,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H12" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -872,10 +872,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H13" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B14" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -910,10 +910,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H14" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -948,10 +948,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H15" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -986,10 +986,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H16" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B17" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1024,10 +1024,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H17" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B18" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1062,10 +1062,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H18" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B19" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1100,10 +1100,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H19" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:37</v>
+        <v>3:46</v>
       </c>
       <c r="H20" t="str">
-        <v>Bella White</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1176,10 +1176,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H21" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1214,10 +1214,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H22" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1252,10 +1252,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H23" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1290,10 +1290,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H24" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H25" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:56</v>
       </c>
       <c r="H26" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1404,10 +1404,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H27" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1442,10 +1442,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H28" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1480,10 +1480,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H29" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1518,10 +1518,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H30" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H31" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1597,7 +1597,7 @@
         <v>3:13</v>
       </c>
       <c r="H32" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H33" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H34" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H35" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H36" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H38" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1860,10 +1860,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H39" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B40" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1898,10 +1898,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H40" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H41" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H42" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H44" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H45" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H46" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H47" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B48" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2202,10 +2202,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H48" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H49" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H50" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H51" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B52" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2354,10 +2354,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H52" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H53" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B54" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2430,10 +2430,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H54" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H55" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2506,10 +2506,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H56" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2544,10 +2544,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H57" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2582,10 +2582,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H58" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2620,10 +2620,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H59" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B60" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2658,10 +2658,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H60" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B61" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2696,10 +2696,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H61" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H62" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H63" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H64" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H65" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H66" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H67" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:11</v>
+        <v>3:11</v>
       </c>
       <c r="H68" t="str">
-        <v>Ocean Alley</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:31</v>
+        <v>4:11</v>
       </c>
       <c r="H69" t="str">
-        <v>OneRepublic</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Ty Myers</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:42</v>
+        <v>4:16</v>
       </c>
       <c r="H71" t="str">
-        <v>JavaJazzFest</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:47</v>
+        <v>4:42</v>
       </c>
       <c r="H72" t="str">
-        <v>Teo Glacier</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:59</v>
+        <v>2:47</v>
       </c>
       <c r="H73" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:09</v>
+        <v>3:59</v>
       </c>
       <c r="H74" t="str">
-        <v>Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="H75" t="str">
-        <v>ella jane</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H76" t="str">
-        <v>Johnny Orlando</v>
+        <v>ella jane</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="H77" t="str">
-        <v>Kungs</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:15</v>
+        <v>3:32</v>
       </c>
       <c r="H78" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kungs</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:03</v>
+        <v>3:15</v>
       </c>
       <c r="H79" t="str">
-        <v>NathanEvanss</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H80" t="str">
-        <v>Stephen Sanchez</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:33</v>
+        <v>3:04</v>
       </c>
       <c r="H81" t="str">
-        <v>Bruno Mars</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="H82" t="str">
-        <v>MAX</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:11</v>
+        <v>2:53</v>
       </c>
       <c r="H83" t="str">
-        <v>Jessie J</v>
+        <v>MAX</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:45</v>
+        <v>4:11</v>
       </c>
       <c r="H84" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jessie J</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:00</v>
+        <v>2:45</v>
       </c>
       <c r="H85" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:27</v>
+        <v>4:00</v>
       </c>
       <c r="H86" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H87" t="str">
-        <v>Olivia Dean</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:34</v>
+        <v>3:25</v>
       </c>
       <c r="H88" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:25</v>
+        <v>3:34</v>
       </c>
       <c r="H89" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:26</v>
+        <v>2:25</v>
       </c>
       <c r="H90" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:46</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Keith Urban</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3874,7 +3874,7 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:24</v>
+        <v>4:46</v>
       </c>
       <c r="H92" t="str">
         <v>Keith Urban</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H93" t="str">
-        <v>Madonna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:06</v>
+        <v>2:52</v>
       </c>
       <c r="H94" t="str">
-        <v>Estás Tonné</v>
+        <v>Madonna</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-29</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:09</v>
+        <v>2:06</v>
       </c>
       <c r="H95" t="str">
-        <v>Anna Graves</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-29</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:11</v>
+        <v>3:09</v>
       </c>
       <c r="H96" t="str">
-        <v>Ocean Alley</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-29</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:40</v>
+        <v>5:11</v>
       </c>
       <c r="H97" t="str">
-        <v>Zara Larsson</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-29</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:49</v>
+        <v>3:40</v>
       </c>
       <c r="H98" t="str">
-        <v>Lauren Watkins</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-29</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:42</v>
+        <v>3:49</v>
       </c>
       <c r="H99" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-29</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:11</v>
+        <v>3:42</v>
       </c>
       <c r="H100" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-29</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:57</v>
+        <v>5:11</v>
       </c>
       <c r="H101" t="str">
-        <v>Lainey Wilson</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>For Hire</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>For Hire - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:44</v>
+        <v>3:57</v>
       </c>
       <c r="H102" t="str">
-        <v>People I’ve Met</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Aperture</v>
+        <v>For Hire</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>5:11</v>
+        <v>3:44</v>
       </c>
       <c r="H103" t="str">
-        <v>Harry Styles</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L103" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Opening Night</v>
+        <v>Aperture</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>HELP(2)</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G104" t="str">
-        <v>4:19</v>
+        <v>5:11</v>
       </c>
       <c r="H104" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L104" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>Opening Night</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Don't Be Dumb</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G105" t="str">
-        <v>2:20</v>
+        <v>4:19</v>
       </c>
       <c r="H105" t="str">
-        <v>A$AP Rocky</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>CAMBIARÉ</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G106" t="str">
-        <v>3:01</v>
+        <v>2:20</v>
       </c>
       <c r="H106" t="str">
-        <v>Luis Fonsi</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L106" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Piss In The Wind</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:29</v>
+        <v>3:01</v>
       </c>
       <c r="H107" t="str">
-        <v>Joji</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L107" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>High Key</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Vacancy</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G108" t="str">
-        <v>2:12</v>
+        <v>2:29</v>
       </c>
       <c r="H108" t="str">
-        <v>Ari Lennox</v>
+        <v>Joji</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L108" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>scared</v>
+        <v>High Key</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>scared - Single</v>
+        <v>Vacancy</v>
       </c>
       <c r="G109" t="str">
-        <v>3:46</v>
+        <v>2:12</v>
       </c>
       <c r="H109" t="str">
-        <v>Fred again..</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L109" t="str">
-        <v>scared - Fred again..</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Death of Love</v>
+        <v>scared</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Trying Times</v>
+        <v>scared - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H110" t="str">
-        <v>James Blake</v>
+        <v>Fred again..</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L110" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Death of Love</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G111" t="str">
-        <v>4:03</v>
+        <v>3:26</v>
       </c>
       <c r="H111" t="str">
-        <v>Parker McCollum</v>
+        <v>James Blake</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L111" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ATM</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>OCTANE</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G112" t="str">
-        <v>3:00</v>
+        <v>4:03</v>
       </c>
       <c r="H112" t="str">
-        <v>Don Toliver</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L112" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Flo Jackson</v>
+        <v>ATM</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>OCTANE</v>
       </c>
       <c r="G113" t="str">
-        <v>2:23</v>
+        <v>3:00</v>
       </c>
       <c r="H113" t="str">
-        <v>Flo Milli</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L113" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Creature of Habit</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:46</v>
+        <v>2:23</v>
       </c>
       <c r="H114" t="str">
-        <v>Courtney Barnett</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L114" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Puppet Parade</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Megadeth</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G115" t="str">
-        <v>4:40</v>
+        <v>2:46</v>
       </c>
       <c r="H115" t="str">
-        <v>Megadeth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L115" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>To Love Somebody</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Cruel World</v>
+        <v>Megadeth</v>
       </c>
       <c r="G116" t="str">
-        <v>3:57</v>
+        <v>4:40</v>
       </c>
       <c r="H116" t="str">
-        <v>Holly Humberstone</v>
+        <v>Megadeth</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L116" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G117" t="str">
-        <v>4:14</v>
+        <v>3:57</v>
       </c>
       <c r="H117" t="str">
-        <v>Cleo Sol</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L117" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>THE CORE - 核</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:50</v>
+        <v>4:14</v>
       </c>
       <c r="H118" t="str">
-        <v>XG</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L118" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Dead End</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Ricochet</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G119" t="str">
-        <v>4:05</v>
+        <v>2:50</v>
       </c>
       <c r="H119" t="str">
-        <v>Snail Mail</v>
+        <v>XG</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L119" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Dead End</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G120" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H120" t="str">
-        <v>Dove Cameron</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L120" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:02</v>
+        <v>3:52</v>
       </c>
       <c r="H121" t="str">
-        <v>Kenia Os</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L121" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>BAD</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BAD - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G122" t="str">
-        <v>2:15</v>
+        <v>3:02</v>
       </c>
       <c r="H122" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L122" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Losing You</v>
+        <v>BAD</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>F.I.G</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:22</v>
+        <v>2:15</v>
       </c>
       <c r="H123" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L123" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>Losing You</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G124" t="str">
-        <v>3:02</v>
+        <v>2:22</v>
       </c>
       <c r="H124" t="str">
-        <v>The Runarounds</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L124" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Infinito</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Yandel</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L125" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Sexy For Me</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Infinito</v>
       </c>
       <c r="G126" t="str">
-        <v>2:08</v>
+        <v>2:14</v>
       </c>
       <c r="H126" t="str">
-        <v>Jason Derulo</v>
+        <v>Yandel</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L126" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Turbulence</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G127" t="str">
-        <v>2:25</v>
+        <v>2:08</v>
       </c>
       <c r="H127" t="str">
-        <v>Wizkid</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L127" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Turbulence</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>2:25</v>
       </c>
       <c r="H128" t="str">
-        <v>Jelly Roll</v>
+        <v>Wizkid</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L128" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:47</v>
+        <v>2:59</v>
       </c>
       <c r="H129" t="str">
-        <v>Dolly Parton</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L129" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:53</v>
+        <v>3:47</v>
       </c>
       <c r="H130" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L130" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Act I</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G131" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H131" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L131" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Imposter</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Act I</v>
       </c>
       <c r="G132" t="str">
-        <v>2:38</v>
+        <v>3:43</v>
       </c>
       <c r="H132" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L132" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Imposter</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G133" t="str">
-        <v>6:01</v>
+        <v>2:38</v>
       </c>
       <c r="H133" t="str">
-        <v>Not for Radio</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L133" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:24</v>
+        <v>6:01</v>
       </c>
       <c r="H134" t="str">
-        <v>GIRLSET</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L134" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:41</v>
+        <v>2:24</v>
       </c>
       <c r="H135" t="str">
-        <v>Jessie Ware</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L135" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>LA VILLA</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H136" t="str">
-        <v>Ryan Castro</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L136" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G137" t="str">
-        <v>3:27</v>
+        <v>3:12</v>
       </c>
       <c r="H137" t="str">
-        <v>Denzel Curry</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L137" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Thick One</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Part 3</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G138" t="str">
-        <v>2:49</v>
+        <v>3:27</v>
       </c>
       <c r="H138" t="str">
-        <v>42 Dugg</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L138" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Thick One</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Part 3</v>
       </c>
       <c r="G139" t="str">
-        <v>3:59</v>
+        <v>2:49</v>
       </c>
       <c r="H139" t="str">
-        <v>Lucinda Williams</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L139" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>THUM</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>THUM - Single</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G140" t="str">
-        <v>2:11</v>
+        <v>3:59</v>
       </c>
       <c r="H140" t="str">
-        <v>Violet Grohl</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L140" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>THUM</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>The Great Satan</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:32</v>
+        <v>2:11</v>
       </c>
       <c r="H141" t="str">
-        <v>Rob Zombie</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L141" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Excuses For Love</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Hyperlove</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G142" t="str">
-        <v>3:04</v>
+        <v>3:32</v>
       </c>
       <c r="H142" t="str">
-        <v>MIKA</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L142" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>3 Tears</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>3 Tears - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G143" t="str">
-        <v>2:50</v>
+        <v>3:04</v>
       </c>
       <c r="H143" t="str">
-        <v>Mergui</v>
+        <v>MIKA</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L143" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Church Girl</v>
+        <v>3 Tears</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Church Girl - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>Carly Pearce</v>
+        <v>Mergui</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L144" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Funeral</v>
+        <v>Church Girl</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>4:03</v>
+        <v>3:19</v>
       </c>
       <c r="H145" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L145" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>dust to dust</v>
+        <v>Funeral</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G146" t="str">
-        <v>3:51</v>
+        <v>4:03</v>
       </c>
       <c r="H146" t="str">
-        <v>Truman Sinclair</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L146" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Say Yes</v>
+        <v>dust to dust</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Say Yes - Single</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H147" t="str">
-        <v>Marques Anthony</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L147" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Say Yes</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>CAMPILATION</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H148" t="str">
-        <v>Camper</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L148" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Ojalá</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ojalá - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G149" t="str">
-        <v>4:11</v>
+        <v>3:10</v>
       </c>
       <c r="H149" t="str">
-        <v>Lunay</v>
+        <v>Camper</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L149" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Ojalá</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:17</v>
+        <v>4:11</v>
       </c>
       <c r="H150" t="str">
-        <v>Ledbyher</v>
+        <v>Lunay</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L150" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H151" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L151" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H152" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L152" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H153" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L153" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H154" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L154" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G155" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H155" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L155" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H156" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L156" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G157" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H157" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L157" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H158" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L158" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G159" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H159" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L159" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H160" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L160" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H161" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L161" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H162" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L162" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H163" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L163" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H164" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L164" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H165" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L165" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G166" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H166" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L166" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G167" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H167" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L167" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H168" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L168" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H169" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L169" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H170" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L170" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H171" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L171" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Odisea</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Odisea - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:56</v>
+        <v>2:58</v>
       </c>
       <c r="H172" t="str">
-        <v>BASSYY</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L172" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Lucky Day</v>
+        <v>Odisea</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Speed Kills</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:13</v>
+        <v>3:56</v>
       </c>
       <c r="H173" t="str">
-        <v>Ally Evenson</v>
+        <v>BASSYY</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L173" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Breathe On It</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G174" t="str">
-        <v>4:00</v>
+        <v>3:13</v>
       </c>
       <c r="H174" t="str">
-        <v>Tauren Wells</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L174" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Easy</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Easy - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:30</v>
+        <v>4:00</v>
       </c>
       <c r="H175" t="str">
-        <v>lydi lynn</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L175" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Break Me In</v>
+        <v>Easy</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Break Me In - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:52</v>
+        <v>4:30</v>
       </c>
       <c r="H176" t="str">
-        <v>Joyce Wrice</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L176" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Long Live Love</v>
+        <v>Break Me In</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H177" t="str">
-        <v>Sugar</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L177" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Depressed</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Boycott Heaven</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H178" t="str">
-        <v>The Format</v>
+        <v>Sugar</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L178" t="str">
-        <v>Depressed - The Format</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Empty Hands</v>
+        <v>Depressed</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Empty Hands</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G179" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H179" t="str">
-        <v>Poppy</v>
+        <v>The Format</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L179" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G180" t="str">
-        <v>3:45</v>
+        <v>3:09</v>
       </c>
       <c r="H180" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Poppy</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L180" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Angela</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Angela - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G181" t="str">
-        <v>3:32</v>
+        <v>3:45</v>
       </c>
       <c r="H181" t="str">
-        <v>Hayden Everett</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L181" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Disappear</v>
+        <v>Angela</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Greyhound</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:31</v>
+        <v>3:32</v>
       </c>
       <c r="H182" t="str">
-        <v>Katie Tupper</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L182" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Catapult</v>
+        <v>Disappear</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Catapult - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G183" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H183" t="str">
-        <v>Cape Francis</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L183" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Think Twice</v>
+        <v>Catapult</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Think Twice - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:22</v>
+        <v>2:57</v>
       </c>
       <c r="H184" t="str">
-        <v>Leonie Biney</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L184" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>LOVESONGS</v>
+        <v>Think Twice</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:33</v>
+        <v>2:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Agnes</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L185" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Down South</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Down South - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G186" t="str">
-        <v>2:19</v>
+        <v>3:33</v>
       </c>
       <c r="H186" t="str">
-        <v>Trap Dickey</v>
+        <v>Agnes</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L186" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Down South</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H187" t="str">
-        <v>SALIMATA</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L187" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Love Like This</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Love Like This - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:30</v>
+        <v>2:16</v>
       </c>
       <c r="H188" t="str">
-        <v>Jacob Banks</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L188" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Plan Plan</v>
+        <v>Love Like This</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H189" t="str">
-        <v>Funky</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L189" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>double edged sword</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D190" t="str">
         <v>2026-01-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>double edged sword - Single</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G190" t="str">
-        <v>3:28</v>
+        <v>3:10</v>
       </c>
       <c r="H190" t="str">
-        <v>Hailey Picardi</v>
+        <v>Funky</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L190" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D191" t="str">
         <v>2026-01-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:27</v>
+        <v>3:28</v>
       </c>
       <c r="H191" t="str">
-        <v>Matt Hansen</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L191" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Decay</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D192" t="str">
         <v>2026-01-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H192" t="str">
-        <v>Pop Evil</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L192" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>3111</v>
+        <v>The Decay</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D193" t="str">
         <v>2026-01-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Goliath</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G193" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H193" t="str">
-        <v>Exodus</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L193" t="str">
-        <v>3111 - Exodus</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Touch My Love And Die</v>
+        <v>3111</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D194" t="str">
         <v>2026-01-29</v>
@@ -7747,68 +7747,106 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G194" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H194" t="str">
-        <v>Myrkur</v>
+        <v>Exodus</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L194" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G195" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H195" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K195" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L195" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D195" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
+      <c r="D196" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G195" t="str">
+      <c r="G196" t="str">
         <v>2:41</v>
       </c>
-      <c r="H195" t="str">
+      <c r="H196" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K195" t="str">
+      <c r="K196" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L195" t="str">
+      <c r="L196" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מרסדס בנד – טינדר גירל</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-29</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a8%d7%a1%d7%93%d7%a1-%d7%91%d7%a0%d7%93-%d7%98%d7%99%d7%a0%d7%93%d7%a8-%d7%92%d7%99%d7%a8%d7%9c/</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "טינדר גירל" של מרסדס בנד מציג באופן אירוני, מלודי ולעיתים גם משעשע – אך בו־זמנית כואב – דיוקן של בדידות אנושית בעידן הדיגיטלי. מאחורי ההומור והקלילות המוזיקלית מסתתרת ביקורת חברתית עדינה על הדרך שבה טכנולוגיה, אפליקציות ואלגוריתמים מחליפים קשרים</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>2:57</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>The Offspring</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מרסדס בנד – טינדר גירל</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:57</v>
+        <v>4:10</v>
       </c>
       <c r="H3" t="str">
-        <v>The Offspring</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:10</v>
+        <v>2:10</v>
       </c>
       <c r="H4" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:10</v>
+        <v>3:52</v>
       </c>
       <c r="H5" t="str">
-        <v>Jason Derulo</v>
+        <v>lights</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:52</v>
+        <v>3:50</v>
       </c>
       <c r="H6" t="str">
-        <v>lights</v>
+        <v>Telenova</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>I Played "How Music Works" LIVE To 1500 People</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:50</v>
+        <v>5:32</v>
       </c>
       <c r="H7" t="str">
-        <v>Telenova</v>
+        <v>Marcin</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>5:32</v>
+        <v>4:27</v>
       </c>
       <c r="H8" t="str">
-        <v>Marcin</v>
+        <v>We Three</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:27</v>
+        <v>3:01</v>
       </c>
       <c r="H9" t="str">
-        <v>We Three</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:01</v>
+        <v>3:20</v>
       </c>
       <c r="H10" t="str">
-        <v>Timebelle Official</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:20</v>
+        <v>3:34</v>
       </c>
       <c r="H11" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -834,10 +834,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:34</v>
+        <v>4:01</v>
       </c>
       <c r="H12" t="str">
-        <v>Clinton Kane</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B13" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -872,10 +872,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:01</v>
+        <v>3:24</v>
       </c>
       <c r="H13" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -910,10 +910,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:24</v>
+        <v>5:52</v>
       </c>
       <c r="H14" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -948,10 +948,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>5:52</v>
+        <v>5:01</v>
       </c>
       <c r="H15" t="str">
-        <v>Harry Styles</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -986,10 +986,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>5:01</v>
+        <v>4:12</v>
       </c>
       <c r="H16" t="str">
-        <v>Neal Francis</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B17" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1024,10 +1024,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:12</v>
+        <v>3:59</v>
       </c>
       <c r="H17" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B18" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1062,10 +1062,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:59</v>
+        <v>2:56</v>
       </c>
       <c r="H18" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H19" t="str">
-        <v>Cliff Richard</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:46</v>
+        <v>4:37</v>
       </c>
       <c r="H20" t="str">
-        <v>Jessie Ware</v>
+        <v>Bella White</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1176,10 +1176,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:37</v>
+        <v>4:06</v>
       </c>
       <c r="H21" t="str">
-        <v>Bella White</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1214,10 +1214,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:06</v>
+        <v>3:54</v>
       </c>
       <c r="H22" t="str">
-        <v>Ryan Wright</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1252,10 +1252,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:54</v>
+        <v>4:10</v>
       </c>
       <c r="H23" t="str">
-        <v>Dove Cameron</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1290,10 +1290,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:10</v>
+        <v>3:26</v>
       </c>
       <c r="H24" t="str">
-        <v>Parker McCollum</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H25" t="str">
-        <v>Matt Hansen</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:56</v>
       </c>
       <c r="H26" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1404,10 +1404,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H27" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1442,10 +1442,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H28" t="str">
-        <v>Tauren Wells</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1480,10 +1480,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:05</v>
+        <v>2:27</v>
       </c>
       <c r="H29" t="str">
-        <v>Maiah Manser</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1518,10 +1518,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H30" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H31" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1597,7 +1597,7 @@
         <v>3:13</v>
       </c>
       <c r="H32" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H33" t="str">
-        <v>Louis Tomlinson</v>
+        <v>CAIN</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:08</v>
+        <v>5:14</v>
       </c>
       <c r="H34" t="str">
-        <v>CAIN</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>5:14</v>
+        <v>2:59</v>
       </c>
       <c r="H35" t="str">
-        <v>Harry Styles</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:59</v>
+        <v>4:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Lana Lubany</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:21</v>
+        <v>4:09</v>
       </c>
       <c r="H37" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B39" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1860,10 +1860,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:34</v>
+        <v>3:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B40" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1898,10 +1898,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H40" t="str">
-        <v>Olivia Dean</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H41" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H42" t="str">
-        <v>The Avett Brothers</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:21</v>
+        <v>7:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Jordana Bryant</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>7:21</v>
+        <v>3:17</v>
       </c>
       <c r="H44" t="str">
-        <v>Katy Perry</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:17</v>
+        <v>3:45</v>
       </c>
       <c r="H45" t="str">
-        <v>Lauren Watkins</v>
+        <v>Tones And I</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:45</v>
+        <v>3:57</v>
       </c>
       <c r="H46" t="str">
-        <v>Tones And I</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:57</v>
+        <v>3:03</v>
       </c>
       <c r="H47" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B48" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2202,10 +2202,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:03</v>
+        <v>4:27</v>
       </c>
       <c r="H48" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:27</v>
+        <v>4:34</v>
       </c>
       <c r="H49" t="str">
-        <v>Chappell Roan</v>
+        <v>Armik</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:34</v>
+        <v>2:54</v>
       </c>
       <c r="H50" t="str">
-        <v>Armik</v>
+        <v>LØLØ</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:54</v>
+        <v>3:25</v>
       </c>
       <c r="H51" t="str">
-        <v>LØLØ</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2354,10 +2354,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:25</v>
+        <v>2:01</v>
       </c>
       <c r="H52" t="str">
-        <v>Tenille Townes</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:01</v>
+        <v>2:25</v>
       </c>
       <c r="H53" t="str">
-        <v>Alan Walker</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2430,10 +2430,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:25</v>
+        <v>1:14</v>
       </c>
       <c r="H54" t="str">
-        <v>Charli xcx</v>
+        <v>Labrinth</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>1:14</v>
+        <v>2:59</v>
       </c>
       <c r="H55" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2506,10 +2506,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:59</v>
+        <v>2:29</v>
       </c>
       <c r="H56" t="str">
-        <v>Charlie Puth</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2544,10 +2544,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:29</v>
+        <v>2:34</v>
       </c>
       <c r="H57" t="str">
-        <v>Girl Tones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2582,10 +2582,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:34</v>
+        <v>3:48</v>
       </c>
       <c r="H58" t="str">
-        <v>Jagwar Twin</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B59" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2620,10 +2620,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:48</v>
+        <v>3:32</v>
       </c>
       <c r="H59" t="str">
-        <v>Caroline Jones</v>
+        <v>The Beaches</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B60" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2658,10 +2658,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:32</v>
+        <v>3:49</v>
       </c>
       <c r="H60" t="str">
-        <v>The Beaches</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2696,10 +2696,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:49</v>
+        <v>4:28</v>
       </c>
       <c r="H61" t="str">
-        <v>Dolly Parton</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:28</v>
+        <v>3:37</v>
       </c>
       <c r="H62" t="str">
-        <v>Madison Beer</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:37</v>
+        <v>3:35</v>
       </c>
       <c r="H63" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:35</v>
+        <v>2:31</v>
       </c>
       <c r="H64" t="str">
-        <v>Megan Moroney</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:31</v>
+        <v>3:21</v>
       </c>
       <c r="H65" t="str">
-        <v>Julia Cole Music</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:21</v>
+        <v>5:24</v>
       </c>
       <c r="H66" t="str">
-        <v>Lily Allen</v>
+        <v>Nickless</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>5:24</v>
+        <v>3:11</v>
       </c>
       <c r="H67" t="str">
-        <v>Nickless</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:11</v>
+        <v>4:11</v>
       </c>
       <c r="H68" t="str">
-        <v>Peach PRC</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:11</v>
+        <v>3:31</v>
       </c>
       <c r="H69" t="str">
-        <v>Ocean Alley</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:31</v>
+        <v>4:16</v>
       </c>
       <c r="H70" t="str">
-        <v>OneRepublic</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:16</v>
+        <v>4:42</v>
       </c>
       <c r="H71" t="str">
-        <v>Ty Myers</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:42</v>
+        <v>2:47</v>
       </c>
       <c r="H72" t="str">
-        <v>JavaJazzFest</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:47</v>
+        <v>3:59</v>
       </c>
       <c r="H73" t="str">
-        <v>Teo Glacier</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:59</v>
+        <v>4:09</v>
       </c>
       <c r="H74" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:09</v>
+        <v>3:24</v>
       </c>
       <c r="H75" t="str">
-        <v>Louie TheSinger</v>
+        <v>ella jane</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:24</v>
+        <v>3:14</v>
       </c>
       <c r="H76" t="str">
-        <v>ella jane</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:14</v>
+        <v>3:32</v>
       </c>
       <c r="H77" t="str">
-        <v>Johnny Orlando</v>
+        <v>Kungs</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:32</v>
+        <v>3:15</v>
       </c>
       <c r="H78" t="str">
-        <v>Kungs</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:15</v>
+        <v>3:03</v>
       </c>
       <c r="H79" t="str">
-        <v>Billy Raffoul</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H80" t="str">
-        <v>NathanEvanss</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:04</v>
+        <v>3:33</v>
       </c>
       <c r="H81" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:33</v>
+        <v>2:53</v>
       </c>
       <c r="H82" t="str">
-        <v>Bruno Mars</v>
+        <v>MAX</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:53</v>
+        <v>4:11</v>
       </c>
       <c r="H83" t="str">
-        <v>MAX</v>
+        <v>Jessie J</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:11</v>
+        <v>2:45</v>
       </c>
       <c r="H84" t="str">
-        <v>Jessie J</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:45</v>
+        <v>4:00</v>
       </c>
       <c r="H85" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:00</v>
+        <v>3:27</v>
       </c>
       <c r="H86" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:27</v>
+        <v>3:25</v>
       </c>
       <c r="H87" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:25</v>
+        <v>3:34</v>
       </c>
       <c r="H88" t="str">
-        <v>Olivia Dean</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:34</v>
+        <v>2:25</v>
       </c>
       <c r="H89" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:25</v>
+        <v>3:26</v>
       </c>
       <c r="H90" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H91" t="str">
-        <v>Demi Lovato</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3874,7 +3874,7 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:46</v>
+        <v>3:24</v>
       </c>
       <c r="H92" t="str">
         <v>Keith Urban</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:24</v>
+        <v>2:52</v>
       </c>
       <c r="H93" t="str">
-        <v>Keith Urban</v>
+        <v>Madonna</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:52</v>
+        <v>2:06</v>
       </c>
       <c r="H94" t="str">
-        <v>Madonna</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-29</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:06</v>
+        <v>3:09</v>
       </c>
       <c r="H95" t="str">
-        <v>Estás Tonné</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-29</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:09</v>
+        <v>5:11</v>
       </c>
       <c r="H96" t="str">
-        <v>Anna Graves</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-29</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>5:11</v>
+        <v>3:40</v>
       </c>
       <c r="H97" t="str">
-        <v>Ocean Alley</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-29</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:40</v>
+        <v>3:49</v>
       </c>
       <c r="H98" t="str">
-        <v>Zara Larsson</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-29</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:49</v>
+        <v>3:42</v>
       </c>
       <c r="H99" t="str">
-        <v>Lauren Watkins</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-29</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:42</v>
+        <v>5:11</v>
       </c>
       <c r="H100" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-29</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:11</v>
+        <v>3:57</v>
       </c>
       <c r="H101" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>For Hire</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:57</v>
+        <v>3:44</v>
       </c>
       <c r="H102" t="str">
-        <v>Lainey Wilson</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L102" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>For Hire</v>
+        <v>Aperture</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>For Hire - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G103" t="str">
-        <v>3:44</v>
+        <v>5:11</v>
       </c>
       <c r="H103" t="str">
-        <v>People I’ve Met</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L103" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Aperture</v>
+        <v>Opening Night</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G104" t="str">
-        <v>5:11</v>
+        <v>4:19</v>
       </c>
       <c r="H104" t="str">
-        <v>Harry Styles</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L104" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Opening Night</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>HELP(2)</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G105" t="str">
-        <v>4:19</v>
+        <v>2:20</v>
       </c>
       <c r="H105" t="str">
-        <v>Arctic Monkeys</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L105" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Don't Be Dumb</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>2:20</v>
+        <v>3:01</v>
       </c>
       <c r="H106" t="str">
-        <v>A$AP Rocky</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L106" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G107" t="str">
-        <v>3:01</v>
+        <v>2:29</v>
       </c>
       <c r="H107" t="str">
-        <v>Luis Fonsi</v>
+        <v>Joji</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L107" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>High Key</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Piss In The Wind</v>
+        <v>Vacancy</v>
       </c>
       <c r="G108" t="str">
-        <v>2:29</v>
+        <v>2:12</v>
       </c>
       <c r="H108" t="str">
-        <v>Joji</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L108" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>High Key</v>
+        <v>scared</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Vacancy</v>
+        <v>scared - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:12</v>
+        <v>3:46</v>
       </c>
       <c r="H109" t="str">
-        <v>Ari Lennox</v>
+        <v>Fred again..</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L109" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>scared</v>
+        <v>Death of Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>scared - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G110" t="str">
-        <v>3:46</v>
+        <v>3:26</v>
       </c>
       <c r="H110" t="str">
-        <v>Fred again..</v>
+        <v>James Blake</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L110" t="str">
-        <v>scared - Fred again..</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Death of Love</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Trying Times</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G111" t="str">
-        <v>3:26</v>
+        <v>4:03</v>
       </c>
       <c r="H111" t="str">
-        <v>James Blake</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L111" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>ATM</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>OCTANE</v>
       </c>
       <c r="G112" t="str">
-        <v>4:03</v>
+        <v>3:00</v>
       </c>
       <c r="H112" t="str">
-        <v>Parker McCollum</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L112" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ATM</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>OCTANE</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:00</v>
+        <v>2:23</v>
       </c>
       <c r="H113" t="str">
-        <v>Don Toliver</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L113" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Flo Jackson</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G114" t="str">
-        <v>2:23</v>
+        <v>2:46</v>
       </c>
       <c r="H114" t="str">
-        <v>Flo Milli</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L114" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Creature of Habit</v>
+        <v>Megadeth</v>
       </c>
       <c r="G115" t="str">
-        <v>2:46</v>
+        <v>4:40</v>
       </c>
       <c r="H115" t="str">
-        <v>Courtney Barnett</v>
+        <v>Megadeth</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L115" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Puppet Parade</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Megadeth</v>
+        <v>Cruel World</v>
       </c>
       <c r="G116" t="str">
-        <v>4:40</v>
+        <v>3:57</v>
       </c>
       <c r="H116" t="str">
-        <v>Megadeth</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L116" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>To Love Somebody</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Cruel World</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:57</v>
+        <v>4:14</v>
       </c>
       <c r="H117" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L117" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G118" t="str">
-        <v>4:14</v>
+        <v>2:50</v>
       </c>
       <c r="H118" t="str">
-        <v>Cleo Sol</v>
+        <v>XG</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L118" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Dead End</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>THE CORE - 核</v>
+        <v>Ricochet</v>
       </c>
       <c r="G119" t="str">
-        <v>2:50</v>
+        <v>4:05</v>
       </c>
       <c r="H119" t="str">
-        <v>XG</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L119" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Dead End</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Ricochet</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>4:05</v>
+        <v>3:52</v>
       </c>
       <c r="H120" t="str">
-        <v>Snail Mail</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L120" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G121" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H121" t="str">
-        <v>Dove Cameron</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L121" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Una y Otra Vez</v>
+        <v>BAD</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:02</v>
+        <v>2:15</v>
       </c>
       <c r="H122" t="str">
-        <v>Kenia Os</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L122" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>BAD</v>
+        <v>Losing You</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>BAD - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G123" t="str">
-        <v>2:15</v>
+        <v>2:22</v>
       </c>
       <c r="H123" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L123" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Losing You</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>F.I.G</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:22</v>
+        <v>3:02</v>
       </c>
       <c r="H124" t="str">
-        <v>Naomi Scott</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L124" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>Infinito</v>
       </c>
       <c r="G125" t="str">
-        <v>3:02</v>
+        <v>2:14</v>
       </c>
       <c r="H125" t="str">
-        <v>The Runarounds</v>
+        <v>Yandel</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L125" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Infinito</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G126" t="str">
-        <v>2:14</v>
+        <v>2:08</v>
       </c>
       <c r="H126" t="str">
-        <v>Yandel</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L126" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Sexy For Me</v>
+        <v>Turbulence</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G127" t="str">
-        <v>2:08</v>
+        <v>2:25</v>
       </c>
       <c r="H127" t="str">
-        <v>Jason Derulo</v>
+        <v>Wizkid</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L127" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turbulence</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G128" t="str">
-        <v>2:25</v>
+        <v>2:59</v>
       </c>
       <c r="H128" t="str">
-        <v>Wizkid</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L128" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:59</v>
+        <v>3:47</v>
       </c>
       <c r="H129" t="str">
-        <v>Jelly Roll</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L129" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G130" t="str">
-        <v>3:47</v>
+        <v>2:53</v>
       </c>
       <c r="H130" t="str">
-        <v>Dolly Parton</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L130" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Act I</v>
       </c>
       <c r="G131" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H131" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L131" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>Imposter</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Act I</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G132" t="str">
-        <v>3:43</v>
+        <v>2:38</v>
       </c>
       <c r="H132" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L132" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Imposter</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:38</v>
+        <v>6:01</v>
       </c>
       <c r="H133" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L133" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>6:01</v>
+        <v>2:24</v>
       </c>
       <c r="H134" t="str">
-        <v>Not for Radio</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L134" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:24</v>
+        <v>3:41</v>
       </c>
       <c r="H135" t="str">
-        <v>GIRLSET</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L135" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>I Could Get Used To This</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G136" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H136" t="str">
-        <v>Jessie Ware</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L136" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>LA VILLA</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G137" t="str">
-        <v>3:12</v>
+        <v>3:27</v>
       </c>
       <c r="H137" t="str">
-        <v>Ryan Castro</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L137" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>Thick One</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Part 3</v>
       </c>
       <c r="G138" t="str">
-        <v>3:27</v>
+        <v>2:49</v>
       </c>
       <c r="H138" t="str">
-        <v>Denzel Curry</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L138" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Thick One</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Part 3</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G139" t="str">
-        <v>2:49</v>
+        <v>3:59</v>
       </c>
       <c r="H139" t="str">
-        <v>42 Dugg</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L139" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>THUM</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>World's Gone Wrong</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:59</v>
+        <v>2:11</v>
       </c>
       <c r="H140" t="str">
-        <v>Lucinda Williams</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L140" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>THUM</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>THUM - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G141" t="str">
-        <v>2:11</v>
+        <v>3:32</v>
       </c>
       <c r="H141" t="str">
-        <v>Violet Grohl</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L141" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Great Satan</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G142" t="str">
-        <v>3:32</v>
+        <v>3:04</v>
       </c>
       <c r="H142" t="str">
-        <v>Rob Zombie</v>
+        <v>MIKA</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L142" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Excuses For Love</v>
+        <v>3 Tears</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Hyperlove</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:04</v>
+        <v>2:50</v>
       </c>
       <c r="H143" t="str">
-        <v>MIKA</v>
+        <v>Mergui</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L143" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>3 Tears</v>
+        <v>Church Girl</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>3 Tears - Single</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>3:19</v>
       </c>
       <c r="H144" t="str">
-        <v>Mergui</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L144" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Church Girl</v>
+        <v>Funeral</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Church Girl - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G145" t="str">
-        <v>3:19</v>
+        <v>4:03</v>
       </c>
       <c r="H145" t="str">
-        <v>Carly Pearce</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L145" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Funeral</v>
+        <v>dust to dust</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G146" t="str">
-        <v>4:03</v>
+        <v>3:51</v>
       </c>
       <c r="H146" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L146" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>dust to dust</v>
+        <v>Say Yes</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:51</v>
+        <v>2:50</v>
       </c>
       <c r="H147" t="str">
-        <v>Truman Sinclair</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L147" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Say Yes</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Say Yes - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G148" t="str">
-        <v>2:50</v>
+        <v>3:10</v>
       </c>
       <c r="H148" t="str">
-        <v>Marques Anthony</v>
+        <v>Camper</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L148" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Ojalá</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>CAMPILATION</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:10</v>
+        <v>4:11</v>
       </c>
       <c r="H149" t="str">
-        <v>Camper</v>
+        <v>Lunay</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L149" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Ojalá</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ojalá - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:11</v>
+        <v>2:17</v>
       </c>
       <c r="H150" t="str">
-        <v>Lunay</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L150" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Wallflower</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:17</v>
+        <v>3:25</v>
       </c>
       <c r="H151" t="str">
-        <v>Ledbyher</v>
+        <v>Sikarus</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L151" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Wallflower</v>
+        <v>You Phase</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Wallflower - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:25</v>
+        <v>2:51</v>
       </c>
       <c r="H152" t="str">
-        <v>Sikarus</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L152" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>You Phase</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>You Phase - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:51</v>
+        <v>2:40</v>
       </c>
       <c r="H153" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L153" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Miss Independent</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Miss Independent - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G154" t="str">
-        <v>2:40</v>
+        <v>5:47</v>
       </c>
       <c r="H154" t="str">
-        <v>1Ski OG</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L154" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>go again</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>go again - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>5:47</v>
+        <v>2:07</v>
       </c>
       <c r="H155" t="str">
-        <v>Elevation Worship</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L155" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>go again</v>
+        <v>Autopilot</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>go again - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G156" t="str">
-        <v>2:07</v>
+        <v>2:46</v>
       </c>
       <c r="H156" t="str">
-        <v>NateTaylorr</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L156" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Autopilot</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Autopilot</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:46</v>
+        <v>3:04</v>
       </c>
       <c r="H157" t="str">
-        <v>ALEXSUCKS</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L157" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>In Violet</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G158" t="str">
-        <v>3:04</v>
+        <v>4:09</v>
       </c>
       <c r="H158" t="str">
-        <v>SPELLLING</v>
+        <v>Searows</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L158" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>In Violet</v>
+        <v>Baby Run</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:09</v>
+        <v>4:47</v>
       </c>
       <c r="H159" t="str">
-        <v>Searows</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L159" t="str">
-        <v>In Violet - Searows</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Baby Run</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Baby Run - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>4:47</v>
+        <v>3:06</v>
       </c>
       <c r="H160" t="str">
-        <v>Jimi Jules</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L160" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>What If We Don't</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:06</v>
+        <v>2:58</v>
       </c>
       <c r="H161" t="str">
-        <v>Ashley McBryde</v>
+        <v>Juanes</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L161" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Hagamos Que</v>
+        <v>World Change Me</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:58</v>
+        <v>3:03</v>
       </c>
       <c r="H162" t="str">
-        <v>Juanes</v>
+        <v>Max McNown</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L162" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>World Change Me</v>
+        <v>Exclusive</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>World Change Me - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>3:03</v>
+        <v>3:20</v>
       </c>
       <c r="H163" t="str">
-        <v>Max McNown</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L163" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Exclusive</v>
+        <v>Say Less</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Exclusive - EP</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:20</v>
+        <v>2:18</v>
       </c>
       <c r="H164" t="str">
-        <v>Hudson Westbrook</v>
+        <v>JYT</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L164" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Say Less</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Say Less - Single</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G165" t="str">
-        <v>2:18</v>
+        <v>3:52</v>
       </c>
       <c r="H165" t="str">
-        <v>JYT</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L165" t="str">
-        <v>Say Less - JYT</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Angels Cry</v>
+        <v>Over You</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G166" t="str">
-        <v>3:52</v>
+        <v>4:44</v>
       </c>
       <c r="H166" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L166" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Over You</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>A Love For Strangers</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:44</v>
+        <v>2:42</v>
       </c>
       <c r="H167" t="str">
-        <v>Chet Faker</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L167" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:42</v>
+        <v>3:06</v>
       </c>
       <c r="H168" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L168" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H169" t="str">
-        <v>Disco Lines</v>
+        <v>David Guetta</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L169" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Rejoice</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:48</v>
+        <v>4:20</v>
       </c>
       <c r="H170" t="str">
-        <v>David Guetta</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L170" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Rejoice</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Rejoice - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>4:20</v>
+        <v>2:58</v>
       </c>
       <c r="H171" t="str">
-        <v>Def Leppard</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L171" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Odisea</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:58</v>
+        <v>3:56</v>
       </c>
       <c r="H172" t="str">
-        <v>Honey Dijon</v>
+        <v>BASSYY</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L172" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Odisea</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Odisea - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G173" t="str">
-        <v>3:56</v>
+        <v>3:13</v>
       </c>
       <c r="H173" t="str">
-        <v>BASSYY</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L173" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Lucky Day</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Speed Kills</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:13</v>
+        <v>4:00</v>
       </c>
       <c r="H174" t="str">
-        <v>Ally Evenson</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L174" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Breathe On It</v>
+        <v>Easy</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:00</v>
+        <v>4:30</v>
       </c>
       <c r="H175" t="str">
-        <v>Tauren Wells</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L175" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Easy</v>
+        <v>Break Me In</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Easy - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:30</v>
+        <v>2:52</v>
       </c>
       <c r="H176" t="str">
-        <v>lydi lynn</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L176" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Break Me In</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Break Me In - Single</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:52</v>
+        <v>2:36</v>
       </c>
       <c r="H177" t="str">
-        <v>Joyce Wrice</v>
+        <v>Sugar</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L177" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Long Live Love</v>
+        <v>Depressed</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G178" t="str">
-        <v>2:36</v>
+        <v>3:32</v>
       </c>
       <c r="H178" t="str">
-        <v>Sugar</v>
+        <v>The Format</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L178" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Depressed</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Boycott Heaven</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G179" t="str">
-        <v>3:32</v>
+        <v>3:09</v>
       </c>
       <c r="H179" t="str">
-        <v>The Format</v>
+        <v>Poppy</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L179" t="str">
-        <v>Depressed - The Format</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Empty Hands</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Empty Hands</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G180" t="str">
-        <v>3:09</v>
+        <v>3:45</v>
       </c>
       <c r="H180" t="str">
-        <v>Poppy</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L180" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The Long Surrender</v>
+        <v>Angela</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>The Long Surrender</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:45</v>
+        <v>3:32</v>
       </c>
       <c r="H181" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L181" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Angela</v>
+        <v>Disappear</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Angela - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G182" t="str">
-        <v>3:32</v>
+        <v>3:31</v>
       </c>
       <c r="H182" t="str">
-        <v>Hayden Everett</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L182" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Disappear</v>
+        <v>Catapult</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Greyhound</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:31</v>
+        <v>2:57</v>
       </c>
       <c r="H183" t="str">
-        <v>Katie Tupper</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L183" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Catapult</v>
+        <v>Think Twice</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Catapult - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:57</v>
+        <v>2:22</v>
       </c>
       <c r="H184" t="str">
-        <v>Cape Francis</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L184" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Think Twice</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Think Twice - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G185" t="str">
-        <v>2:22</v>
+        <v>3:33</v>
       </c>
       <c r="H185" t="str">
-        <v>Leonie Biney</v>
+        <v>Agnes</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L185" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>LOVESONGS</v>
+        <v>Down South</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:33</v>
+        <v>2:19</v>
       </c>
       <c r="H186" t="str">
-        <v>Agnes</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L186" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Down South</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Down South - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:19</v>
+        <v>2:16</v>
       </c>
       <c r="H187" t="str">
-        <v>Trap Dickey</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L187" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Love Like This</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:16</v>
+        <v>3:30</v>
       </c>
       <c r="H188" t="str">
-        <v>SALIMATA</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L188" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Love Like This</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Love Like This - Single</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G189" t="str">
-        <v>3:30</v>
+        <v>3:10</v>
       </c>
       <c r="H189" t="str">
-        <v>Jacob Banks</v>
+        <v>Funky</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L189" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Plan Plan</v>
+        <v>double edged sword</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D190" t="str">
         <v>2026-01-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:10</v>
+        <v>3:28</v>
       </c>
       <c r="H190" t="str">
-        <v>Funky</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L190" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>double edged sword</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D191" t="str">
         <v>2026-01-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>double edged sword - Single</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:28</v>
+        <v>3:27</v>
       </c>
       <c r="H191" t="str">
-        <v>Hailey Picardi</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L191" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>The Decay</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D192" t="str">
         <v>2026-01-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G192" t="str">
-        <v>3:27</v>
+        <v>3:20</v>
       </c>
       <c r="H192" t="str">
-        <v>Matt Hansen</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L192" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Decay</v>
+        <v>3111</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D193" t="str">
         <v>2026-01-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>Goliath</v>
       </c>
       <c r="G193" t="str">
-        <v>3:20</v>
+        <v>4:08</v>
       </c>
       <c r="H193" t="str">
-        <v>Pop Evil</v>
+        <v>Exodus</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L193" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>3111</v>
+        <v>Touch My Love And Die</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D194" t="str">
         <v>2026-01-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Goliath</v>
+        <v>Touch My Love And Die - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:08</v>
+        <v>2:57</v>
       </c>
       <c r="H194" t="str">
-        <v>Exodus</v>
+        <v>Myrkur</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
       </c>
       <c r="L194" t="str">
-        <v>3111 - Exodus</v>
+        <v>Touch My Love And Die - Myrkur</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Touch My Love And Die</v>
+        <v>Bomb To A Knife Fight</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D195" t="str">
         <v>2026-01-29</v>
@@ -7785,68 +7785,30 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Bomb To A Knife Fight - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H195" t="str">
-        <v>Myrkur</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
       <c r="L195" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Bomb To A Knife Fight</v>
-      </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
-      </c>
-      <c r="D196" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
-        <v>Bomb To A Knife Fight - Single</v>
-      </c>
-      <c r="G196" t="str">
-        <v>2:41</v>
-      </c>
-      <c r="H196" t="str">
-        <v>The Barbarians of California</v>
-      </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
-      </c>
-      <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
-      </c>
-      <c r="L196" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>איתי בירמן – אין אהבה ללא כאב</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%91%d7%99%d7%a8%d7%9e%d7%9f-%d7%90%d7%99%d7%9f-%d7%90%d7%94%d7%91%d7%94-%d7%9c%d7%9c%d7%90-%d7%9b%d7%90%d7%91/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>השיר "אין אהבה ללא כאב" של איתי בקרמן הוא יצירה אישית, חשופה ובוגרת, שמצליחה להפוך סיפור משפחתי מורכב לבלדה רוקית מידטמפו בעלת עוצמה רגשית. זהו שיר שמתבונן באהבה לא כאגדה רומנטית, אלא כתהליך אנושי עמוק, רצוף סדקים, בחירות קשות ויכולת</v>
       </c>
       <c r="G2" t="str">
-        <v>2:57</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>The Offspring</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>איתי בירמן – אין אהבה ללא כאב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B3" t="str">
         <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -492,10 +492,10 @@
         <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:10</v>
+        <v>2:57</v>
       </c>
       <c r="H3" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B4" t="str">
         <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -530,10 +530,10 @@
         <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:10</v>
+        <v>4:10</v>
       </c>
       <c r="H4" t="str">
-        <v>Jason Derulo</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:52</v>
+        <v>2:10</v>
       </c>
       <c r="H5" t="str">
-        <v>lights</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B6" t="str">
-        <v>19 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>19 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H6" t="str">
-        <v>Telenova</v>
+        <v>lights</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>5:32</v>
+        <v>3:50</v>
       </c>
       <c r="H7" t="str">
-        <v>Marcin</v>
+        <v>Telenova</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>I Played "How Music Works" LIVE To 1500 People</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:27</v>
+        <v>5:32</v>
       </c>
       <c r="H8" t="str">
-        <v>We Three</v>
+        <v>Marcin</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H9" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H10" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H11" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -834,10 +834,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H12" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -872,10 +872,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H13" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B14" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -910,10 +910,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H14" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -948,10 +948,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H15" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -986,10 +986,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H16" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B17" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1024,10 +1024,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H17" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B18" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1062,10 +1062,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H18" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1100,10 +1100,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H19" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1138,10 +1138,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:37</v>
+        <v>3:46</v>
       </c>
       <c r="H20" t="str">
-        <v>Bella White</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1176,10 +1176,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H21" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1214,10 +1214,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H22" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1252,10 +1252,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H23" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1290,10 +1290,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H24" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H25" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:56</v>
       </c>
       <c r="H26" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1404,10 +1404,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H27" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1442,10 +1442,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H28" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1480,10 +1480,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H29" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1518,10 +1518,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H30" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H31" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1597,7 +1597,7 @@
         <v>3:13</v>
       </c>
       <c r="H32" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H33" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H34" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H35" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H36" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H38" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1860,10 +1860,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H39" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B40" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1898,10 +1898,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H40" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H41" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H42" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H44" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H45" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H46" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H47" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B48" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2202,10 +2202,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H48" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H49" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H50" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H51" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B52" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2354,10 +2354,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H52" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H53" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B54" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2430,10 +2430,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H54" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H55" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2506,10 +2506,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H56" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2544,10 +2544,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H57" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2582,10 +2582,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H58" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2620,10 +2620,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H59" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B60" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2658,10 +2658,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H60" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B61" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2696,10 +2696,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H61" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H62" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H63" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H64" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H65" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H66" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H67" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:11</v>
+        <v>3:11</v>
       </c>
       <c r="H68" t="str">
-        <v>Ocean Alley</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:31</v>
+        <v>4:11</v>
       </c>
       <c r="H69" t="str">
-        <v>OneRepublic</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Ty Myers</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:42</v>
+        <v>4:16</v>
       </c>
       <c r="H71" t="str">
-        <v>JavaJazzFest</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:47</v>
+        <v>4:42</v>
       </c>
       <c r="H72" t="str">
-        <v>Teo Glacier</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:59</v>
+        <v>2:47</v>
       </c>
       <c r="H73" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:09</v>
+        <v>3:59</v>
       </c>
       <c r="H74" t="str">
-        <v>Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="H75" t="str">
-        <v>ella jane</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H76" t="str">
-        <v>Johnny Orlando</v>
+        <v>ella jane</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="H77" t="str">
-        <v>Kungs</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:15</v>
+        <v>3:32</v>
       </c>
       <c r="H78" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kungs</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:03</v>
+        <v>3:15</v>
       </c>
       <c r="H79" t="str">
-        <v>NathanEvanss</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H80" t="str">
-        <v>Stephen Sanchez</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:33</v>
+        <v>3:04</v>
       </c>
       <c r="H81" t="str">
-        <v>Bruno Mars</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="H82" t="str">
-        <v>MAX</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:11</v>
+        <v>2:53</v>
       </c>
       <c r="H83" t="str">
-        <v>Jessie J</v>
+        <v>MAX</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:45</v>
+        <v>4:11</v>
       </c>
       <c r="H84" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jessie J</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:00</v>
+        <v>2:45</v>
       </c>
       <c r="H85" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:27</v>
+        <v>4:00</v>
       </c>
       <c r="H86" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H87" t="str">
-        <v>Olivia Dean</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:34</v>
+        <v>3:25</v>
       </c>
       <c r="H88" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:25</v>
+        <v>3:34</v>
       </c>
       <c r="H89" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:26</v>
+        <v>2:25</v>
       </c>
       <c r="H90" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:46</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Keith Urban</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3874,7 +3874,7 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:24</v>
+        <v>4:46</v>
       </c>
       <c r="H92" t="str">
         <v>Keith Urban</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H93" t="str">
-        <v>Madonna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:06</v>
+        <v>2:52</v>
       </c>
       <c r="H94" t="str">
-        <v>Estás Tonné</v>
+        <v>Madonna</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-29</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:09</v>
+        <v>2:06</v>
       </c>
       <c r="H95" t="str">
-        <v>Anna Graves</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-29</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:11</v>
+        <v>3:09</v>
       </c>
       <c r="H96" t="str">
-        <v>Ocean Alley</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-29</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:40</v>
+        <v>5:11</v>
       </c>
       <c r="H97" t="str">
-        <v>Zara Larsson</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-29</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:49</v>
+        <v>3:40</v>
       </c>
       <c r="H98" t="str">
-        <v>Lauren Watkins</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-29</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:42</v>
+        <v>3:49</v>
       </c>
       <c r="H99" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-29</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:11</v>
+        <v>3:42</v>
       </c>
       <c r="H100" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-29</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:57</v>
+        <v>5:11</v>
       </c>
       <c r="H101" t="str">
-        <v>Lainey Wilson</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>For Hire</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>For Hire - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:44</v>
+        <v>3:57</v>
       </c>
       <c r="H102" t="str">
-        <v>People I’ve Met</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Aperture</v>
+        <v>For Hire</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>5:11</v>
+        <v>3:44</v>
       </c>
       <c r="H103" t="str">
-        <v>Harry Styles</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L103" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Opening Night</v>
+        <v>Aperture</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>HELP(2)</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G104" t="str">
-        <v>4:19</v>
+        <v>5:11</v>
       </c>
       <c r="H104" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L104" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>Opening Night</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Don't Be Dumb</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G105" t="str">
-        <v>2:20</v>
+        <v>4:19</v>
       </c>
       <c r="H105" t="str">
-        <v>A$AP Rocky</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>CAMBIARÉ</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G106" t="str">
-        <v>3:01</v>
+        <v>2:20</v>
       </c>
       <c r="H106" t="str">
-        <v>Luis Fonsi</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L106" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Piss In The Wind</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:29</v>
+        <v>3:01</v>
       </c>
       <c r="H107" t="str">
-        <v>Joji</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L107" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>High Key</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Vacancy</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G108" t="str">
-        <v>2:12</v>
+        <v>2:29</v>
       </c>
       <c r="H108" t="str">
-        <v>Ari Lennox</v>
+        <v>Joji</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L108" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>scared</v>
+        <v>High Key</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>scared - Single</v>
+        <v>Vacancy</v>
       </c>
       <c r="G109" t="str">
-        <v>3:46</v>
+        <v>2:12</v>
       </c>
       <c r="H109" t="str">
-        <v>Fred again..</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L109" t="str">
-        <v>scared - Fred again..</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Death of Love</v>
+        <v>scared</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Trying Times</v>
+        <v>scared - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H110" t="str">
-        <v>James Blake</v>
+        <v>Fred again..</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L110" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Death of Love</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G111" t="str">
-        <v>4:03</v>
+        <v>3:26</v>
       </c>
       <c r="H111" t="str">
-        <v>Parker McCollum</v>
+        <v>James Blake</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L111" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ATM</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>OCTANE</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G112" t="str">
-        <v>3:00</v>
+        <v>4:03</v>
       </c>
       <c r="H112" t="str">
-        <v>Don Toliver</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L112" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Flo Jackson</v>
+        <v>ATM</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>OCTANE</v>
       </c>
       <c r="G113" t="str">
-        <v>2:23</v>
+        <v>3:00</v>
       </c>
       <c r="H113" t="str">
-        <v>Flo Milli</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L113" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Creature of Habit</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:46</v>
+        <v>2:23</v>
       </c>
       <c r="H114" t="str">
-        <v>Courtney Barnett</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L114" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Puppet Parade</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Megadeth</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G115" t="str">
-        <v>4:40</v>
+        <v>2:46</v>
       </c>
       <c r="H115" t="str">
-        <v>Megadeth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L115" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>To Love Somebody</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Cruel World</v>
+        <v>Megadeth</v>
       </c>
       <c r="G116" t="str">
-        <v>3:57</v>
+        <v>4:40</v>
       </c>
       <c r="H116" t="str">
-        <v>Holly Humberstone</v>
+        <v>Megadeth</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L116" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G117" t="str">
-        <v>4:14</v>
+        <v>3:57</v>
       </c>
       <c r="H117" t="str">
-        <v>Cleo Sol</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L117" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>THE CORE - 核</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:50</v>
+        <v>4:14</v>
       </c>
       <c r="H118" t="str">
-        <v>XG</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L118" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Dead End</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Ricochet</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G119" t="str">
-        <v>4:05</v>
+        <v>2:50</v>
       </c>
       <c r="H119" t="str">
-        <v>Snail Mail</v>
+        <v>XG</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L119" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Dead End</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G120" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H120" t="str">
-        <v>Dove Cameron</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L120" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:02</v>
+        <v>3:52</v>
       </c>
       <c r="H121" t="str">
-        <v>Kenia Os</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L121" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>BAD</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BAD - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G122" t="str">
-        <v>2:15</v>
+        <v>3:02</v>
       </c>
       <c r="H122" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L122" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Losing You</v>
+        <v>BAD</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>F.I.G</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:22</v>
+        <v>2:15</v>
       </c>
       <c r="H123" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L123" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>Losing You</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G124" t="str">
-        <v>3:02</v>
+        <v>2:22</v>
       </c>
       <c r="H124" t="str">
-        <v>The Runarounds</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L124" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Infinito</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Yandel</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L125" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Sexy For Me</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Infinito</v>
       </c>
       <c r="G126" t="str">
-        <v>2:08</v>
+        <v>2:14</v>
       </c>
       <c r="H126" t="str">
-        <v>Jason Derulo</v>
+        <v>Yandel</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L126" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Turbulence</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G127" t="str">
-        <v>2:25</v>
+        <v>2:08</v>
       </c>
       <c r="H127" t="str">
-        <v>Wizkid</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L127" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Turbulence</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>2:25</v>
       </c>
       <c r="H128" t="str">
-        <v>Jelly Roll</v>
+        <v>Wizkid</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L128" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:47</v>
+        <v>2:59</v>
       </c>
       <c r="H129" t="str">
-        <v>Dolly Parton</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L129" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:53</v>
+        <v>3:47</v>
       </c>
       <c r="H130" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L130" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Act I</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G131" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H131" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L131" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Imposter</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Act I</v>
       </c>
       <c r="G132" t="str">
-        <v>2:38</v>
+        <v>3:43</v>
       </c>
       <c r="H132" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L132" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Imposter</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G133" t="str">
-        <v>6:01</v>
+        <v>2:38</v>
       </c>
       <c r="H133" t="str">
-        <v>Not for Radio</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L133" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:24</v>
+        <v>6:01</v>
       </c>
       <c r="H134" t="str">
-        <v>GIRLSET</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L134" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:41</v>
+        <v>2:24</v>
       </c>
       <c r="H135" t="str">
-        <v>Jessie Ware</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L135" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>LA VILLA</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H136" t="str">
-        <v>Ryan Castro</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L136" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G137" t="str">
-        <v>3:27</v>
+        <v>3:12</v>
       </c>
       <c r="H137" t="str">
-        <v>Denzel Curry</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L137" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Thick One</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Part 3</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G138" t="str">
-        <v>2:49</v>
+        <v>3:27</v>
       </c>
       <c r="H138" t="str">
-        <v>42 Dugg</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L138" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Thick One</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Part 3</v>
       </c>
       <c r="G139" t="str">
-        <v>3:59</v>
+        <v>2:49</v>
       </c>
       <c r="H139" t="str">
-        <v>Lucinda Williams</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L139" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>THUM</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>THUM - Single</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G140" t="str">
-        <v>2:11</v>
+        <v>3:59</v>
       </c>
       <c r="H140" t="str">
-        <v>Violet Grohl</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L140" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>THUM</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>The Great Satan</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:32</v>
+        <v>2:11</v>
       </c>
       <c r="H141" t="str">
-        <v>Rob Zombie</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L141" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Excuses For Love</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Hyperlove</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G142" t="str">
-        <v>3:04</v>
+        <v>3:32</v>
       </c>
       <c r="H142" t="str">
-        <v>MIKA</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L142" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>3 Tears</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>3 Tears - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G143" t="str">
-        <v>2:50</v>
+        <v>3:04</v>
       </c>
       <c r="H143" t="str">
-        <v>Mergui</v>
+        <v>MIKA</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L143" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Church Girl</v>
+        <v>3 Tears</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Church Girl - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>Carly Pearce</v>
+        <v>Mergui</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L144" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Funeral</v>
+        <v>Church Girl</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>4:03</v>
+        <v>3:19</v>
       </c>
       <c r="H145" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L145" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>dust to dust</v>
+        <v>Funeral</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G146" t="str">
-        <v>3:51</v>
+        <v>4:03</v>
       </c>
       <c r="H146" t="str">
-        <v>Truman Sinclair</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L146" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Say Yes</v>
+        <v>dust to dust</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Say Yes - Single</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H147" t="str">
-        <v>Marques Anthony</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L147" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Say Yes</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>CAMPILATION</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H148" t="str">
-        <v>Camper</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L148" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Ojalá</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ojalá - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G149" t="str">
-        <v>4:11</v>
+        <v>3:10</v>
       </c>
       <c r="H149" t="str">
-        <v>Lunay</v>
+        <v>Camper</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L149" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Ojalá</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:17</v>
+        <v>4:11</v>
       </c>
       <c r="H150" t="str">
-        <v>Ledbyher</v>
+        <v>Lunay</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L150" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H151" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L151" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H152" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L152" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H153" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L153" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H154" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L154" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G155" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H155" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L155" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H156" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L156" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G157" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H157" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L157" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H158" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L158" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G159" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H159" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L159" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H160" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L160" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H161" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L161" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H162" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L162" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H163" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L163" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H164" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L164" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H165" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L165" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G166" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H166" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L166" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G167" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H167" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L167" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H168" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L168" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H169" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L169" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H170" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L170" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H171" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L171" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Odisea</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Odisea - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:56</v>
+        <v>2:58</v>
       </c>
       <c r="H172" t="str">
-        <v>BASSYY</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L172" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Lucky Day</v>
+        <v>Odisea</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Speed Kills</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:13</v>
+        <v>3:56</v>
       </c>
       <c r="H173" t="str">
-        <v>Ally Evenson</v>
+        <v>BASSYY</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L173" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Breathe On It</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G174" t="str">
-        <v>4:00</v>
+        <v>3:13</v>
       </c>
       <c r="H174" t="str">
-        <v>Tauren Wells</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L174" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Easy</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Easy - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:30</v>
+        <v>4:00</v>
       </c>
       <c r="H175" t="str">
-        <v>lydi lynn</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L175" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Break Me In</v>
+        <v>Easy</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Break Me In - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:52</v>
+        <v>4:30</v>
       </c>
       <c r="H176" t="str">
-        <v>Joyce Wrice</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L176" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Long Live Love</v>
+        <v>Break Me In</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H177" t="str">
-        <v>Sugar</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L177" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Depressed</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Boycott Heaven</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H178" t="str">
-        <v>The Format</v>
+        <v>Sugar</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L178" t="str">
-        <v>Depressed - The Format</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Empty Hands</v>
+        <v>Depressed</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Empty Hands</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G179" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H179" t="str">
-        <v>Poppy</v>
+        <v>The Format</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L179" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G180" t="str">
-        <v>3:45</v>
+        <v>3:09</v>
       </c>
       <c r="H180" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Poppy</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L180" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Angela</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Angela - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G181" t="str">
-        <v>3:32</v>
+        <v>3:45</v>
       </c>
       <c r="H181" t="str">
-        <v>Hayden Everett</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L181" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Disappear</v>
+        <v>Angela</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Greyhound</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:31</v>
+        <v>3:32</v>
       </c>
       <c r="H182" t="str">
-        <v>Katie Tupper</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L182" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Catapult</v>
+        <v>Disappear</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Catapult - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G183" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H183" t="str">
-        <v>Cape Francis</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L183" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Think Twice</v>
+        <v>Catapult</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Think Twice - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:22</v>
+        <v>2:57</v>
       </c>
       <c r="H184" t="str">
-        <v>Leonie Biney</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L184" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>LOVESONGS</v>
+        <v>Think Twice</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:33</v>
+        <v>2:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Agnes</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L185" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Down South</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Down South - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G186" t="str">
-        <v>2:19</v>
+        <v>3:33</v>
       </c>
       <c r="H186" t="str">
-        <v>Trap Dickey</v>
+        <v>Agnes</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L186" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Down South</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H187" t="str">
-        <v>SALIMATA</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L187" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Love Like This</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Love Like This - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:30</v>
+        <v>2:16</v>
       </c>
       <c r="H188" t="str">
-        <v>Jacob Banks</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L188" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Plan Plan</v>
+        <v>Love Like This</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H189" t="str">
-        <v>Funky</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L189" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>double edged sword</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D190" t="str">
         <v>2026-01-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>double edged sword - Single</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G190" t="str">
-        <v>3:28</v>
+        <v>3:10</v>
       </c>
       <c r="H190" t="str">
-        <v>Hailey Picardi</v>
+        <v>Funky</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L190" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D191" t="str">
         <v>2026-01-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:27</v>
+        <v>3:28</v>
       </c>
       <c r="H191" t="str">
-        <v>Matt Hansen</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L191" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Decay</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D192" t="str">
         <v>2026-01-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H192" t="str">
-        <v>Pop Evil</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L192" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>3111</v>
+        <v>The Decay</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D193" t="str">
         <v>2026-01-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Goliath</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G193" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H193" t="str">
-        <v>Exodus</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L193" t="str">
-        <v>3111 - Exodus</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Touch My Love And Die</v>
+        <v>3111</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D194" t="str">
         <v>2026-01-29</v>
@@ -7747,68 +7747,106 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G194" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H194" t="str">
-        <v>Myrkur</v>
+        <v>Exodus</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L194" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G195" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H195" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K195" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L195" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D195" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
+      <c r="D196" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G195" t="str">
+      <c r="G196" t="str">
         <v>2:41</v>
       </c>
-      <c r="H195" t="str">
+      <c r="H196" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K195" t="str">
+      <c r="K196" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L195" t="str">
+      <c r="L196" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי בירמן – אין אהבה ללא כאב</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-29</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%91%d7%99%d7%a8%d7%9e%d7%9f-%d7%90%d7%99%d7%9f-%d7%90%d7%94%d7%91%d7%94-%d7%9c%d7%9c%d7%90-%d7%9b%d7%90%d7%91/</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "אין אהבה ללא כאב" של איתי בקרמן הוא יצירה אישית, חשופה ובוגרת, שמצליחה להפוך סיפור משפחתי מורכב לבלדה רוקית מידטמפו בעלת עוצמה רגשית. זהו שיר שמתבונן באהבה לא כאגדה רומנטית, אלא כתהליך אנושי עמוק, רצוף סדקים, בחירות קשות ויכולת</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>2:57</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>The Offspring</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי בירמן – אין אהבה ללא כאב</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:57</v>
+        <v>4:10</v>
       </c>
       <c r="H3" t="str">
-        <v>The Offspring</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:10</v>
+        <v>2:10</v>
       </c>
       <c r="H4" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:10</v>
+        <v>3:52</v>
       </c>
       <c r="H5" t="str">
-        <v>Jason Derulo</v>
+        <v>lights</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:52</v>
+        <v>3:50</v>
       </c>
       <c r="H6" t="str">
-        <v>lights</v>
+        <v>Telenova</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B7" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:50</v>
+        <v>5:32</v>
       </c>
       <c r="H7" t="str">
-        <v>Telenova</v>
+        <v>Marcin</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>5:32</v>
+        <v>4:27</v>
       </c>
       <c r="H8" t="str">
-        <v>Marcin</v>
+        <v>We Three</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:27</v>
+        <v>3:01</v>
       </c>
       <c r="H9" t="str">
-        <v>We Three</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:01</v>
+        <v>3:20</v>
       </c>
       <c r="H10" t="str">
-        <v>Timebelle Official</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:20</v>
+        <v>3:34</v>
       </c>
       <c r="H11" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -834,10 +834,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:34</v>
+        <v>4:01</v>
       </c>
       <c r="H12" t="str">
-        <v>Clinton Kane</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B13" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -872,10 +872,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:01</v>
+        <v>3:24</v>
       </c>
       <c r="H13" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -910,10 +910,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:24</v>
+        <v>5:52</v>
       </c>
       <c r="H14" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -948,10 +948,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>5:52</v>
+        <v>5:01</v>
       </c>
       <c r="H15" t="str">
-        <v>Harry Styles</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -986,10 +986,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>5:01</v>
+        <v>4:12</v>
       </c>
       <c r="H16" t="str">
-        <v>Neal Francis</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:12</v>
+        <v>3:59</v>
       </c>
       <c r="H17" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:59</v>
+        <v>2:56</v>
       </c>
       <c r="H18" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1100,10 +1100,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H19" t="str">
-        <v>Cliff Richard</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1138,10 +1138,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:46</v>
+        <v>4:37</v>
       </c>
       <c r="H20" t="str">
-        <v>Jessie Ware</v>
+        <v>Bella White</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1176,10 +1176,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:37</v>
+        <v>4:06</v>
       </c>
       <c r="H21" t="str">
-        <v>Bella White</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1214,10 +1214,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:06</v>
+        <v>3:54</v>
       </c>
       <c r="H22" t="str">
-        <v>Ryan Wright</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1252,10 +1252,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:54</v>
+        <v>4:10</v>
       </c>
       <c r="H23" t="str">
-        <v>Dove Cameron</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1290,10 +1290,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:10</v>
+        <v>3:26</v>
       </c>
       <c r="H24" t="str">
-        <v>Parker McCollum</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H25" t="str">
-        <v>Matt Hansen</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:56</v>
       </c>
       <c r="H26" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1404,10 +1404,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H27" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1442,10 +1442,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H28" t="str">
-        <v>Tauren Wells</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1480,10 +1480,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:05</v>
+        <v>2:27</v>
       </c>
       <c r="H29" t="str">
-        <v>Maiah Manser</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1518,10 +1518,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H30" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H31" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1597,7 +1597,7 @@
         <v>3:13</v>
       </c>
       <c r="H32" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H33" t="str">
-        <v>Louis Tomlinson</v>
+        <v>CAIN</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:08</v>
+        <v>5:14</v>
       </c>
       <c r="H34" t="str">
-        <v>CAIN</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>5:14</v>
+        <v>2:59</v>
       </c>
       <c r="H35" t="str">
-        <v>Harry Styles</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:59</v>
+        <v>4:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Lana Lubany</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:21</v>
+        <v>4:09</v>
       </c>
       <c r="H37" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B39" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1860,10 +1860,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:34</v>
+        <v>3:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B40" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1898,10 +1898,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H40" t="str">
-        <v>Olivia Dean</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H41" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H42" t="str">
-        <v>The Avett Brothers</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:21</v>
+        <v>7:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Jordana Bryant</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>7:21</v>
+        <v>3:17</v>
       </c>
       <c r="H44" t="str">
-        <v>Katy Perry</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:17</v>
+        <v>3:45</v>
       </c>
       <c r="H45" t="str">
-        <v>Lauren Watkins</v>
+        <v>Tones And I</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:45</v>
+        <v>3:57</v>
       </c>
       <c r="H46" t="str">
-        <v>Tones And I</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:57</v>
+        <v>3:03</v>
       </c>
       <c r="H47" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B48" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2202,10 +2202,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:03</v>
+        <v>4:27</v>
       </c>
       <c r="H48" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B49" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2240,10 +2240,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:27</v>
+        <v>4:34</v>
       </c>
       <c r="H49" t="str">
-        <v>Chappell Roan</v>
+        <v>Armik</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2278,10 +2278,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:34</v>
+        <v>2:54</v>
       </c>
       <c r="H50" t="str">
-        <v>Armik</v>
+        <v>LØLØ</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2316,10 +2316,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:54</v>
+        <v>3:25</v>
       </c>
       <c r="H51" t="str">
-        <v>LØLØ</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:25</v>
+        <v>2:01</v>
       </c>
       <c r="H52" t="str">
-        <v>Tenille Townes</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:01</v>
+        <v>2:25</v>
       </c>
       <c r="H53" t="str">
-        <v>Alan Walker</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2430,10 +2430,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:25</v>
+        <v>1:14</v>
       </c>
       <c r="H54" t="str">
-        <v>Charli xcx</v>
+        <v>Labrinth</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>1:14</v>
+        <v>2:59</v>
       </c>
       <c r="H55" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2506,10 +2506,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:59</v>
+        <v>2:29</v>
       </c>
       <c r="H56" t="str">
-        <v>Charlie Puth</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2544,10 +2544,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:29</v>
+        <v>2:34</v>
       </c>
       <c r="H57" t="str">
-        <v>Girl Tones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2582,10 +2582,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:34</v>
+        <v>3:48</v>
       </c>
       <c r="H58" t="str">
-        <v>Jagwar Twin</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B59" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2620,10 +2620,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:48</v>
+        <v>3:32</v>
       </c>
       <c r="H59" t="str">
-        <v>Caroline Jones</v>
+        <v>The Beaches</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B60" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2658,10 +2658,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:32</v>
+        <v>3:49</v>
       </c>
       <c r="H60" t="str">
-        <v>The Beaches</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2696,10 +2696,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:49</v>
+        <v>4:28</v>
       </c>
       <c r="H61" t="str">
-        <v>Dolly Parton</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:28</v>
+        <v>3:37</v>
       </c>
       <c r="H62" t="str">
-        <v>Madison Beer</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:37</v>
+        <v>3:35</v>
       </c>
       <c r="H63" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:35</v>
+        <v>2:31</v>
       </c>
       <c r="H64" t="str">
-        <v>Megan Moroney</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:31</v>
+        <v>3:21</v>
       </c>
       <c r="H65" t="str">
-        <v>Julia Cole Music</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:21</v>
+        <v>5:24</v>
       </c>
       <c r="H66" t="str">
-        <v>Lily Allen</v>
+        <v>Nickless</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>5:24</v>
+        <v>3:11</v>
       </c>
       <c r="H67" t="str">
-        <v>Nickless</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:11</v>
+        <v>4:11</v>
       </c>
       <c r="H68" t="str">
-        <v>Peach PRC</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:11</v>
+        <v>3:31</v>
       </c>
       <c r="H69" t="str">
-        <v>Ocean Alley</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:31</v>
+        <v>4:16</v>
       </c>
       <c r="H70" t="str">
-        <v>OneRepublic</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:16</v>
+        <v>4:42</v>
       </c>
       <c r="H71" t="str">
-        <v>Ty Myers</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:42</v>
+        <v>2:47</v>
       </c>
       <c r="H72" t="str">
-        <v>JavaJazzFest</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:47</v>
+        <v>3:59</v>
       </c>
       <c r="H73" t="str">
-        <v>Teo Glacier</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:59</v>
+        <v>4:09</v>
       </c>
       <c r="H74" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:09</v>
+        <v>3:24</v>
       </c>
       <c r="H75" t="str">
-        <v>Louie TheSinger</v>
+        <v>ella jane</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:24</v>
+        <v>3:14</v>
       </c>
       <c r="H76" t="str">
-        <v>ella jane</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:14</v>
+        <v>3:32</v>
       </c>
       <c r="H77" t="str">
-        <v>Johnny Orlando</v>
+        <v>Kungs</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:32</v>
+        <v>3:15</v>
       </c>
       <c r="H78" t="str">
-        <v>Kungs</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:15</v>
+        <v>3:03</v>
       </c>
       <c r="H79" t="str">
-        <v>Billy Raffoul</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H80" t="str">
-        <v>NathanEvanss</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:04</v>
+        <v>3:33</v>
       </c>
       <c r="H81" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:33</v>
+        <v>2:53</v>
       </c>
       <c r="H82" t="str">
-        <v>Bruno Mars</v>
+        <v>MAX</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:53</v>
+        <v>4:11</v>
       </c>
       <c r="H83" t="str">
-        <v>MAX</v>
+        <v>Jessie J</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:11</v>
+        <v>2:45</v>
       </c>
       <c r="H84" t="str">
-        <v>Jessie J</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:45</v>
+        <v>4:00</v>
       </c>
       <c r="H85" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:00</v>
+        <v>3:27</v>
       </c>
       <c r="H86" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:27</v>
+        <v>3:25</v>
       </c>
       <c r="H87" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:25</v>
+        <v>3:34</v>
       </c>
       <c r="H88" t="str">
-        <v>Olivia Dean</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3760,10 +3760,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:34</v>
+        <v>2:25</v>
       </c>
       <c r="H89" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:25</v>
+        <v>3:26</v>
       </c>
       <c r="H90" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H91" t="str">
-        <v>Demi Lovato</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3874,7 +3874,7 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:46</v>
+        <v>3:24</v>
       </c>
       <c r="H92" t="str">
         <v>Keith Urban</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:24</v>
+        <v>2:52</v>
       </c>
       <c r="H93" t="str">
-        <v>Keith Urban</v>
+        <v>Madonna</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:52</v>
+        <v>2:06</v>
       </c>
       <c r="H94" t="str">
-        <v>Madonna</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-29</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:06</v>
+        <v>3:09</v>
       </c>
       <c r="H95" t="str">
-        <v>Estás Tonné</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-29</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:09</v>
+        <v>5:11</v>
       </c>
       <c r="H96" t="str">
-        <v>Anna Graves</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-29</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>5:11</v>
+        <v>3:40</v>
       </c>
       <c r="H97" t="str">
-        <v>Ocean Alley</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-29</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:40</v>
+        <v>3:49</v>
       </c>
       <c r="H98" t="str">
-        <v>Zara Larsson</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-29</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:49</v>
+        <v>3:42</v>
       </c>
       <c r="H99" t="str">
-        <v>Lauren Watkins</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-29</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:42</v>
+        <v>5:11</v>
       </c>
       <c r="H100" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-29</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:11</v>
+        <v>3:57</v>
       </c>
       <c r="H101" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>For Hire</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:57</v>
+        <v>3:44</v>
       </c>
       <c r="H102" t="str">
-        <v>Lainey Wilson</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L102" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>For Hire</v>
+        <v>Aperture</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>For Hire - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G103" t="str">
-        <v>3:44</v>
+        <v>5:11</v>
       </c>
       <c r="H103" t="str">
-        <v>People I’ve Met</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L103" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Aperture</v>
+        <v>Opening Night</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G104" t="str">
-        <v>5:11</v>
+        <v>4:19</v>
       </c>
       <c r="H104" t="str">
-        <v>Harry Styles</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L104" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Opening Night</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>HELP(2)</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G105" t="str">
-        <v>4:19</v>
+        <v>2:20</v>
       </c>
       <c r="H105" t="str">
-        <v>Arctic Monkeys</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L105" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Don't Be Dumb</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>2:20</v>
+        <v>3:01</v>
       </c>
       <c r="H106" t="str">
-        <v>A$AP Rocky</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L106" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G107" t="str">
-        <v>3:01</v>
+        <v>2:29</v>
       </c>
       <c r="H107" t="str">
-        <v>Luis Fonsi</v>
+        <v>Joji</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L107" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>High Key</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Piss In The Wind</v>
+        <v>Vacancy</v>
       </c>
       <c r="G108" t="str">
-        <v>2:29</v>
+        <v>2:12</v>
       </c>
       <c r="H108" t="str">
-        <v>Joji</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L108" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>High Key</v>
+        <v>scared</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Vacancy</v>
+        <v>scared - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:12</v>
+        <v>3:46</v>
       </c>
       <c r="H109" t="str">
-        <v>Ari Lennox</v>
+        <v>Fred again..</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L109" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>scared</v>
+        <v>Death of Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>scared - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G110" t="str">
-        <v>3:46</v>
+        <v>3:26</v>
       </c>
       <c r="H110" t="str">
-        <v>Fred again..</v>
+        <v>James Blake</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L110" t="str">
-        <v>scared - Fred again..</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Death of Love</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Trying Times</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G111" t="str">
-        <v>3:26</v>
+        <v>4:03</v>
       </c>
       <c r="H111" t="str">
-        <v>James Blake</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L111" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>ATM</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>OCTANE</v>
       </c>
       <c r="G112" t="str">
-        <v>4:03</v>
+        <v>3:00</v>
       </c>
       <c r="H112" t="str">
-        <v>Parker McCollum</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L112" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ATM</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>OCTANE</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:00</v>
+        <v>2:23</v>
       </c>
       <c r="H113" t="str">
-        <v>Don Toliver</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L113" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Flo Jackson</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G114" t="str">
-        <v>2:23</v>
+        <v>2:46</v>
       </c>
       <c r="H114" t="str">
-        <v>Flo Milli</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L114" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Creature of Habit</v>
+        <v>Megadeth</v>
       </c>
       <c r="G115" t="str">
-        <v>2:46</v>
+        <v>4:40</v>
       </c>
       <c r="H115" t="str">
-        <v>Courtney Barnett</v>
+        <v>Megadeth</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L115" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Puppet Parade</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Megadeth</v>
+        <v>Cruel World</v>
       </c>
       <c r="G116" t="str">
-        <v>4:40</v>
+        <v>3:57</v>
       </c>
       <c r="H116" t="str">
-        <v>Megadeth</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L116" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>To Love Somebody</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Cruel World</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:57</v>
+        <v>4:14</v>
       </c>
       <c r="H117" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L117" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G118" t="str">
-        <v>4:14</v>
+        <v>2:50</v>
       </c>
       <c r="H118" t="str">
-        <v>Cleo Sol</v>
+        <v>XG</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L118" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Dead End</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>THE CORE - 核</v>
+        <v>Ricochet</v>
       </c>
       <c r="G119" t="str">
-        <v>2:50</v>
+        <v>4:05</v>
       </c>
       <c r="H119" t="str">
-        <v>XG</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L119" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Dead End</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Ricochet</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>4:05</v>
+        <v>3:52</v>
       </c>
       <c r="H120" t="str">
-        <v>Snail Mail</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L120" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G121" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H121" t="str">
-        <v>Dove Cameron</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L121" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Una y Otra Vez</v>
+        <v>BAD</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:02</v>
+        <v>2:15</v>
       </c>
       <c r="H122" t="str">
-        <v>Kenia Os</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L122" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>BAD</v>
+        <v>Losing You</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>BAD - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G123" t="str">
-        <v>2:15</v>
+        <v>2:22</v>
       </c>
       <c r="H123" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L123" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Losing You</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>F.I.G</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:22</v>
+        <v>3:02</v>
       </c>
       <c r="H124" t="str">
-        <v>Naomi Scott</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L124" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>Infinito</v>
       </c>
       <c r="G125" t="str">
-        <v>3:02</v>
+        <v>2:14</v>
       </c>
       <c r="H125" t="str">
-        <v>The Runarounds</v>
+        <v>Yandel</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L125" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Infinito</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G126" t="str">
-        <v>2:14</v>
+        <v>2:08</v>
       </c>
       <c r="H126" t="str">
-        <v>Yandel</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L126" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Sexy For Me</v>
+        <v>Turbulence</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G127" t="str">
-        <v>2:08</v>
+        <v>2:25</v>
       </c>
       <c r="H127" t="str">
-        <v>Jason Derulo</v>
+        <v>Wizkid</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L127" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turbulence</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G128" t="str">
-        <v>2:25</v>
+        <v>2:59</v>
       </c>
       <c r="H128" t="str">
-        <v>Wizkid</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L128" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:59</v>
+        <v>3:47</v>
       </c>
       <c r="H129" t="str">
-        <v>Jelly Roll</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L129" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G130" t="str">
-        <v>3:47</v>
+        <v>2:53</v>
       </c>
       <c r="H130" t="str">
-        <v>Dolly Parton</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L130" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Act I</v>
       </c>
       <c r="G131" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H131" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L131" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>Imposter</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Act I</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G132" t="str">
-        <v>3:43</v>
+        <v>2:38</v>
       </c>
       <c r="H132" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L132" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Imposter</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:38</v>
+        <v>6:01</v>
       </c>
       <c r="H133" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L133" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>6:01</v>
+        <v>2:24</v>
       </c>
       <c r="H134" t="str">
-        <v>Not for Radio</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L134" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:24</v>
+        <v>3:41</v>
       </c>
       <c r="H135" t="str">
-        <v>GIRLSET</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L135" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>I Could Get Used To This</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G136" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H136" t="str">
-        <v>Jessie Ware</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L136" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>LA VILLA</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G137" t="str">
-        <v>3:12</v>
+        <v>3:27</v>
       </c>
       <c r="H137" t="str">
-        <v>Ryan Castro</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L137" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>Thick One</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Part 3</v>
       </c>
       <c r="G138" t="str">
-        <v>3:27</v>
+        <v>2:49</v>
       </c>
       <c r="H138" t="str">
-        <v>Denzel Curry</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L138" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Thick One</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Part 3</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G139" t="str">
-        <v>2:49</v>
+        <v>3:59</v>
       </c>
       <c r="H139" t="str">
-        <v>42 Dugg</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L139" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>THUM</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>World's Gone Wrong</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:59</v>
+        <v>2:11</v>
       </c>
       <c r="H140" t="str">
-        <v>Lucinda Williams</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L140" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>THUM</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>THUM - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G141" t="str">
-        <v>2:11</v>
+        <v>3:32</v>
       </c>
       <c r="H141" t="str">
-        <v>Violet Grohl</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L141" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Great Satan</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G142" t="str">
-        <v>3:32</v>
+        <v>3:04</v>
       </c>
       <c r="H142" t="str">
-        <v>Rob Zombie</v>
+        <v>MIKA</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L142" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Excuses For Love</v>
+        <v>3 Tears</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Hyperlove</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:04</v>
+        <v>2:50</v>
       </c>
       <c r="H143" t="str">
-        <v>MIKA</v>
+        <v>Mergui</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L143" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>3 Tears</v>
+        <v>Church Girl</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>3 Tears - Single</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>3:19</v>
       </c>
       <c r="H144" t="str">
-        <v>Mergui</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L144" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Church Girl</v>
+        <v>Funeral</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Church Girl - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G145" t="str">
-        <v>3:19</v>
+        <v>4:03</v>
       </c>
       <c r="H145" t="str">
-        <v>Carly Pearce</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L145" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Funeral</v>
+        <v>dust to dust</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G146" t="str">
-        <v>4:03</v>
+        <v>3:51</v>
       </c>
       <c r="H146" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L146" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>dust to dust</v>
+        <v>Say Yes</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:51</v>
+        <v>2:50</v>
       </c>
       <c r="H147" t="str">
-        <v>Truman Sinclair</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L147" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Say Yes</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Say Yes - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G148" t="str">
-        <v>2:50</v>
+        <v>3:10</v>
       </c>
       <c r="H148" t="str">
-        <v>Marques Anthony</v>
+        <v>Camper</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L148" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Ojalá</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>CAMPILATION</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:10</v>
+        <v>4:11</v>
       </c>
       <c r="H149" t="str">
-        <v>Camper</v>
+        <v>Lunay</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L149" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Ojalá</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ojalá - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:11</v>
+        <v>2:17</v>
       </c>
       <c r="H150" t="str">
-        <v>Lunay</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L150" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Wallflower</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:17</v>
+        <v>3:25</v>
       </c>
       <c r="H151" t="str">
-        <v>Ledbyher</v>
+        <v>Sikarus</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L151" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Wallflower</v>
+        <v>You Phase</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Wallflower - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:25</v>
+        <v>2:51</v>
       </c>
       <c r="H152" t="str">
-        <v>Sikarus</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L152" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>You Phase</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>You Phase - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:51</v>
+        <v>2:40</v>
       </c>
       <c r="H153" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L153" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Miss Independent</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Miss Independent - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G154" t="str">
-        <v>2:40</v>
+        <v>5:47</v>
       </c>
       <c r="H154" t="str">
-        <v>1Ski OG</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L154" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>go again</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>go again - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>5:47</v>
+        <v>2:07</v>
       </c>
       <c r="H155" t="str">
-        <v>Elevation Worship</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L155" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>go again</v>
+        <v>Autopilot</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>go again - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G156" t="str">
-        <v>2:07</v>
+        <v>2:46</v>
       </c>
       <c r="H156" t="str">
-        <v>NateTaylorr</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L156" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Autopilot</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Autopilot</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:46</v>
+        <v>3:04</v>
       </c>
       <c r="H157" t="str">
-        <v>ALEXSUCKS</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L157" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>In Violet</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G158" t="str">
-        <v>3:04</v>
+        <v>4:09</v>
       </c>
       <c r="H158" t="str">
-        <v>SPELLLING</v>
+        <v>Searows</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L158" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>In Violet</v>
+        <v>Baby Run</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:09</v>
+        <v>4:47</v>
       </c>
       <c r="H159" t="str">
-        <v>Searows</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L159" t="str">
-        <v>In Violet - Searows</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Baby Run</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Baby Run - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>4:47</v>
+        <v>3:06</v>
       </c>
       <c r="H160" t="str">
-        <v>Jimi Jules</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L160" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>What If We Don't</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:06</v>
+        <v>2:58</v>
       </c>
       <c r="H161" t="str">
-        <v>Ashley McBryde</v>
+        <v>Juanes</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L161" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Hagamos Que</v>
+        <v>World Change Me</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:58</v>
+        <v>3:03</v>
       </c>
       <c r="H162" t="str">
-        <v>Juanes</v>
+        <v>Max McNown</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L162" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>World Change Me</v>
+        <v>Exclusive</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>World Change Me - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>3:03</v>
+        <v>3:20</v>
       </c>
       <c r="H163" t="str">
-        <v>Max McNown</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L163" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Exclusive</v>
+        <v>Say Less</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Exclusive - EP</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:20</v>
+        <v>2:18</v>
       </c>
       <c r="H164" t="str">
-        <v>Hudson Westbrook</v>
+        <v>JYT</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L164" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Say Less</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Say Less - Single</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G165" t="str">
-        <v>2:18</v>
+        <v>3:52</v>
       </c>
       <c r="H165" t="str">
-        <v>JYT</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L165" t="str">
-        <v>Say Less - JYT</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Angels Cry</v>
+        <v>Over You</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G166" t="str">
-        <v>3:52</v>
+        <v>4:44</v>
       </c>
       <c r="H166" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L166" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Over You</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>A Love For Strangers</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:44</v>
+        <v>2:42</v>
       </c>
       <c r="H167" t="str">
-        <v>Chet Faker</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L167" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:42</v>
+        <v>3:06</v>
       </c>
       <c r="H168" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L168" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H169" t="str">
-        <v>Disco Lines</v>
+        <v>David Guetta</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L169" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Rejoice</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:48</v>
+        <v>4:20</v>
       </c>
       <c r="H170" t="str">
-        <v>David Guetta</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L170" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Rejoice</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Rejoice - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>4:20</v>
+        <v>2:58</v>
       </c>
       <c r="H171" t="str">
-        <v>Def Leppard</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L171" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Odisea</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:58</v>
+        <v>3:56</v>
       </c>
       <c r="H172" t="str">
-        <v>Honey Dijon</v>
+        <v>BASSYY</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L172" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Odisea</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Odisea - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G173" t="str">
-        <v>3:56</v>
+        <v>3:13</v>
       </c>
       <c r="H173" t="str">
-        <v>BASSYY</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L173" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Lucky Day</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Speed Kills</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:13</v>
+        <v>4:00</v>
       </c>
       <c r="H174" t="str">
-        <v>Ally Evenson</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L174" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Breathe On It</v>
+        <v>Easy</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:00</v>
+        <v>4:30</v>
       </c>
       <c r="H175" t="str">
-        <v>Tauren Wells</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L175" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Easy</v>
+        <v>Break Me In</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Easy - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:30</v>
+        <v>2:52</v>
       </c>
       <c r="H176" t="str">
-        <v>lydi lynn</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L176" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Break Me In</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Break Me In - Single</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:52</v>
+        <v>2:36</v>
       </c>
       <c r="H177" t="str">
-        <v>Joyce Wrice</v>
+        <v>Sugar</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L177" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Long Live Love</v>
+        <v>Depressed</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G178" t="str">
-        <v>2:36</v>
+        <v>3:32</v>
       </c>
       <c r="H178" t="str">
-        <v>Sugar</v>
+        <v>The Format</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L178" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Depressed</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Boycott Heaven</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G179" t="str">
-        <v>3:32</v>
+        <v>3:09</v>
       </c>
       <c r="H179" t="str">
-        <v>The Format</v>
+        <v>Poppy</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L179" t="str">
-        <v>Depressed - The Format</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Empty Hands</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Empty Hands</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G180" t="str">
-        <v>3:09</v>
+        <v>3:45</v>
       </c>
       <c r="H180" t="str">
-        <v>Poppy</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L180" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The Long Surrender</v>
+        <v>Angela</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>The Long Surrender</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:45</v>
+        <v>3:32</v>
       </c>
       <c r="H181" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L181" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Angela</v>
+        <v>Disappear</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Angela - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G182" t="str">
-        <v>3:32</v>
+        <v>3:31</v>
       </c>
       <c r="H182" t="str">
-        <v>Hayden Everett</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L182" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Disappear</v>
+        <v>Catapult</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Greyhound</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:31</v>
+        <v>2:57</v>
       </c>
       <c r="H183" t="str">
-        <v>Katie Tupper</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L183" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Catapult</v>
+        <v>Think Twice</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Catapult - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:57</v>
+        <v>2:22</v>
       </c>
       <c r="H184" t="str">
-        <v>Cape Francis</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L184" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Think Twice</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Think Twice - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G185" t="str">
-        <v>2:22</v>
+        <v>3:33</v>
       </c>
       <c r="H185" t="str">
-        <v>Leonie Biney</v>
+        <v>Agnes</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L185" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>LOVESONGS</v>
+        <v>Down South</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:33</v>
+        <v>2:19</v>
       </c>
       <c r="H186" t="str">
-        <v>Agnes</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L186" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Down South</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Down South - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:19</v>
+        <v>2:16</v>
       </c>
       <c r="H187" t="str">
-        <v>Trap Dickey</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L187" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Love Like This</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:16</v>
+        <v>3:30</v>
       </c>
       <c r="H188" t="str">
-        <v>SALIMATA</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L188" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Love Like This</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Love Like This - Single</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G189" t="str">
-        <v>3:30</v>
+        <v>3:10</v>
       </c>
       <c r="H189" t="str">
-        <v>Jacob Banks</v>
+        <v>Funky</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L189" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Plan Plan</v>
+        <v>double edged sword</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D190" t="str">
         <v>2026-01-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:10</v>
+        <v>3:28</v>
       </c>
       <c r="H190" t="str">
-        <v>Funky</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L190" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>double edged sword</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D191" t="str">
         <v>2026-01-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>double edged sword - Single</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:28</v>
+        <v>3:27</v>
       </c>
       <c r="H191" t="str">
-        <v>Hailey Picardi</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L191" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>The Decay</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D192" t="str">
         <v>2026-01-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G192" t="str">
-        <v>3:27</v>
+        <v>3:20</v>
       </c>
       <c r="H192" t="str">
-        <v>Matt Hansen</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L192" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Decay</v>
+        <v>3111</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D193" t="str">
         <v>2026-01-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>Goliath</v>
       </c>
       <c r="G193" t="str">
-        <v>3:20</v>
+        <v>4:08</v>
       </c>
       <c r="H193" t="str">
-        <v>Pop Evil</v>
+        <v>Exodus</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L193" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>3111</v>
+        <v>Touch My Love And Die</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D194" t="str">
         <v>2026-01-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Goliath</v>
+        <v>Touch My Love And Die - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:08</v>
+        <v>2:57</v>
       </c>
       <c r="H194" t="str">
-        <v>Exodus</v>
+        <v>Myrkur</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
       </c>
       <c r="L194" t="str">
-        <v>3111 - Exodus</v>
+        <v>Touch My Love And Die - Myrkur</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Touch My Love And Die</v>
+        <v>Bomb To A Knife Fight</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D195" t="str">
         <v>2026-01-29</v>
@@ -7785,68 +7785,30 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Bomb To A Knife Fight - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H195" t="str">
-        <v>Myrkur</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
       <c r="L195" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Bomb To A Knife Fight</v>
-      </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
-      </c>
-      <c r="D196" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
-        <v>Bomb To A Knife Fight - Single</v>
-      </c>
-      <c r="G196" t="str">
-        <v>2:41</v>
-      </c>
-      <c r="H196" t="str">
-        <v>The Barbarians of California</v>
-      </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
-      </c>
-      <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
-      </c>
-      <c r="L196" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:57</v>
@@ -477,7 +477,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:10</v>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:10</v>
@@ -553,7 +553,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:52</v>
@@ -591,7 +591,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:50</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>I Played "How Music Works" LIVE To 1500 People</v>
       </c>
       <c r="B7" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:32</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
@@ -1731,7 +1731,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>4:21</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:57</v>
@@ -477,7 +477,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:10</v>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:10</v>
@@ -553,7 +553,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:52</v>
@@ -591,7 +591,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:50</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B7" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:32</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="8">
@@ -705,7 +705,7 @@
         <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:01</v>
@@ -968,7 +968,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
@@ -1883,7 +1883,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:21</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:57</v>
@@ -477,7 +477,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:10</v>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:10</v>
@@ -553,7 +553,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:52</v>
@@ -591,7 +591,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:50</v>
@@ -629,7 +629,7 @@
         <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v>5:32</v>
@@ -968,7 +968,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
@@ -1845,7 +1845,7 @@
         <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:10</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:57</v>
@@ -477,7 +477,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:10</v>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:10</v>
@@ -553,7 +553,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:52</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>I Played "How Music Works" LIVE To 1500 People</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
@@ -2301,7 +2301,7 @@
         <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:25</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:57</v>
@@ -477,7 +477,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:10</v>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:10</v>
@@ -553,7 +553,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:52</v>
@@ -968,7 +968,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B16" t="str">
         <v>5 days ago</v>
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
@@ -2263,7 +2263,7 @@
         <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>2:54</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:57</v>
@@ -477,7 +477,7 @@
         <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:10</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>I Played "How Music Works" LIVE To 1500 People - Marcin</v>
+        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="8">
@@ -933,7 +933,7 @@
         <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>5:01</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>4:12</v>
@@ -1001,7 +1001,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="17">
@@ -1693,7 +1693,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:59</v>
@@ -2073,7 +2073,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>3:45</v>
@@ -2871,7 +2871,7 @@
         <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v>5:24</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>יניב רם - כוחה של אמונה</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409407&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>2:57</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>The Offspring</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>יניב רם - כוחה של אמונה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>זואי קפלן - סיפור אחר</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409406&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>4:10</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>זואי קפלן - סיפור אחר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>גיל קדלר - נשכבה</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409405&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>2:10</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Jason Derulo</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>גיל קדלר - נשכבה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409404&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:52</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>lights</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>אליקם בוטה - תהיה מאושר</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409403&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:50</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Telenova</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>אליקם בוטה - תהיה מאושר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People</v>
+        <v>אליה רומנו - הילד הקטן שלך</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409402&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>5:32</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Marcin</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>I Did "HOW MUSIC WORKS" Live To 1500 People - Marcin</v>
+        <v>אליה רומנו - הילד הקטן שלך</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>אלחנן אלחדד - תנגן את זה</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409401&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>4:27</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>We Three</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>אלחנן אלחדד - תנגן את זה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:01</v>
+        <v>2:57</v>
       </c>
       <c r="H9" t="str">
-        <v>Timebelle Official</v>
+        <v>The Offspring</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:20</v>
+        <v>4:10</v>
       </c>
       <c r="H10" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:34</v>
+        <v>2:10</v>
       </c>
       <c r="H11" t="str">
-        <v>Clinton Kane</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:01</v>
+        <v>3:52</v>
       </c>
       <c r="H12" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>lights</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H13" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Telenova</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>HOW MUSIC WORKS: Live on One Guitar</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>5:52</v>
+        <v>5:32</v>
       </c>
       <c r="H14" t="str">
-        <v>Harry Styles</v>
+        <v>Marcin</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>HOW MUSIC WORKS: Live on One Guitar - Marcin</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>5:01</v>
+        <v>4:27</v>
       </c>
       <c r="H15" t="str">
-        <v>Neal Francis</v>
+        <v>We Three</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:12</v>
+        <v>3:01</v>
       </c>
       <c r="H16" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:59</v>
+        <v>3:20</v>
       </c>
       <c r="H17" t="str">
-        <v>Holly Humberstone</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:56</v>
+        <v>3:34</v>
       </c>
       <c r="H18" t="str">
-        <v>Cliff Richard</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:46</v>
+        <v>4:01</v>
       </c>
       <c r="H19" t="str">
-        <v>Jessie Ware</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B20" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1138,10 +1138,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:37</v>
+        <v>3:24</v>
       </c>
       <c r="H20" t="str">
-        <v>Bella White</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1176,10 +1176,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:06</v>
+        <v>5:52</v>
       </c>
       <c r="H21" t="str">
-        <v>Ryan Wright</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1214,10 +1214,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:54</v>
+        <v>5:01</v>
       </c>
       <c r="H22" t="str">
-        <v>Dove Cameron</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1252,10 +1252,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:10</v>
+        <v>4:12</v>
       </c>
       <c r="H23" t="str">
-        <v>Parker McCollum</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1290,10 +1290,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:26</v>
+        <v>3:59</v>
       </c>
       <c r="H24" t="str">
-        <v>Matt Hansen</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:56</v>
       </c>
       <c r="H25" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B26" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1366,10 +1366,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H26" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1404,10 +1404,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:01</v>
+        <v>4:37</v>
       </c>
       <c r="H27" t="str">
-        <v>Tauren Wells</v>
+        <v>Bella White</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1442,10 +1442,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:05</v>
+        <v>4:06</v>
       </c>
       <c r="H28" t="str">
-        <v>Maiah Manser</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1480,10 +1480,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:27</v>
+        <v>3:54</v>
       </c>
       <c r="H29" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1518,10 +1518,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:34</v>
+        <v>4:10</v>
       </c>
       <c r="H30" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H31" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1591,10 +1591,10 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H32" t="str">
         <v>Louis Tomlinson</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H33" t="str">
-        <v>CAIN</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>5:14</v>
+        <v>4:01</v>
       </c>
       <c r="H34" t="str">
-        <v>Harry Styles</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:59</v>
+        <v>3:05</v>
       </c>
       <c r="H35" t="str">
-        <v>Lana Lubany</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:21</v>
+        <v>2:27</v>
       </c>
       <c r="H36" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H37" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H38" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>3:13</v>
       </c>
       <c r="H39" t="str">
-        <v>Olivia Dean</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:21</v>
+        <v>3:08</v>
       </c>
       <c r="H40" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>CAIN</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:06</v>
+        <v>5:14</v>
       </c>
       <c r="H41" t="str">
-        <v>The Avett Brothers</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:21</v>
+        <v>2:59</v>
       </c>
       <c r="H42" t="str">
-        <v>Jordana Bryant</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>7:21</v>
+        <v>4:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Katy Perry</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:17</v>
+        <v>4:09</v>
       </c>
       <c r="H44" t="str">
-        <v>Lauren Watkins</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:45</v>
+        <v>2:34</v>
       </c>
       <c r="H45" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B46" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:57</v>
+        <v>3:10</v>
       </c>
       <c r="H46" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B47" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H47" t="str">
-        <v>Charlie Puth</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:27</v>
+        <v>3:06</v>
       </c>
       <c r="H48" t="str">
-        <v>Chappell Roan</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:34</v>
+        <v>3:21</v>
       </c>
       <c r="H49" t="str">
-        <v>Armik</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:54</v>
+        <v>7:21</v>
       </c>
       <c r="H50" t="str">
-        <v>LØLØ</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:25</v>
+        <v>3:17</v>
       </c>
       <c r="H51" t="str">
-        <v>Tenille Townes</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:01</v>
+        <v>3:45</v>
       </c>
       <c r="H52" t="str">
-        <v>Alan Walker</v>
+        <v>Tones And I</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:25</v>
+        <v>3:57</v>
       </c>
       <c r="H53" t="str">
-        <v>Charli xcx</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>1:14</v>
+        <v>3:03</v>
       </c>
       <c r="H54" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:59</v>
+        <v>4:27</v>
       </c>
       <c r="H55" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2506,10 +2506,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:29</v>
+        <v>4:34</v>
       </c>
       <c r="H56" t="str">
-        <v>Girl Tones</v>
+        <v>Armik</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2544,10 +2544,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:34</v>
+        <v>2:54</v>
       </c>
       <c r="H57" t="str">
-        <v>Jagwar Twin</v>
+        <v>LØLØ</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2582,10 +2582,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:48</v>
+        <v>3:25</v>
       </c>
       <c r="H58" t="str">
-        <v>Caroline Jones</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2620,10 +2620,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:32</v>
+        <v>2:01</v>
       </c>
       <c r="H59" t="str">
-        <v>The Beaches</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B60" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2658,10 +2658,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:49</v>
+        <v>2:25</v>
       </c>
       <c r="H60" t="str">
-        <v>Dolly Parton</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2696,10 +2696,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:28</v>
+        <v>1:14</v>
       </c>
       <c r="H61" t="str">
-        <v>Madison Beer</v>
+        <v>Labrinth</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:37</v>
+        <v>2:59</v>
       </c>
       <c r="H62" t="str">
-        <v>Ty Myers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:35</v>
+        <v>2:29</v>
       </c>
       <c r="H63" t="str">
-        <v>Megan Moroney</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:31</v>
+        <v>2:34</v>
       </c>
       <c r="H64" t="str">
-        <v>Julia Cole Music</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:21</v>
+        <v>3:48</v>
       </c>
       <c r="H65" t="str">
-        <v>Lily Allen</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:24</v>
+        <v>3:32</v>
       </c>
       <c r="H66" t="str">
-        <v>Nickless</v>
+        <v>The Beaches</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:11</v>
+        <v>3:49</v>
       </c>
       <c r="H67" t="str">
-        <v>Peach PRC</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:11</v>
+        <v>4:28</v>
       </c>
       <c r="H68" t="str">
-        <v>Ocean Alley</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:31</v>
+        <v>3:37</v>
       </c>
       <c r="H69" t="str">
-        <v>OneRepublic</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:16</v>
+        <v>3:35</v>
       </c>
       <c r="H70" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:42</v>
+        <v>2:31</v>
       </c>
       <c r="H71" t="str">
-        <v>JavaJazzFest</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:47</v>
+        <v>3:21</v>
       </c>
       <c r="H72" t="str">
-        <v>Teo Glacier</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:59</v>
+        <v>5:24</v>
       </c>
       <c r="H73" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Nickless</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:09</v>
+        <v>3:11</v>
       </c>
       <c r="H74" t="str">
-        <v>Louie TheSinger</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H75" t="str">
-        <v>ella jane</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:14</v>
+        <v>3:31</v>
       </c>
       <c r="H76" t="str">
-        <v>Johnny Orlando</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:32</v>
+        <v>4:16</v>
       </c>
       <c r="H77" t="str">
-        <v>Kungs</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:15</v>
+        <v>4:42</v>
       </c>
       <c r="H78" t="str">
-        <v>Billy Raffoul</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:03</v>
+        <v>2:47</v>
       </c>
       <c r="H79" t="str">
-        <v>NathanEvanss</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:04</v>
+        <v>3:59</v>
       </c>
       <c r="H80" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:33</v>
+        <v>4:09</v>
       </c>
       <c r="H81" t="str">
-        <v>Bruno Mars</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:53</v>
+        <v>3:24</v>
       </c>
       <c r="H82" t="str">
-        <v>MAX</v>
+        <v>ella jane</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:11</v>
+        <v>3:14</v>
       </c>
       <c r="H83" t="str">
-        <v>Jessie J</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:45</v>
+        <v>3:32</v>
       </c>
       <c r="H84" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Kungs</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:00</v>
+        <v>3:15</v>
       </c>
       <c r="H85" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:27</v>
+        <v>3:03</v>
       </c>
       <c r="H86" t="str">
-        <v>The Kid LAROI.</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H87" t="str">
-        <v>Olivia Dean</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:34</v>
+        <v>3:33</v>
       </c>
       <c r="H88" t="str">
-        <v>Demi Lovato</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:25</v>
+        <v>2:53</v>
       </c>
       <c r="H89" t="str">
-        <v>Joseph</v>
+        <v>MAX</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:26</v>
+        <v>4:11</v>
       </c>
       <c r="H90" t="str">
-        <v>Demi Lovato</v>
+        <v>Jessie J</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:46</v>
+        <v>2:45</v>
       </c>
       <c r="H91" t="str">
-        <v>Keith Urban</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:24</v>
+        <v>4:00</v>
       </c>
       <c r="H92" t="str">
-        <v>Keith Urban</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:52</v>
+        <v>3:27</v>
       </c>
       <c r="H93" t="str">
-        <v>Madonna</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:06</v>
+        <v>3:25</v>
       </c>
       <c r="H94" t="str">
-        <v>Estás Tonné</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-29</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:09</v>
+        <v>3:34</v>
       </c>
       <c r="H95" t="str">
-        <v>Anna Graves</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-29</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:11</v>
+        <v>2:25</v>
       </c>
       <c r="H96" t="str">
-        <v>Ocean Alley</v>
+        <v>Joseph</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-29</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:40</v>
+        <v>3:26</v>
       </c>
       <c r="H97" t="str">
-        <v>Zara Larsson</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-29</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:49</v>
+        <v>4:46</v>
       </c>
       <c r="H98" t="str">
-        <v>Lauren Watkins</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-29</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:42</v>
+        <v>3:24</v>
       </c>
       <c r="H99" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-29</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:11</v>
+        <v>2:52</v>
       </c>
       <c r="H100" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Madonna</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-29</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:57</v>
+        <v>2:06</v>
       </c>
       <c r="H101" t="str">
-        <v>Lainey Wilson</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>For Hire</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>For Hire - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:44</v>
+        <v>3:09</v>
       </c>
       <c r="H102" t="str">
-        <v>People I’ve Met</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Aperture</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G103" t="str">
         <v>5:11</v>
       </c>
       <c r="H103" t="str">
-        <v>Harry Styles</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Opening Night</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>HELP(2)</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>4:19</v>
+        <v>3:40</v>
       </c>
       <c r="H104" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Don't Be Dumb</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:20</v>
+        <v>3:49</v>
       </c>
       <c r="H105" t="str">
-        <v>A$AP Rocky</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:01</v>
+        <v>3:42</v>
       </c>
       <c r="H106" t="str">
-        <v>Luis Fonsi</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Piss In The Wind</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:29</v>
+        <v>5:11</v>
       </c>
       <c r="H107" t="str">
-        <v>Joji</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>High Key</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Vacancy</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:12</v>
+        <v>3:57</v>
       </c>
       <c r="H108" t="str">
-        <v>Ari Lennox</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>scared</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>scared - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G109" t="str">
-        <v>3:46</v>
+        <v>2:30</v>
       </c>
       <c r="H109" t="str">
-        <v>Fred again..</v>
+        <v>Thundercat</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L109" t="str">
-        <v>scared - Fred again..</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Death of Love</v>
+        <v>Aperture</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Trying Times</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G110" t="str">
-        <v>3:26</v>
+        <v>5:11</v>
       </c>
       <c r="H110" t="str">
-        <v>James Blake</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L110" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Opening Night</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G111" t="str">
-        <v>4:03</v>
+        <v>4:19</v>
       </c>
       <c r="H111" t="str">
-        <v>Parker McCollum</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L111" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ATM</v>
+        <v>For Hire</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>OCTANE</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:00</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>Don Toliver</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L112" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Flo Jackson</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G113" t="str">
-        <v>2:23</v>
+        <v>2:20</v>
       </c>
       <c r="H113" t="str">
-        <v>Flo Milli</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L113" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Creature of Habit</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:46</v>
+        <v>3:01</v>
       </c>
       <c r="H114" t="str">
-        <v>Courtney Barnett</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L114" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Puppet Parade</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Megadeth</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G115" t="str">
-        <v>4:40</v>
+        <v>2:29</v>
       </c>
       <c r="H115" t="str">
-        <v>Megadeth</v>
+        <v>Joji</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L115" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>To Love Somebody</v>
+        <v>High Key</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Cruel World</v>
+        <v>Vacancy</v>
       </c>
       <c r="G116" t="str">
-        <v>3:57</v>
+        <v>2:12</v>
       </c>
       <c r="H116" t="str">
-        <v>Holly Humberstone</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L116" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>scared</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>scared - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>4:14</v>
+        <v>3:46</v>
       </c>
       <c r="H117" t="str">
-        <v>Cleo Sol</v>
+        <v>Fred again..</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L117" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Death of Love</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>THE CORE - 核</v>
+        <v>Trying Times</v>
       </c>
       <c r="G118" t="str">
-        <v>2:50</v>
+        <v>3:26</v>
       </c>
       <c r="H118" t="str">
-        <v>XG</v>
+        <v>James Blake</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L118" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Dead End</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Ricochet</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G119" t="str">
-        <v>4:05</v>
+        <v>4:03</v>
       </c>
       <c r="H119" t="str">
-        <v>Snail Mail</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L119" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>ATM</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>OCTANE</v>
       </c>
       <c r="G120" t="str">
-        <v>3:52</v>
+        <v>3:00</v>
       </c>
       <c r="H120" t="str">
-        <v>Dove Cameron</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L120" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:02</v>
+        <v>2:23</v>
       </c>
       <c r="H121" t="str">
-        <v>Kenia Os</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L121" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>BAD</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BAD - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G122" t="str">
-        <v>2:15</v>
+        <v>2:46</v>
       </c>
       <c r="H122" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L122" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Losing You</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>F.I.G</v>
+        <v>Megadeth</v>
       </c>
       <c r="G123" t="str">
-        <v>2:22</v>
+        <v>4:40</v>
       </c>
       <c r="H123" t="str">
-        <v>Naomi Scott</v>
+        <v>Megadeth</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L123" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G124" t="str">
-        <v>3:02</v>
+        <v>3:57</v>
       </c>
       <c r="H124" t="str">
-        <v>The Runarounds</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L124" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Infinito</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:14</v>
+        <v>4:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Yandel</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L125" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Sexy For Me</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G126" t="str">
-        <v>2:08</v>
+        <v>2:50</v>
       </c>
       <c r="H126" t="str">
-        <v>Jason Derulo</v>
+        <v>XG</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L126" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Turbulence</v>
+        <v>Dead End</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>Ricochet</v>
       </c>
       <c r="G127" t="str">
-        <v>2:25</v>
+        <v>4:05</v>
       </c>
       <c r="H127" t="str">
-        <v>Wizkid</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L127" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>3:52</v>
       </c>
       <c r="H128" t="str">
-        <v>Jelly Roll</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L128" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:47</v>
+        <v>3:02</v>
       </c>
       <c r="H129" t="str">
-        <v>Dolly Parton</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L129" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>ESCONDIDAS</v>
+        <v>BAD</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:53</v>
+        <v>2:15</v>
       </c>
       <c r="H130" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L130" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>Losing You</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Act I</v>
+        <v>F.I.G</v>
       </c>
       <c r="G131" t="str">
-        <v>3:43</v>
+        <v>2:22</v>
       </c>
       <c r="H131" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L131" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Imposter</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:38</v>
+        <v>3:02</v>
       </c>
       <c r="H132" t="str">
-        <v>Louis Tomlinson</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L132" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>Infinito</v>
       </c>
       <c r="G133" t="str">
-        <v>6:01</v>
+        <v>2:14</v>
       </c>
       <c r="H133" t="str">
-        <v>Not for Radio</v>
+        <v>Yandel</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L133" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G134" t="str">
-        <v>2:24</v>
+        <v>2:08</v>
       </c>
       <c r="H134" t="str">
-        <v>GIRLSET</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L134" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Turbulence</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G135" t="str">
-        <v>3:41</v>
+        <v>2:25</v>
       </c>
       <c r="H135" t="str">
-        <v>Jessie Ware</v>
+        <v>Wizkid</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L135" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>LA VILLA</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G136" t="str">
-        <v>3:12</v>
+        <v>2:59</v>
       </c>
       <c r="H136" t="str">
-        <v>Ryan Castro</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L136" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:27</v>
+        <v>3:47</v>
       </c>
       <c r="H137" t="str">
-        <v>Denzel Curry</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L137" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Thick One</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Part 3</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G138" t="str">
-        <v>2:49</v>
+        <v>2:53</v>
       </c>
       <c r="H138" t="str">
-        <v>42 Dugg</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L138" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Act I</v>
       </c>
       <c r="G139" t="str">
-        <v>3:59</v>
+        <v>3:43</v>
       </c>
       <c r="H139" t="str">
-        <v>Lucinda Williams</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L139" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>THUM</v>
+        <v>Imposter</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>THUM - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G140" t="str">
-        <v>2:11</v>
+        <v>2:38</v>
       </c>
       <c r="H140" t="str">
-        <v>Violet Grohl</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L140" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>The Great Satan</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:32</v>
+        <v>6:01</v>
       </c>
       <c r="H141" t="str">
-        <v>Rob Zombie</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L141" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Excuses For Love</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Hyperlove</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:04</v>
+        <v>2:24</v>
       </c>
       <c r="H142" t="str">
-        <v>MIKA</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L142" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>3 Tears</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>3 Tears - Single</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:50</v>
+        <v>3:41</v>
       </c>
       <c r="H143" t="str">
-        <v>Mergui</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L143" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Church Girl</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Church Girl - Single</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G144" t="str">
-        <v>3:19</v>
+        <v>3:12</v>
       </c>
       <c r="H144" t="str">
-        <v>Carly Pearce</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L144" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Funeral</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G145" t="str">
-        <v>4:03</v>
+        <v>3:27</v>
       </c>
       <c r="H145" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L145" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>dust to dust</v>
+        <v>Thick One</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>Part 3</v>
       </c>
       <c r="G146" t="str">
-        <v>3:51</v>
+        <v>2:49</v>
       </c>
       <c r="H146" t="str">
-        <v>Truman Sinclair</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L146" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Say Yes</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Say Yes - Single</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G147" t="str">
-        <v>2:50</v>
+        <v>3:59</v>
       </c>
       <c r="H147" t="str">
-        <v>Marques Anthony</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L147" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>THUM</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>CAMPILATION</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:10</v>
+        <v>2:11</v>
       </c>
       <c r="H148" t="str">
-        <v>Camper</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L148" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Ojalá</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ojalá - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G149" t="str">
-        <v>4:11</v>
+        <v>3:32</v>
       </c>
       <c r="H149" t="str">
-        <v>Lunay</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L149" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G150" t="str">
-        <v>2:17</v>
+        <v>3:04</v>
       </c>
       <c r="H150" t="str">
-        <v>Ledbyher</v>
+        <v>MIKA</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L150" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Wallflower</v>
+        <v>3 Tears</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Wallflower - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:25</v>
+        <v>2:50</v>
       </c>
       <c r="H151" t="str">
-        <v>Sikarus</v>
+        <v>Mergui</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L151" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>You Phase</v>
+        <v>Church Girl</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>You Phase - Single</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:51</v>
+        <v>3:19</v>
       </c>
       <c r="H152" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L152" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Miss Independent</v>
+        <v>Funeral</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Miss Independent - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G153" t="str">
-        <v>2:40</v>
+        <v>4:03</v>
       </c>
       <c r="H153" t="str">
-        <v>1Ski OG</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L153" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>dust to dust</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G154" t="str">
-        <v>5:47</v>
+        <v>3:51</v>
       </c>
       <c r="H154" t="str">
-        <v>Elevation Worship</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L154" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>go again</v>
+        <v>Say Yes</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>go again - Single</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:07</v>
+        <v>2:50</v>
       </c>
       <c r="H155" t="str">
-        <v>NateTaylorr</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L155" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Autopilot</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Autopilot</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G156" t="str">
-        <v>2:46</v>
+        <v>3:10</v>
       </c>
       <c r="H156" t="str">
-        <v>ALEXSUCKS</v>
+        <v>Camper</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L156" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Ojalá</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:04</v>
+        <v>4:11</v>
       </c>
       <c r="H157" t="str">
-        <v>SPELLLING</v>
+        <v>Lunay</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L157" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>In Violet</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>4:09</v>
+        <v>2:17</v>
       </c>
       <c r="H158" t="str">
-        <v>Searows</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L158" t="str">
-        <v>In Violet - Searows</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Baby Run</v>
+        <v>Wallflower</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Baby Run - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:47</v>
+        <v>3:25</v>
       </c>
       <c r="H159" t="str">
-        <v>Jimi Jules</v>
+        <v>Sikarus</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L159" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>What If We Don't</v>
+        <v>You Phase</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>What If We Don't - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H160" t="str">
-        <v>Ashley McBryde</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L160" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Hagamos Que</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:58</v>
+        <v>2:40</v>
       </c>
       <c r="H161" t="str">
-        <v>Juanes</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L161" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>World Change Me</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>World Change Me - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G162" t="str">
-        <v>3:03</v>
+        <v>5:47</v>
       </c>
       <c r="H162" t="str">
-        <v>Max McNown</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L162" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Exclusive</v>
+        <v>go again</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Exclusive - EP</v>
+        <v>go again - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:20</v>
+        <v>2:07</v>
       </c>
       <c r="H163" t="str">
-        <v>Hudson Westbrook</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L163" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Say Less</v>
+        <v>Autopilot</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Say Less - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G164" t="str">
-        <v>2:18</v>
+        <v>2:46</v>
       </c>
       <c r="H164" t="str">
-        <v>JYT</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L164" t="str">
-        <v>Say Less - JYT</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Angels Cry</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:52</v>
+        <v>3:04</v>
       </c>
       <c r="H165" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L165" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Over You</v>
+        <v>In Violet</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>A Love For Strangers</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G166" t="str">
-        <v>4:44</v>
+        <v>4:09</v>
       </c>
       <c r="H166" t="str">
-        <v>Chet Faker</v>
+        <v>Searows</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L166" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Baby Run</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:42</v>
+        <v>4:47</v>
       </c>
       <c r="H167" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L167" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G168" t="str">
         <v>3:06</v>
       </c>
       <c r="H168" t="str">
-        <v>Disco Lines</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L168" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:48</v>
+        <v>2:58</v>
       </c>
       <c r="H169" t="str">
-        <v>David Guetta</v>
+        <v>Juanes</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L169" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Rejoice</v>
+        <v>World Change Me</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Rejoice - Single</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>4:20</v>
+        <v>3:03</v>
       </c>
       <c r="H170" t="str">
-        <v>Def Leppard</v>
+        <v>Max McNown</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L170" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Exclusive</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>2:58</v>
+        <v>3:20</v>
       </c>
       <c r="H171" t="str">
-        <v>Honey Dijon</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L171" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Odisea</v>
+        <v>Say Less</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Odisea - Single</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:56</v>
+        <v>2:18</v>
       </c>
       <c r="H172" t="str">
-        <v>BASSYY</v>
+        <v>JYT</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L172" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Lucky Day</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Speed Kills</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G173" t="str">
-        <v>3:13</v>
+        <v>3:52</v>
       </c>
       <c r="H173" t="str">
-        <v>Ally Evenson</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L173" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Breathe On It</v>
+        <v>Over You</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Breathe On It - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G174" t="str">
-        <v>4:00</v>
+        <v>4:44</v>
       </c>
       <c r="H174" t="str">
-        <v>Tauren Wells</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L174" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Easy</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Easy - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:30</v>
+        <v>2:42</v>
       </c>
       <c r="H175" t="str">
-        <v>lydi lynn</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L175" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Break Me In</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Break Me In - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:52</v>
+        <v>3:06</v>
       </c>
       <c r="H176" t="str">
-        <v>Joyce Wrice</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L176" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Long Live Love</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:36</v>
+        <v>2:48</v>
       </c>
       <c r="H177" t="str">
-        <v>Sugar</v>
+        <v>David Guetta</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L177" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Depressed</v>
+        <v>Rejoice</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Boycott Heaven</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:32</v>
+        <v>4:20</v>
       </c>
       <c r="H178" t="str">
-        <v>The Format</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L178" t="str">
-        <v>Depressed - The Format</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Empty Hands</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Empty Hands</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:09</v>
+        <v>2:58</v>
       </c>
       <c r="H179" t="str">
-        <v>Poppy</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L179" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The Long Surrender</v>
+        <v>Odisea</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>The Long Surrender</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:45</v>
+        <v>3:56</v>
       </c>
       <c r="H180" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>BASSYY</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L180" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Angela</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Angela - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G181" t="str">
-        <v>3:32</v>
+        <v>3:13</v>
       </c>
       <c r="H181" t="str">
-        <v>Hayden Everett</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L181" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Disappear</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Greyhound</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:31</v>
+        <v>4:00</v>
       </c>
       <c r="H182" t="str">
-        <v>Katie Tupper</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L182" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Catapult</v>
+        <v>Easy</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Catapult - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:57</v>
+        <v>4:30</v>
       </c>
       <c r="H183" t="str">
-        <v>Cape Francis</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L183" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Think Twice</v>
+        <v>Break Me In</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Think Twice - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:22</v>
+        <v>2:52</v>
       </c>
       <c r="H184" t="str">
-        <v>Leonie Biney</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L184" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>LOVESONGS</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:33</v>
+        <v>2:36</v>
       </c>
       <c r="H185" t="str">
-        <v>Agnes</v>
+        <v>Sugar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L185" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Down South</v>
+        <v>Depressed</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Down South - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G186" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H186" t="str">
-        <v>Trap Dickey</v>
+        <v>The Format</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L186" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G187" t="str">
-        <v>2:16</v>
+        <v>3:09</v>
       </c>
       <c r="H187" t="str">
-        <v>SALIMATA</v>
+        <v>Poppy</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L187" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Love Like This</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Love Like This - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G188" t="str">
-        <v>3:30</v>
+        <v>3:45</v>
       </c>
       <c r="H188" t="str">
-        <v>Jacob Banks</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L188" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Plan Plan</v>
+        <v>Angela</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:10</v>
+        <v>3:32</v>
       </c>
       <c r="H189" t="str">
-        <v>Funky</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L189" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>double edged sword</v>
+        <v>Disappear</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D190" t="str">
         <v>2026-01-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>double edged sword - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G190" t="str">
-        <v>3:28</v>
+        <v>3:31</v>
       </c>
       <c r="H190" t="str">
-        <v>Hailey Picardi</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L190" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>Catapult</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D191" t="str">
         <v>2026-01-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:27</v>
+        <v>2:57</v>
       </c>
       <c r="H191" t="str">
-        <v>Matt Hansen</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L191" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>The Decay</v>
+        <v>Think Twice</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D192" t="str">
         <v>2026-01-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:20</v>
+        <v>2:22</v>
       </c>
       <c r="H192" t="str">
-        <v>Pop Evil</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L192" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>3111</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D193" t="str">
         <v>2026-01-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Goliath</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G193" t="str">
-        <v>4:08</v>
+        <v>3:33</v>
       </c>
       <c r="H193" t="str">
-        <v>Exodus</v>
+        <v>Agnes</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L193" t="str">
-        <v>3111 - Exodus</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Touch My Love And Die</v>
+        <v>Down South</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D194" t="str">
         <v>2026-01-29</v>
@@ -7747,68 +7747,372 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:57</v>
+        <v>2:19</v>
       </c>
       <c r="H194" t="str">
-        <v>Myrkur</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L194" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+      </c>
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+      </c>
+      <c r="G195" t="str">
+        <v>2:16</v>
+      </c>
+      <c r="H195" t="str">
+        <v>SALIMATA</v>
+      </c>
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+      </c>
+      <c r="K195" t="str">
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+      </c>
+      <c r="L195" t="str">
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Love Like This</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>Love Like This - Single</v>
+      </c>
+      <c r="G196" t="str">
+        <v>3:30</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Jacob Banks</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Love Like This - Jacob Banks</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Plan Plan</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>La Locura, Vol. 1</v>
+      </c>
+      <c r="G197" t="str">
+        <v>3:10</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Funky</v>
+      </c>
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
+      </c>
+      <c r="K197" t="str">
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Plan Plan - Funky</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>double edged sword</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>double edged sword - Single</v>
+      </c>
+      <c r="G198" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Hailey Picardi</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+      </c>
+      <c r="L198" t="str">
+        <v>double edged sword - Hailey Picardi</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>SOMEWHERE IN BETWEEN</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>SOMEWHERE IN BETWEEN - Single</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:27</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Matt Hansen</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+      </c>
+      <c r="L199" t="str">
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>The Decay</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>What Remains (Midnight Edition)</v>
+      </c>
+      <c r="G200" t="str">
+        <v>3:20</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Pop Evil</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+      </c>
+      <c r="L200" t="str">
+        <v>The Decay - Pop Evil</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>3111</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Goliath</v>
+      </c>
+      <c r="G201" t="str">
+        <v>4:08</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Exodus</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
+      </c>
+      <c r="L201" t="str">
+        <v>3111 - Exodus</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G202" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D195" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
+      <c r="D203" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G195" t="str">
+      <c r="G203" t="str">
         <v>2:41</v>
       </c>
-      <c r="H195" t="str">
+      <c r="H203" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K195" t="str">
+      <c r="K203" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L195" t="str">
+      <c r="L203" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יניב רם - כוחה של אמונה</v>
+        <v>פרחי ירושלים - רני שב הביתה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409407&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409411&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יניב רם - כוחה של אמונה</v>
+        <v>פרחי ירושלים - רני שב הביתה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>זואי קפלן - סיפור אחר</v>
+        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409406&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409410&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>זואי קפלן - סיפור אחר</v>
+        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>גיל קדלר - נשכבה</v>
+        <v>סיימון גרידיש - חמש לפנות בוקר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409405&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409409&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>גיל קדלר - נשכבה</v>
+        <v>סיימון גרידיש - חמש לפנות בוקר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
+        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-29</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409404&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409408&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>גבריאל דמרי - מחרוזת קצב של פעם 2026</v>
+        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אליקם בוטה - תהיה מאושר</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-29</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409403&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>2:57</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>The Offspring</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אליקם בוטה - תהיה מאושר</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אליה רומנו - הילד הקטן שלך</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-29</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409402&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>4:10</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אליה רומנו - הילד הקטן שלך</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אלחנן אלחדד - תנגן את זה</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-01-29</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409401&amp;sid=5970a759bdaf153328e4dde9a385d228</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>2:10</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Jason Derulo</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אלחנן אלחדד - תנגן את זה</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:57</v>
+        <v>3:52</v>
       </c>
       <c r="H9" t="str">
-        <v>The Offspring</v>
+        <v>lights</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:10</v>
+        <v>3:50</v>
       </c>
       <c r="H10" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Telenova</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>HOW MUSIC WORKS: Live on One Guitar</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -796,10 +796,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:10</v>
+        <v>5:32</v>
       </c>
       <c r="H11" t="str">
-        <v>Jason Derulo</v>
+        <v>Marcin</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>HOW MUSIC WORKS: Live on One Guitar - Marcin</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -834,10 +834,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:52</v>
+        <v>4:27</v>
       </c>
       <c r="H12" t="str">
-        <v>lights</v>
+        <v>We Three</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:50</v>
+        <v>3:01</v>
       </c>
       <c r="H13" t="str">
-        <v>Telenova</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HOW MUSIC WORKS: Live on One Guitar</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>5:32</v>
+        <v>3:20</v>
       </c>
       <c r="H14" t="str">
-        <v>Marcin</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>HOW MUSIC WORKS: Live on One Guitar - Marcin</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:27</v>
+        <v>3:34</v>
       </c>
       <c r="H15" t="str">
-        <v>We Three</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:01</v>
+        <v>4:01</v>
       </c>
       <c r="H16" t="str">
-        <v>Timebelle Official</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:20</v>
+        <v>3:24</v>
       </c>
       <c r="H17" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:34</v>
+        <v>5:52</v>
       </c>
       <c r="H18" t="str">
-        <v>Clinton Kane</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:01</v>
+        <v>5:01</v>
       </c>
       <c r="H19" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B20" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1138,10 +1138,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:24</v>
+        <v>4:12</v>
       </c>
       <c r="H20" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1176,10 +1176,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:52</v>
+        <v>3:59</v>
       </c>
       <c r="H21" t="str">
-        <v>Harry Styles</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1214,10 +1214,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:01</v>
+        <v>2:56</v>
       </c>
       <c r="H22" t="str">
-        <v>Neal Francis</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1252,10 +1252,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:12</v>
+        <v>3:46</v>
       </c>
       <c r="H23" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1290,10 +1290,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:59</v>
+        <v>4:37</v>
       </c>
       <c r="H24" t="str">
-        <v>Holly Humberstone</v>
+        <v>Bella White</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1328,10 +1328,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:56</v>
+        <v>4:06</v>
       </c>
       <c r="H25" t="str">
-        <v>Cliff Richard</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1366,10 +1366,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:46</v>
+        <v>3:54</v>
       </c>
       <c r="H26" t="str">
-        <v>Jessie Ware</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B27" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1404,10 +1404,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:37</v>
+        <v>4:10</v>
       </c>
       <c r="H27" t="str">
-        <v>Bella White</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1442,10 +1442,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:06</v>
+        <v>3:26</v>
       </c>
       <c r="H28" t="str">
-        <v>Ryan Wright</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:54</v>
+        <v>2:56</v>
       </c>
       <c r="H29" t="str">
-        <v>Dove Cameron</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1518,10 +1518,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:10</v>
+        <v>2:56</v>
       </c>
       <c r="H30" t="str">
-        <v>Parker McCollum</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:26</v>
+        <v>4:01</v>
       </c>
       <c r="H31" t="str">
-        <v>Matt Hansen</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:56</v>
+        <v>3:05</v>
       </c>
       <c r="H32" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:56</v>
+        <v>2:27</v>
       </c>
       <c r="H33" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:01</v>
+        <v>2:34</v>
       </c>
       <c r="H34" t="str">
-        <v>Tauren Wells</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:05</v>
+        <v>3:13</v>
       </c>
       <c r="H35" t="str">
-        <v>Maiah Manser</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:27</v>
+        <v>3:13</v>
       </c>
       <c r="H36" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1784,10 +1784,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:34</v>
+        <v>3:08</v>
       </c>
       <c r="H37" t="str">
-        <v>Chelsea Cutler</v>
+        <v>CAIN</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B38" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1822,10 +1822,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:13</v>
+        <v>5:14</v>
       </c>
       <c r="H38" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:13</v>
+        <v>2:59</v>
       </c>
       <c r="H39" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:08</v>
+        <v>4:21</v>
       </c>
       <c r="H40" t="str">
-        <v>CAIN</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:14</v>
+        <v>4:09</v>
       </c>
       <c r="H41" t="str">
-        <v>Harry Styles</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:59</v>
+        <v>2:34</v>
       </c>
       <c r="H42" t="str">
-        <v>Lana Lubany</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:21</v>
+        <v>3:10</v>
       </c>
       <c r="H43" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:09</v>
+        <v>3:21</v>
       </c>
       <c r="H44" t="str">
-        <v>Dermot Kennedy</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:34</v>
+        <v>3:06</v>
       </c>
       <c r="H45" t="str">
-        <v>Lauren Sanderson</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2126,10 +2126,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H46" t="str">
-        <v>Olivia Dean</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B47" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2164,10 +2164,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:21</v>
+        <v>7:21</v>
       </c>
       <c r="H47" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B48" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2202,10 +2202,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H48" t="str">
-        <v>The Avett Brothers</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:21</v>
+        <v>3:45</v>
       </c>
       <c r="H49" t="str">
-        <v>Jordana Bryant</v>
+        <v>Tones And I</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>7:21</v>
+        <v>3:57</v>
       </c>
       <c r="H50" t="str">
-        <v>Katy Perry</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:17</v>
+        <v>3:03</v>
       </c>
       <c r="H51" t="str">
-        <v>Lauren Watkins</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:45</v>
+        <v>4:27</v>
       </c>
       <c r="H52" t="str">
-        <v>Tones And I</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:57</v>
+        <v>4:34</v>
       </c>
       <c r="H53" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Armik</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:03</v>
+        <v>2:54</v>
       </c>
       <c r="H54" t="str">
-        <v>Charlie Puth</v>
+        <v>LØLØ</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:27</v>
+        <v>3:25</v>
       </c>
       <c r="H55" t="str">
-        <v>Chappell Roan</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2506,10 +2506,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:34</v>
+        <v>2:01</v>
       </c>
       <c r="H56" t="str">
-        <v>Armik</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B57" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2544,10 +2544,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:54</v>
+        <v>2:25</v>
       </c>
       <c r="H57" t="str">
-        <v>LØLØ</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2582,10 +2582,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:25</v>
+        <v>1:14</v>
       </c>
       <c r="H58" t="str">
-        <v>Tenille Townes</v>
+        <v>Labrinth</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B59" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2620,10 +2620,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:01</v>
+        <v>2:59</v>
       </c>
       <c r="H59" t="str">
-        <v>Alan Walker</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2658,10 +2658,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:25</v>
+        <v>2:29</v>
       </c>
       <c r="H60" t="str">
-        <v>Charli xcx</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2696,10 +2696,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>1:14</v>
+        <v>2:34</v>
       </c>
       <c r="H61" t="str">
-        <v>Labrinth</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:59</v>
+        <v>3:48</v>
       </c>
       <c r="H62" t="str">
-        <v>Charlie Puth</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:29</v>
+        <v>3:32</v>
       </c>
       <c r="H63" t="str">
-        <v>Girl Tones</v>
+        <v>The Beaches</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:34</v>
+        <v>3:49</v>
       </c>
       <c r="H64" t="str">
-        <v>Jagwar Twin</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:48</v>
+        <v>4:28</v>
       </c>
       <c r="H65" t="str">
-        <v>Caroline Jones</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:32</v>
+        <v>3:37</v>
       </c>
       <c r="H66" t="str">
-        <v>The Beaches</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B67" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2924,10 +2924,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:49</v>
+        <v>3:35</v>
       </c>
       <c r="H67" t="str">
-        <v>Dolly Parton</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2962,10 +2962,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:28</v>
+        <v>2:31</v>
       </c>
       <c r="H68" t="str">
-        <v>Madison Beer</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:37</v>
+        <v>3:21</v>
       </c>
       <c r="H69" t="str">
-        <v>Ty Myers</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:35</v>
+        <v>5:24</v>
       </c>
       <c r="H70" t="str">
-        <v>Megan Moroney</v>
+        <v>Nickless</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:31</v>
+        <v>3:11</v>
       </c>
       <c r="H71" t="str">
-        <v>Julia Cole Music</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:21</v>
+        <v>4:11</v>
       </c>
       <c r="H72" t="str">
-        <v>Lily Allen</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>5:24</v>
+        <v>3:31</v>
       </c>
       <c r="H73" t="str">
-        <v>Nickless</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:11</v>
+        <v>4:16</v>
       </c>
       <c r="H74" t="str">
-        <v>Peach PRC</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:11</v>
+        <v>4:42</v>
       </c>
       <c r="H75" t="str">
-        <v>Ocean Alley</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:31</v>
+        <v>2:47</v>
       </c>
       <c r="H76" t="str">
-        <v>OneRepublic</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:16</v>
+        <v>3:59</v>
       </c>
       <c r="H77" t="str">
-        <v>Ty Myers</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:42</v>
+        <v>4:09</v>
       </c>
       <c r="H78" t="str">
-        <v>JavaJazzFest</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H79" t="str">
-        <v>Teo Glacier</v>
+        <v>ella jane</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:59</v>
+        <v>3:14</v>
       </c>
       <c r="H80" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:09</v>
+        <v>3:32</v>
       </c>
       <c r="H81" t="str">
-        <v>Louie TheSinger</v>
+        <v>Kungs</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H82" t="str">
-        <v>ella jane</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:14</v>
+        <v>3:03</v>
       </c>
       <c r="H83" t="str">
-        <v>Johnny Orlando</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:32</v>
+        <v>3:04</v>
       </c>
       <c r="H84" t="str">
-        <v>Kungs</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:15</v>
+        <v>3:33</v>
       </c>
       <c r="H85" t="str">
-        <v>Billy Raffoul</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:03</v>
+        <v>2:53</v>
       </c>
       <c r="H86" t="str">
-        <v>NathanEvanss</v>
+        <v>MAX</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:04</v>
+        <v>4:11</v>
       </c>
       <c r="H87" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Jessie J</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:33</v>
+        <v>2:45</v>
       </c>
       <c r="H88" t="str">
-        <v>Bruno Mars</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:53</v>
+        <v>4:00</v>
       </c>
       <c r="H89" t="str">
-        <v>MAX</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:11</v>
+        <v>3:27</v>
       </c>
       <c r="H90" t="str">
-        <v>Jessie J</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:45</v>
+        <v>3:25</v>
       </c>
       <c r="H91" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:00</v>
+        <v>3:34</v>
       </c>
       <c r="H92" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:27</v>
+        <v>2:25</v>
       </c>
       <c r="H93" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Joseph</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H94" t="str">
-        <v>Olivia Dean</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-29</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:34</v>
+        <v>4:46</v>
       </c>
       <c r="H95" t="str">
-        <v>Demi Lovato</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-29</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:25</v>
+        <v>3:24</v>
       </c>
       <c r="H96" t="str">
-        <v>Joseph</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-29</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:26</v>
+        <v>2:52</v>
       </c>
       <c r="H97" t="str">
-        <v>Demi Lovato</v>
+        <v>Madonna</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-29</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:46</v>
+        <v>2:06</v>
       </c>
       <c r="H98" t="str">
-        <v>Keith Urban</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-29</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:24</v>
+        <v>3:09</v>
       </c>
       <c r="H99" t="str">
-        <v>Keith Urban</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-29</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:52</v>
+        <v>5:11</v>
       </c>
       <c r="H100" t="str">
-        <v>Madonna</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-29</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:06</v>
+        <v>3:40</v>
       </c>
       <c r="H101" t="str">
-        <v>Estás Tonné</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B102" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-29</v>
@@ -4254,10 +4254,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:09</v>
+        <v>3:49</v>
       </c>
       <c r="H102" t="str">
-        <v>Anna Graves</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B103" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-29</v>
@@ -4292,10 +4292,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>5:11</v>
+        <v>3:42</v>
       </c>
       <c r="H103" t="str">
-        <v>Ocean Alley</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B104" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-29</v>
@@ -4330,10 +4330,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:40</v>
+        <v>5:11</v>
       </c>
       <c r="H104" t="str">
-        <v>Zara Larsson</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,18 +4345,18 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B105" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-29</v>
@@ -4368,10 +4368,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:49</v>
+        <v>3:57</v>
       </c>
       <c r="H105" t="str">
-        <v>Lauren Watkins</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4383,18 +4383,18 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B106" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>3 weeks ago</v>
+        <v>Distracted</v>
       </c>
       <c r="G106" t="str">
-        <v>3:42</v>
+        <v>2:30</v>
       </c>
       <c r="H106" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L106" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Aperture</v>
       </c>
       <c r="B107" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>3 weeks ago</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G107" t="str">
         <v>5:11</v>
       </c>
       <c r="H107" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L107" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Opening Night</v>
       </c>
       <c r="B108" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>3 weeks ago</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G108" t="str">
-        <v>3:57</v>
+        <v>4:19</v>
       </c>
       <c r="H108" t="str">
-        <v>Lainey Wilson</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L108" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>I Did This To Myself</v>
+        <v>For Hire</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Distracted</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:30</v>
+        <v>3:44</v>
       </c>
       <c r="H109" t="str">
-        <v>Thundercat</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L109" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Aperture</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G110" t="str">
-        <v>5:11</v>
+        <v>2:20</v>
       </c>
       <c r="H110" t="str">
-        <v>Harry Styles</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L110" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Opening Night</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>HELP(2)</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:19</v>
+        <v>3:01</v>
       </c>
       <c r="H111" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L111" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>For Hire</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>For Hire - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>2:29</v>
       </c>
       <c r="H112" t="str">
-        <v>People I’ve Met</v>
+        <v>Joji</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L112" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>High Key</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Don't Be Dumb</v>
+        <v>Vacancy</v>
       </c>
       <c r="G113" t="str">
-        <v>2:20</v>
+        <v>2:12</v>
       </c>
       <c r="H113" t="str">
-        <v>A$AP Rocky</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L113" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>CAMBIARÉ</v>
+        <v>scared</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>scared - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:01</v>
+        <v>3:46</v>
       </c>
       <c r="H114" t="str">
-        <v>Luis Fonsi</v>
+        <v>Fred again..</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L114" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>Death of Love</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Piss In The Wind</v>
+        <v>Trying Times</v>
       </c>
       <c r="G115" t="str">
-        <v>2:29</v>
+        <v>3:26</v>
       </c>
       <c r="H115" t="str">
-        <v>Joji</v>
+        <v>James Blake</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L115" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>High Key</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Vacancy</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G116" t="str">
-        <v>2:12</v>
+        <v>4:03</v>
       </c>
       <c r="H116" t="str">
-        <v>Ari Lennox</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L116" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>scared</v>
+        <v>ATM</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>scared - Single</v>
+        <v>OCTANE</v>
       </c>
       <c r="G117" t="str">
-        <v>3:46</v>
+        <v>3:00</v>
       </c>
       <c r="H117" t="str">
-        <v>Fred again..</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L117" t="str">
-        <v>scared - Fred again..</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Death of Love</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Trying Times</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:26</v>
+        <v>2:23</v>
       </c>
       <c r="H118" t="str">
-        <v>James Blake</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L118" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G119" t="str">
-        <v>4:03</v>
+        <v>2:46</v>
       </c>
       <c r="H119" t="str">
-        <v>Parker McCollum</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L119" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ATM</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>OCTANE</v>
+        <v>Megadeth</v>
       </c>
       <c r="G120" t="str">
-        <v>3:00</v>
+        <v>4:40</v>
       </c>
       <c r="H120" t="str">
-        <v>Don Toliver</v>
+        <v>Megadeth</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L120" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Flo Jackson</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G121" t="str">
-        <v>2:23</v>
+        <v>3:57</v>
       </c>
       <c r="H121" t="str">
-        <v>Flo Milli</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L121" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Creature of Habit</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:46</v>
+        <v>4:14</v>
       </c>
       <c r="H122" t="str">
-        <v>Courtney Barnett</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L122" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Puppet Parade</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Megadeth</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G123" t="str">
-        <v>4:40</v>
+        <v>2:50</v>
       </c>
       <c r="H123" t="str">
-        <v>Megadeth</v>
+        <v>XG</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L123" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>To Love Somebody</v>
+        <v>Dead End</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Cruel World</v>
+        <v>Ricochet</v>
       </c>
       <c r="G124" t="str">
-        <v>3:57</v>
+        <v>4:05</v>
       </c>
       <c r="H124" t="str">
-        <v>Holly Humberstone</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L124" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:14</v>
+        <v>3:52</v>
       </c>
       <c r="H125" t="str">
-        <v>Cleo Sol</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L125" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>THE CORE - 核</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G126" t="str">
-        <v>2:50</v>
+        <v>3:02</v>
       </c>
       <c r="H126" t="str">
-        <v>XG</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L126" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Dead End</v>
+        <v>BAD</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Ricochet</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:05</v>
+        <v>2:15</v>
       </c>
       <c r="H127" t="str">
-        <v>Snail Mail</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L127" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Losing You</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G128" t="str">
-        <v>3:52</v>
+        <v>2:22</v>
       </c>
       <c r="H128" t="str">
-        <v>Dove Cameron</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L128" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G129" t="str">
         <v>3:02</v>
       </c>
       <c r="H129" t="str">
-        <v>Kenia Os</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L129" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>BAD</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>BAD - Single</v>
+        <v>Infinito</v>
       </c>
       <c r="G130" t="str">
-        <v>2:15</v>
+        <v>2:14</v>
       </c>
       <c r="H130" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Yandel</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L130" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Losing You</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>F.I.G</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G131" t="str">
-        <v>2:22</v>
+        <v>2:08</v>
       </c>
       <c r="H131" t="str">
-        <v>Naomi Scott</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L131" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>Turbulence</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G132" t="str">
-        <v>3:02</v>
+        <v>2:25</v>
       </c>
       <c r="H132" t="str">
-        <v>The Runarounds</v>
+        <v>Wizkid</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L132" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Infinito</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G133" t="str">
-        <v>2:14</v>
+        <v>2:59</v>
       </c>
       <c r="H133" t="str">
-        <v>Yandel</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L133" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Sexy For Me</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:08</v>
+        <v>3:47</v>
       </c>
       <c r="H134" t="str">
-        <v>Jason Derulo</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L134" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Turbulence</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G135" t="str">
-        <v>2:25</v>
+        <v>2:53</v>
       </c>
       <c r="H135" t="str">
-        <v>Wizkid</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L135" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Act I</v>
       </c>
       <c r="G136" t="str">
-        <v>2:59</v>
+        <v>3:43</v>
       </c>
       <c r="H136" t="str">
-        <v>Jelly Roll</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L136" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Imposter</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G137" t="str">
-        <v>3:47</v>
+        <v>2:38</v>
       </c>
       <c r="H137" t="str">
-        <v>Dolly Parton</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L137" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:53</v>
+        <v>6:01</v>
       </c>
       <c r="H138" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L138" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Act I</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:43</v>
+        <v>2:24</v>
       </c>
       <c r="H139" t="str">
-        <v>Kashus Culpepper</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L139" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Imposter</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>How Did I Get Here?</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:38</v>
+        <v>3:41</v>
       </c>
       <c r="H140" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L140" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G141" t="str">
-        <v>6:01</v>
+        <v>3:12</v>
       </c>
       <c r="H141" t="str">
-        <v>Not for Radio</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L141" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G142" t="str">
-        <v>2:24</v>
+        <v>3:27</v>
       </c>
       <c r="H142" t="str">
-        <v>GIRLSET</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L142" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Thick One</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>Part 3</v>
       </c>
       <c r="G143" t="str">
-        <v>3:41</v>
+        <v>2:49</v>
       </c>
       <c r="H143" t="str">
-        <v>Jessie Ware</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L143" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>LA VILLA</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G144" t="str">
-        <v>3:12</v>
+        <v>3:59</v>
       </c>
       <c r="H144" t="str">
-        <v>Ryan Castro</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L144" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>THUM</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:27</v>
+        <v>2:11</v>
       </c>
       <c r="H145" t="str">
-        <v>Denzel Curry</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L145" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Thick One</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Part 3</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G146" t="str">
-        <v>2:49</v>
+        <v>3:32</v>
       </c>
       <c r="H146" t="str">
-        <v>42 Dugg</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L146" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G147" t="str">
-        <v>3:59</v>
+        <v>3:04</v>
       </c>
       <c r="H147" t="str">
-        <v>Lucinda Williams</v>
+        <v>MIKA</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L147" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>THUM</v>
+        <v>3 Tears</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>THUM - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:11</v>
+        <v>2:50</v>
       </c>
       <c r="H148" t="str">
-        <v>Violet Grohl</v>
+        <v>Mergui</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L148" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>Church Girl</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>The Great Satan</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:32</v>
+        <v>3:19</v>
       </c>
       <c r="H149" t="str">
-        <v>Rob Zombie</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L149" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Excuses For Love</v>
+        <v>Funeral</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Hyperlove</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G150" t="str">
-        <v>3:04</v>
+        <v>4:03</v>
       </c>
       <c r="H150" t="str">
-        <v>MIKA</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L150" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>3 Tears</v>
+        <v>dust to dust</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>3 Tears - Single</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H151" t="str">
-        <v>Mergui</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L151" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Church Girl</v>
+        <v>Say Yes</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Church Girl - Single</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H152" t="str">
-        <v>Carly Pearce</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L152" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Funeral</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>The Weight of the Woods</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G153" t="str">
-        <v>4:03</v>
+        <v>3:10</v>
       </c>
       <c r="H153" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Camper</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L153" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>dust to dust</v>
+        <v>Ojalá</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:51</v>
+        <v>4:11</v>
       </c>
       <c r="H154" t="str">
-        <v>Truman Sinclair</v>
+        <v>Lunay</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L154" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Say Yes</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Say Yes - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:50</v>
+        <v>2:17</v>
       </c>
       <c r="H155" t="str">
-        <v>Marques Anthony</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L155" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Wallflower</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>CAMPILATION</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:10</v>
+        <v>3:25</v>
       </c>
       <c r="H156" t="str">
-        <v>Camper</v>
+        <v>Sikarus</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L156" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ojalá</v>
+        <v>You Phase</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Ojalá - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>4:11</v>
+        <v>2:51</v>
       </c>
       <c r="H157" t="str">
-        <v>Lunay</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L157" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:17</v>
+        <v>2:40</v>
       </c>
       <c r="H158" t="str">
-        <v>Ledbyher</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L158" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Wallflower</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Wallflower - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G159" t="str">
-        <v>3:25</v>
+        <v>5:47</v>
       </c>
       <c r="H159" t="str">
-        <v>Sikarus</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L159" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>You Phase</v>
+        <v>go again</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>You Phase - Single</v>
+        <v>go again - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:51</v>
+        <v>2:07</v>
       </c>
       <c r="H160" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L160" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Miss Independent</v>
+        <v>Autopilot</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Miss Independent - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G161" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H161" t="str">
-        <v>1Ski OG</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L161" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>5:47</v>
+        <v>3:04</v>
       </c>
       <c r="H162" t="str">
-        <v>Elevation Worship</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L162" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>go again</v>
+        <v>In Violet</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>go again - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G163" t="str">
-        <v>2:07</v>
+        <v>4:09</v>
       </c>
       <c r="H163" t="str">
-        <v>NateTaylorr</v>
+        <v>Searows</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L163" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Autopilot</v>
+        <v>Baby Run</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Autopilot</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:46</v>
+        <v>4:47</v>
       </c>
       <c r="H164" t="str">
-        <v>ALEXSUCKS</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L164" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H165" t="str">
-        <v>SPELLLING</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L165" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>In Violet</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:09</v>
+        <v>2:58</v>
       </c>
       <c r="H166" t="str">
-        <v>Searows</v>
+        <v>Juanes</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L166" t="str">
-        <v>In Violet - Searows</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Baby Run</v>
+        <v>World Change Me</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Baby Run - Single</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:47</v>
+        <v>3:03</v>
       </c>
       <c r="H167" t="str">
-        <v>Jimi Jules</v>
+        <v>Max McNown</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L167" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>What If We Don't</v>
+        <v>Exclusive</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>3:06</v>
+        <v>3:20</v>
       </c>
       <c r="H168" t="str">
-        <v>Ashley McBryde</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L168" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Hagamos Que</v>
+        <v>Say Less</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:58</v>
+        <v>2:18</v>
       </c>
       <c r="H169" t="str">
-        <v>Juanes</v>
+        <v>JYT</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L169" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>World Change Me</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>World Change Me - Single</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G170" t="str">
-        <v>3:03</v>
+        <v>3:52</v>
       </c>
       <c r="H170" t="str">
-        <v>Max McNown</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L170" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Exclusive</v>
+        <v>Over You</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Exclusive - EP</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G171" t="str">
-        <v>3:20</v>
+        <v>4:44</v>
       </c>
       <c r="H171" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L171" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Say Less</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Say Less - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:18</v>
+        <v>2:42</v>
       </c>
       <c r="H172" t="str">
-        <v>JYT</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L172" t="str">
-        <v>Say Less - JYT</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Angels Cry</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:52</v>
+        <v>3:06</v>
       </c>
       <c r="H173" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L173" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Over You</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>A Love For Strangers</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>4:44</v>
+        <v>2:48</v>
       </c>
       <c r="H174" t="str">
-        <v>Chet Faker</v>
+        <v>David Guetta</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L174" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Rejoice</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:42</v>
+        <v>4:20</v>
       </c>
       <c r="H175" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L175" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:06</v>
+        <v>2:58</v>
       </c>
       <c r="H176" t="str">
-        <v>Disco Lines</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L176" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Odisea</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:48</v>
+        <v>3:56</v>
       </c>
       <c r="H177" t="str">
-        <v>David Guetta</v>
+        <v>BASSYY</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L177" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rejoice</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Rejoice - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G178" t="str">
-        <v>4:20</v>
+        <v>3:13</v>
       </c>
       <c r="H178" t="str">
-        <v>Def Leppard</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L178" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:58</v>
+        <v>4:00</v>
       </c>
       <c r="H179" t="str">
-        <v>Honey Dijon</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L179" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Odisea</v>
+        <v>Easy</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Odisea - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:56</v>
+        <v>4:30</v>
       </c>
       <c r="H180" t="str">
-        <v>BASSYY</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L180" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Lucky Day</v>
+        <v>Break Me In</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Speed Kills</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:13</v>
+        <v>2:52</v>
       </c>
       <c r="H181" t="str">
-        <v>Ally Evenson</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L181" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Breathe On It</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>4:00</v>
+        <v>2:36</v>
       </c>
       <c r="H182" t="str">
-        <v>Tauren Wells</v>
+        <v>Sugar</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L182" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Easy</v>
+        <v>Depressed</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Easy - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G183" t="str">
-        <v>4:30</v>
+        <v>3:32</v>
       </c>
       <c r="H183" t="str">
-        <v>lydi lynn</v>
+        <v>The Format</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L183" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Break Me In</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Break Me In - Single</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G184" t="str">
-        <v>2:52</v>
+        <v>3:09</v>
       </c>
       <c r="H184" t="str">
-        <v>Joyce Wrice</v>
+        <v>Poppy</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L184" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Long Live Love</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Long Live Love - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G185" t="str">
-        <v>2:36</v>
+        <v>3:45</v>
       </c>
       <c r="H185" t="str">
-        <v>Sugar</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L185" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Depressed</v>
+        <v>Angela</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Boycott Heaven</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G186" t="str">
         <v>3:32</v>
       </c>
       <c r="H186" t="str">
-        <v>The Format</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L186" t="str">
-        <v>Depressed - The Format</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Empty Hands</v>
+        <v>Disappear</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Empty Hands</v>
+        <v>Greyhound</v>
       </c>
       <c r="G187" t="str">
-        <v>3:09</v>
+        <v>3:31</v>
       </c>
       <c r="H187" t="str">
-        <v>Poppy</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L187" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>The Long Surrender</v>
+        <v>Catapult</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>The Long Surrender</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:45</v>
+        <v>2:57</v>
       </c>
       <c r="H188" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L188" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Angela</v>
+        <v>Think Twice</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Angela - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:32</v>
+        <v>2:22</v>
       </c>
       <c r="H189" t="str">
-        <v>Hayden Everett</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L189" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Disappear</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D190" t="str">
         <v>2026-01-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Greyhound</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G190" t="str">
-        <v>3:31</v>
+        <v>3:33</v>
       </c>
       <c r="H190" t="str">
-        <v>Katie Tupper</v>
+        <v>Agnes</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L190" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Catapult</v>
+        <v>Down South</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D191" t="str">
         <v>2026-01-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Catapult - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:57</v>
+        <v>2:19</v>
       </c>
       <c r="H191" t="str">
-        <v>Cape Francis</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L191" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Think Twice</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D192" t="str">
         <v>2026-01-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Think Twice - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:22</v>
+        <v>2:16</v>
       </c>
       <c r="H192" t="str">
-        <v>Leonie Biney</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L192" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>LOVESONGS</v>
+        <v>Love Like This</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D193" t="str">
         <v>2026-01-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:33</v>
+        <v>3:30</v>
       </c>
       <c r="H193" t="str">
-        <v>Agnes</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L193" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Down South</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D194" t="str">
         <v>2026-01-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Down South - Single</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G194" t="str">
-        <v>2:19</v>
+        <v>3:10</v>
       </c>
       <c r="H194" t="str">
-        <v>Trap Dickey</v>
+        <v>Funky</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L194" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>double edged sword</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D195" t="str">
         <v>2026-01-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:16</v>
+        <v>3:28</v>
       </c>
       <c r="H195" t="str">
-        <v>SALIMATA</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L195" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Love Like This</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D196" t="str">
         <v>2026-01-29</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Love Like This - Single</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:30</v>
+        <v>3:27</v>
       </c>
       <c r="H196" t="str">
-        <v>Jacob Banks</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L196" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Plan Plan</v>
+        <v>The Decay</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D197" t="str">
         <v>2026-01-29</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G197" t="str">
-        <v>3:10</v>
+        <v>3:20</v>
       </c>
       <c r="H197" t="str">
-        <v>Funky</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L197" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>double edged sword</v>
+        <v>3111</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D198" t="str">
         <v>2026-01-29</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>double edged sword - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G198" t="str">
-        <v>3:28</v>
+        <v>4:08</v>
       </c>
       <c r="H198" t="str">
-        <v>Hailey Picardi</v>
+        <v>Exodus</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L198" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>Touch My Love And Die</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D199" t="str">
         <v>2026-01-29</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>Touch My Love And Die - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:27</v>
+        <v>2:57</v>
       </c>
       <c r="H199" t="str">
-        <v>Matt Hansen</v>
+        <v>Myrkur</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
       </c>
       <c r="L199" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>Touch My Love And Die - Myrkur</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>The Decay</v>
+        <v>Bomb To A Knife Fight</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D200" t="str">
         <v>2026-01-29</v>
@@ -7975,144 +7975,30 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>Bomb To A Knife Fight - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:20</v>
+        <v>2:41</v>
       </c>
       <c r="H200" t="str">
-        <v>Pop Evil</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
       <c r="L200" t="str">
-        <v>The Decay - Pop Evil</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>3111</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Goliath</v>
-      </c>
-      <c r="G201" t="str">
-        <v>4:08</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Exodus</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
-      </c>
-      <c r="L201" t="str">
-        <v>3111 - Exodus</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Touch My Love And Die</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Touch My Love And Die - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>2:57</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Myrkur</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Bomb To A Knife Fight</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Bomb To A Knife Fight - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>2:41</v>
-      </c>
-      <c r="H203" t="str">
-        <v>The Barbarians of California</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
-      </c>
-      <c r="L203" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרחי ירושלים - רני שב הביתה</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-29</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409411&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:16</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Teddy Swims</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרחי ירושלים - רני שב הביתה</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-29</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409410&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>3:14</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Beck</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עופר לוי &amp; גילי זיגמן - מאוהב בגשם 2026</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>סיימון גרידיש - חמש לפנות בוקר</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-29</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409409&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>2:57</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>The Offspring</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>סיימון גרידיש - חמש לפנות בוקר</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-29</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409408&amp;sid=c497b502b049ecd129e0847bcfcd5a46</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>4:10</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יצחק גבריאל - מחרוזת שבת 2026</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:57</v>
+        <v>2:10</v>
       </c>
       <c r="H6" t="str">
-        <v>The Offspring</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:10</v>
+        <v>3:52</v>
       </c>
       <c r="H7" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>lights</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H8" t="str">
-        <v>Jason Derulo</v>
+        <v>Telenova</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>When I Did "How Music Works" LIVE To 1500 People</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:52</v>
+        <v>5:32</v>
       </c>
       <c r="H9" t="str">
-        <v>lights</v>
+        <v>Marcin</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>When I Did "How Music Works" LIVE To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:50</v>
+        <v>4:27</v>
       </c>
       <c r="H10" t="str">
-        <v>Telenova</v>
+        <v>We Three</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HOW MUSIC WORKS: Live on One Guitar</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:32</v>
+        <v>3:01</v>
       </c>
       <c r="H11" t="str">
-        <v>Marcin</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>HOW MUSIC WORKS: Live on One Guitar - Marcin</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:27</v>
+        <v>3:20</v>
       </c>
       <c r="H12" t="str">
-        <v>We Three</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:01</v>
+        <v>3:34</v>
       </c>
       <c r="H13" t="str">
-        <v>Timebelle Official</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:20</v>
+        <v>4:01</v>
       </c>
       <c r="H14" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:34</v>
+        <v>3:24</v>
       </c>
       <c r="H15" t="str">
-        <v>Clinton Kane</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -986,10 +986,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:01</v>
+        <v>5:52</v>
       </c>
       <c r="H16" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B17" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1024,10 +1024,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:24</v>
+        <v>5:01</v>
       </c>
       <c r="H17" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B18" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1062,10 +1062,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:52</v>
+        <v>4:12</v>
       </c>
       <c r="H18" t="str">
-        <v>Harry Styles</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1100,10 +1100,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>5:01</v>
+        <v>3:59</v>
       </c>
       <c r="H19" t="str">
-        <v>Neal Francis</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B20" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1138,10 +1138,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:12</v>
+        <v>2:56</v>
       </c>
       <c r="H20" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1176,10 +1176,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:59</v>
+        <v>3:46</v>
       </c>
       <c r="H21" t="str">
-        <v>Holly Humberstone</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1214,10 +1214,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:56</v>
+        <v>4:37</v>
       </c>
       <c r="H22" t="str">
-        <v>Cliff Richard</v>
+        <v>Bella White</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1252,10 +1252,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:46</v>
+        <v>4:06</v>
       </c>
       <c r="H23" t="str">
-        <v>Jessie Ware</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1290,10 +1290,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:37</v>
+        <v>3:54</v>
       </c>
       <c r="H24" t="str">
-        <v>Bella White</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B25" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1328,10 +1328,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:06</v>
+        <v>4:10</v>
       </c>
       <c r="H25" t="str">
-        <v>Ryan Wright</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1366,10 +1366,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:54</v>
+        <v>3:26</v>
       </c>
       <c r="H26" t="str">
-        <v>Dove Cameron</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:10</v>
+        <v>2:56</v>
       </c>
       <c r="H27" t="str">
-        <v>Parker McCollum</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1442,10 +1442,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H28" t="str">
-        <v>Matt Hansen</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H29" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1518,10 +1518,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:56</v>
+        <v>3:05</v>
       </c>
       <c r="H30" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:01</v>
+        <v>2:27</v>
       </c>
       <c r="H31" t="str">
-        <v>Tauren Wells</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1594,10 +1594,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:05</v>
+        <v>2:34</v>
       </c>
       <c r="H32" t="str">
-        <v>Maiah Manser</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:27</v>
+        <v>3:13</v>
       </c>
       <c r="H33" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H34" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H35" t="str">
-        <v>Ashley Kutcher</v>
+        <v>CAIN</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:13</v>
+        <v>5:14</v>
       </c>
       <c r="H36" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:08</v>
+        <v>2:59</v>
       </c>
       <c r="H37" t="str">
-        <v>CAIN</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>5:14</v>
+        <v>4:21</v>
       </c>
       <c r="H38" t="str">
-        <v>Harry Styles</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:59</v>
+        <v>4:09</v>
       </c>
       <c r="H39" t="str">
-        <v>Lana Lubany</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:21</v>
+        <v>2:34</v>
       </c>
       <c r="H40" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:09</v>
+        <v>3:10</v>
       </c>
       <c r="H41" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:34</v>
+        <v>3:21</v>
       </c>
       <c r="H42" t="str">
-        <v>Lauren Sanderson</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:10</v>
+        <v>3:06</v>
       </c>
       <c r="H43" t="str">
-        <v>Olivia Dean</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2053,7 +2053,7 @@
         <v>3:21</v>
       </c>
       <c r="H44" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:06</v>
+        <v>7:21</v>
       </c>
       <c r="H45" t="str">
-        <v>The Avett Brothers</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H46" t="str">
-        <v>Jordana Bryant</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>7:21</v>
+        <v>3:45</v>
       </c>
       <c r="H47" t="str">
-        <v>Katy Perry</v>
+        <v>Tones And I</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:17</v>
+        <v>3:57</v>
       </c>
       <c r="H48" t="str">
-        <v>Lauren Watkins</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:45</v>
+        <v>3:03</v>
       </c>
       <c r="H49" t="str">
-        <v>Tones And I</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:57</v>
+        <v>4:27</v>
       </c>
       <c r="H50" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:03</v>
+        <v>4:34</v>
       </c>
       <c r="H51" t="str">
-        <v>Charlie Puth</v>
+        <v>Armik</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2354,10 +2354,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:27</v>
+        <v>2:54</v>
       </c>
       <c r="H52" t="str">
-        <v>Chappell Roan</v>
+        <v>LØLØ</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2392,10 +2392,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:34</v>
+        <v>3:25</v>
       </c>
       <c r="H53" t="str">
-        <v>Armik</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2430,10 +2430,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:54</v>
+        <v>2:01</v>
       </c>
       <c r="H54" t="str">
-        <v>LØLØ</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:25</v>
+        <v>2:25</v>
       </c>
       <c r="H55" t="str">
-        <v>Tenille Townes</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2506,10 +2506,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:01</v>
+        <v>1:14</v>
       </c>
       <c r="H56" t="str">
-        <v>Alan Walker</v>
+        <v>Labrinth</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B57" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2544,10 +2544,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:25</v>
+        <v>2:59</v>
       </c>
       <c r="H57" t="str">
-        <v>Charli xcx</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2582,10 +2582,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>1:14</v>
+        <v>2:29</v>
       </c>
       <c r="H58" t="str">
-        <v>Labrinth</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2620,10 +2620,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:59</v>
+        <v>2:34</v>
       </c>
       <c r="H59" t="str">
-        <v>Charlie Puth</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2658,10 +2658,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:29</v>
+        <v>3:48</v>
       </c>
       <c r="H60" t="str">
-        <v>Girl Tones</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B61" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2696,10 +2696,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:34</v>
+        <v>3:32</v>
       </c>
       <c r="H61" t="str">
-        <v>Jagwar Twin</v>
+        <v>The Beaches</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:48</v>
+        <v>3:49</v>
       </c>
       <c r="H62" t="str">
-        <v>Caroline Jones</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:32</v>
+        <v>4:28</v>
       </c>
       <c r="H63" t="str">
-        <v>The Beaches</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:49</v>
+        <v>3:37</v>
       </c>
       <c r="H64" t="str">
-        <v>Dolly Parton</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:28</v>
+        <v>3:35</v>
       </c>
       <c r="H65" t="str">
-        <v>Madison Beer</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:37</v>
+        <v>2:31</v>
       </c>
       <c r="H66" t="str">
-        <v>Ty Myers</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:35</v>
+        <v>3:21</v>
       </c>
       <c r="H67" t="str">
-        <v>Megan Moroney</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:31</v>
+        <v>5:24</v>
       </c>
       <c r="H68" t="str">
-        <v>Julia Cole Music</v>
+        <v>Nickless</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H69" t="str">
-        <v>Lily Allen</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>5:24</v>
+        <v>4:11</v>
       </c>
       <c r="H70" t="str">
-        <v>Nickless</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:11</v>
+        <v>3:31</v>
       </c>
       <c r="H71" t="str">
-        <v>Peach PRC</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:11</v>
+        <v>4:16</v>
       </c>
       <c r="H72" t="str">
-        <v>Ocean Alley</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:31</v>
+        <v>4:42</v>
       </c>
       <c r="H73" t="str">
-        <v>OneRepublic</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:16</v>
+        <v>2:47</v>
       </c>
       <c r="H74" t="str">
-        <v>Ty Myers</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:42</v>
+        <v>3:59</v>
       </c>
       <c r="H75" t="str">
-        <v>JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:47</v>
+        <v>4:09</v>
       </c>
       <c r="H76" t="str">
-        <v>Teo Glacier</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:59</v>
+        <v>3:24</v>
       </c>
       <c r="H77" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>ella jane</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:09</v>
+        <v>3:14</v>
       </c>
       <c r="H78" t="str">
-        <v>Louie TheSinger</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H79" t="str">
-        <v>ella jane</v>
+        <v>Kungs</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:14</v>
+        <v>3:15</v>
       </c>
       <c r="H80" t="str">
-        <v>Johnny Orlando</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:32</v>
+        <v>3:03</v>
       </c>
       <c r="H81" t="str">
-        <v>Kungs</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:15</v>
+        <v>3:04</v>
       </c>
       <c r="H82" t="str">
-        <v>Billy Raffoul</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:03</v>
+        <v>3:33</v>
       </c>
       <c r="H83" t="str">
-        <v>NathanEvanss</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:04</v>
+        <v>2:53</v>
       </c>
       <c r="H84" t="str">
-        <v>Stephen Sanchez</v>
+        <v>MAX</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:33</v>
+        <v>4:11</v>
       </c>
       <c r="H85" t="str">
-        <v>Bruno Mars</v>
+        <v>Jessie J</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:53</v>
+        <v>2:45</v>
       </c>
       <c r="H86" t="str">
-        <v>MAX</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:11</v>
+        <v>4:00</v>
       </c>
       <c r="H87" t="str">
-        <v>Jessie J</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:45</v>
+        <v>3:27</v>
       </c>
       <c r="H88" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:00</v>
+        <v>3:25</v>
       </c>
       <c r="H89" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:27</v>
+        <v>3:34</v>
       </c>
       <c r="H90" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:25</v>
+        <v>2:25</v>
       </c>
       <c r="H91" t="str">
-        <v>Olivia Dean</v>
+        <v>Joseph</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3874,7 +3874,7 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:34</v>
+        <v>3:26</v>
       </c>
       <c r="H92" t="str">
         <v>Demi Lovato</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:25</v>
+        <v>4:46</v>
       </c>
       <c r="H93" t="str">
-        <v>Joseph</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H94" t="str">
-        <v>Demi Lovato</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-29</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:46</v>
+        <v>2:52</v>
       </c>
       <c r="H95" t="str">
-        <v>Keith Urban</v>
+        <v>Madonna</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-29</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:24</v>
+        <v>2:06</v>
       </c>
       <c r="H96" t="str">
-        <v>Keith Urban</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-29</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:52</v>
+        <v>3:09</v>
       </c>
       <c r="H97" t="str">
-        <v>Madonna</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-29</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:06</v>
+        <v>5:11</v>
       </c>
       <c r="H98" t="str">
-        <v>Estás Tonné</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-29</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:09</v>
+        <v>3:40</v>
       </c>
       <c r="H99" t="str">
-        <v>Anna Graves</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-29</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:11</v>
+        <v>3:49</v>
       </c>
       <c r="H100" t="str">
-        <v>Ocean Alley</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-29</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:40</v>
+        <v>3:42</v>
       </c>
       <c r="H101" t="str">
-        <v>Zara Larsson</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>Distracted</v>
       </c>
       <c r="G102" t="str">
-        <v>3:49</v>
+        <v>2:30</v>
       </c>
       <c r="H102" t="str">
-        <v>Lauren Watkins</v>
+        <v>Thundercat</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L102" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Aperture</v>
       </c>
       <c r="B103" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>3 weeks ago</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G103" t="str">
-        <v>3:42</v>
+        <v>5:11</v>
       </c>
       <c r="H103" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L103" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Opening Night</v>
       </c>
       <c r="B104" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>3 weeks ago</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G104" t="str">
-        <v>5:11</v>
+        <v>4:19</v>
       </c>
       <c r="H104" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L104" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>For Hire</v>
       </c>
       <c r="B105" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>3 weeks ago</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:57</v>
+        <v>3:44</v>
       </c>
       <c r="H105" t="str">
-        <v>Lainey Wilson</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L105" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>I Did This To Myself</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Distracted</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G106" t="str">
-        <v>2:30</v>
+        <v>2:20</v>
       </c>
       <c r="H106" t="str">
-        <v>Thundercat</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L106" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Aperture</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>5:11</v>
+        <v>3:01</v>
       </c>
       <c r="H107" t="str">
-        <v>Harry Styles</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L107" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Opening Night</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>HELP(2)</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G108" t="str">
-        <v>4:19</v>
+        <v>2:29</v>
       </c>
       <c r="H108" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Joji</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L108" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>For Hire</v>
+        <v>High Key</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>For Hire - Single</v>
+        <v>Vacancy</v>
       </c>
       <c r="G109" t="str">
-        <v>3:44</v>
+        <v>2:12</v>
       </c>
       <c r="H109" t="str">
-        <v>People I’ve Met</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L109" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>scared</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Don't Be Dumb</v>
+        <v>scared - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>2:20</v>
+        <v>3:46</v>
       </c>
       <c r="H110" t="str">
-        <v>A$AP Rocky</v>
+        <v>Fred again..</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L110" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Death of Love</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G111" t="str">
-        <v>3:01</v>
+        <v>3:26</v>
       </c>
       <c r="H111" t="str">
-        <v>Luis Fonsi</v>
+        <v>James Blake</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L111" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Piss In The Wind</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G112" t="str">
-        <v>2:29</v>
+        <v>4:03</v>
       </c>
       <c r="H112" t="str">
-        <v>Joji</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L112" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>High Key</v>
+        <v>ATM</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/atm/1871258339</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Vacancy</v>
+        <v>OCTANE</v>
       </c>
       <c r="G113" t="str">
-        <v>2:12</v>
+        <v>3:00</v>
       </c>
       <c r="H113" t="str">
-        <v>Ari Lennox</v>
+        <v>Don Toliver</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/atm/1871258329</v>
       </c>
       <c r="L113" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>ATM - Don Toliver</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>scared</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>scared - Single</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:46</v>
+        <v>2:23</v>
       </c>
       <c r="H114" t="str">
-        <v>Fred again..</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L114" t="str">
-        <v>scared - Fred again..</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Death of Love</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Trying Times</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G115" t="str">
-        <v>3:26</v>
+        <v>2:46</v>
       </c>
       <c r="H115" t="str">
-        <v>James Blake</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L115" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Megadeth</v>
       </c>
       <c r="G116" t="str">
-        <v>4:03</v>
+        <v>4:40</v>
       </c>
       <c r="H116" t="str">
-        <v>Parker McCollum</v>
+        <v>Megadeth</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L116" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ATM</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>OCTANE</v>
+        <v>Cruel World</v>
       </c>
       <c r="G117" t="str">
-        <v>3:00</v>
+        <v>3:57</v>
       </c>
       <c r="H117" t="str">
-        <v>Don Toliver</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L117" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Flo Jackson</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:23</v>
+        <v>4:14</v>
       </c>
       <c r="H118" t="str">
-        <v>Flo Milli</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L118" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Creature of Habit</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G119" t="str">
-        <v>2:46</v>
+        <v>2:50</v>
       </c>
       <c r="H119" t="str">
-        <v>Courtney Barnett</v>
+        <v>XG</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L119" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Puppet Parade</v>
+        <v>Dead End</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Megadeth</v>
+        <v>Ricochet</v>
       </c>
       <c r="G120" t="str">
-        <v>4:40</v>
+        <v>4:05</v>
       </c>
       <c r="H120" t="str">
-        <v>Megadeth</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L120" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>To Love Somebody</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Cruel World</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:57</v>
+        <v>3:52</v>
       </c>
       <c r="H121" t="str">
-        <v>Holly Humberstone</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L121" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G122" t="str">
-        <v>4:14</v>
+        <v>3:02</v>
       </c>
       <c r="H122" t="str">
-        <v>Cleo Sol</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L122" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>HYPNOTIZE</v>
+        <v>BAD</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-29</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>THE CORE - 核</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:50</v>
+        <v>2:15</v>
       </c>
       <c r="H123" t="str">
-        <v>XG</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L123" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Dead End</v>
+        <v>Losing You</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-29</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ricochet</v>
+        <v>F.I.G</v>
       </c>
       <c r="G124" t="str">
-        <v>4:05</v>
+        <v>2:22</v>
       </c>
       <c r="H124" t="str">
-        <v>Snail Mail</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L124" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Arrhythmia (I Hope You Stay)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-29</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>Arrhythmia (I Hope You Stay) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Dove Cameron</v>
+        <v>The Runarounds</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
       </c>
       <c r="L125" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-29</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Infinito</v>
       </c>
       <c r="G126" t="str">
-        <v>3:02</v>
+        <v>2:14</v>
       </c>
       <c r="H126" t="str">
-        <v>Kenia Os</v>
+        <v>Yandel</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L126" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>BAD</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-29</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>BAD - Single</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G127" t="str">
-        <v>2:15</v>
+        <v>2:08</v>
       </c>
       <c r="H127" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L127" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Losing You</v>
+        <v>Turbulence</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-29</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>F.I.G</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G128" t="str">
-        <v>2:22</v>
+        <v>2:25</v>
       </c>
       <c r="H128" t="str">
-        <v>Naomi Scott</v>
+        <v>Wizkid</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L128" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Arrhythmia (I Hope You Stay)</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/arrhythmia-i-hope-you-stay/1867164656</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-29</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Arrhythmia (I Hope You Stay) - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:02</v>
+        <v>2:59</v>
       </c>
       <c r="H129" t="str">
-        <v>The Runarounds</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/the-runarounds/1660817420</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/arrhythmia-i-hope-you-stay/1867164652</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L129" t="str">
-        <v>Arrhythmia (I Hope You Stay) - The Runarounds</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-29</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Infinito</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:14</v>
+        <v>3:47</v>
       </c>
       <c r="H130" t="str">
-        <v>Yandel</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L130" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sexy For Me</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-29</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G131" t="str">
-        <v>2:08</v>
+        <v>2:53</v>
       </c>
       <c r="H131" t="str">
-        <v>Jason Derulo</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L131" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Turbulence</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-29</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>Act I</v>
       </c>
       <c r="G132" t="str">
-        <v>2:25</v>
+        <v>3:43</v>
       </c>
       <c r="H132" t="str">
-        <v>Wizkid</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L132" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Imposter</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-29</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G133" t="str">
-        <v>2:59</v>
+        <v>2:38</v>
       </c>
       <c r="H133" t="str">
-        <v>Jelly Roll</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L133" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-29</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:47</v>
+        <v>6:01</v>
       </c>
       <c r="H134" t="str">
-        <v>Dolly Parton</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L134" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-29</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:53</v>
+        <v>2:24</v>
       </c>
       <c r="H135" t="str">
-        <v>Oscar Ortiz</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L135" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-29</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Act I</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:43</v>
+        <v>3:41</v>
       </c>
       <c r="H136" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L136" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Imposter</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-29</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>How Did I Get Here?</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G137" t="str">
-        <v>2:38</v>
+        <v>3:12</v>
       </c>
       <c r="H137" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L137" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-29</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G138" t="str">
-        <v>6:01</v>
+        <v>3:27</v>
       </c>
       <c r="H138" t="str">
-        <v>Not for Radio</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L138" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Thick One</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-29</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>Part 3</v>
       </c>
       <c r="G139" t="str">
-        <v>2:24</v>
+        <v>2:49</v>
       </c>
       <c r="H139" t="str">
-        <v>GIRLSET</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L139" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>I Could Get Used To This</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-29</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G140" t="str">
-        <v>3:41</v>
+        <v>3:59</v>
       </c>
       <c r="H140" t="str">
-        <v>Jessie Ware</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L140" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>LA VILLA</v>
+        <v>THUM</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-29</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:12</v>
+        <v>2:11</v>
       </c>
       <c r="H141" t="str">
-        <v>Ryan Castro</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L141" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-29</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G142" t="str">
-        <v>3:27</v>
+        <v>3:32</v>
       </c>
       <c r="H142" t="str">
-        <v>Denzel Curry</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L142" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Thick One</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-29</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Part 3</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G143" t="str">
-        <v>2:49</v>
+        <v>3:04</v>
       </c>
       <c r="H143" t="str">
-        <v>42 Dugg</v>
+        <v>MIKA</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L143" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>3 Tears</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-29</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>World's Gone Wrong</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:59</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>Lucinda Williams</v>
+        <v>Mergui</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L144" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>THUM</v>
+        <v>Church Girl</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-29</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>THUM - Single</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:11</v>
+        <v>3:19</v>
       </c>
       <c r="H145" t="str">
-        <v>Violet Grohl</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L145" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>Funeral</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-29</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>The Great Satan</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G146" t="str">
-        <v>3:32</v>
+        <v>4:03</v>
       </c>
       <c r="H146" t="str">
-        <v>Rob Zombie</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L146" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Excuses For Love</v>
+        <v>dust to dust</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-29</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Hyperlove</v>
+        <v>Rivers of Sugar and Blood - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>3:04</v>
+        <v>3:51</v>
       </c>
       <c r="H147" t="str">
-        <v>MIKA</v>
+        <v>Truman Sinclair</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
       </c>
       <c r="L147" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>dust to dust - Truman Sinclair</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>3 Tears</v>
+        <v>Say Yes</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-29</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>3 Tears - Single</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G148" t="str">
         <v>2:50</v>
       </c>
       <c r="H148" t="str">
-        <v>Mergui</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L148" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Church Girl</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-29</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Church Girl - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G149" t="str">
-        <v>3:19</v>
+        <v>3:10</v>
       </c>
       <c r="H149" t="str">
-        <v>Carly Pearce</v>
+        <v>Camper</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L149" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Funeral</v>
+        <v>Ojalá</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-29</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>4:03</v>
+        <v>4:11</v>
       </c>
       <c r="H150" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lunay</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L150" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>dust to dust</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/dust-to-dust/1869117280</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-29</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Rivers of Sugar and Blood - EP</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:51</v>
+        <v>2:17</v>
       </c>
       <c r="H151" t="str">
-        <v>Truman Sinclair</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/truman-sinclair/1483104826</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/dust-to-dust/1869116937</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L151" t="str">
-        <v>dust to dust - Truman Sinclair</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Say Yes</v>
+        <v>Wallflower</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-29</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Say Yes - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:50</v>
+        <v>3:25</v>
       </c>
       <c r="H152" t="str">
-        <v>Marques Anthony</v>
+        <v>Sikarus</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L152" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>You Phase</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-29</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>CAMPILATION</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:10</v>
+        <v>2:51</v>
       </c>
       <c r="H153" t="str">
-        <v>Camper</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L153" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Ojalá</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-29</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Ojalá - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:11</v>
+        <v>2:40</v>
       </c>
       <c r="H154" t="str">
-        <v>Lunay</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/lunay/938127685</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L154" t="str">
-        <v>Ojalá - Lunay</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-29</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G155" t="str">
-        <v>2:17</v>
+        <v>5:47</v>
       </c>
       <c r="H155" t="str">
-        <v>Ledbyher</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L155" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Wallflower</v>
+        <v>go again</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-29</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Wallflower - Single</v>
+        <v>go again - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:25</v>
+        <v>2:07</v>
       </c>
       <c r="H156" t="str">
-        <v>Sikarus</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L156" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>You Phase</v>
+        <v>Autopilot</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-29</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>You Phase - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G157" t="str">
-        <v>2:51</v>
+        <v>2:46</v>
       </c>
       <c r="H157" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L157" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Miss Independent</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-29</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Miss Independent - Single</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:40</v>
+        <v>3:04</v>
       </c>
       <c r="H158" t="str">
-        <v>1Ski OG</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L158" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>In Violet</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-29</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G159" t="str">
-        <v>5:47</v>
+        <v>4:09</v>
       </c>
       <c r="H159" t="str">
-        <v>Elevation Worship</v>
+        <v>Searows</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L159" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>go again</v>
+        <v>Baby Run</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-29</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>go again - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:07</v>
+        <v>4:47</v>
       </c>
       <c r="H160" t="str">
-        <v>NateTaylorr</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L160" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Autopilot</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-29</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Autopilot</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:46</v>
+        <v>3:06</v>
       </c>
       <c r="H161" t="str">
-        <v>ALEXSUCKS</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L161" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-29</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:04</v>
+        <v>2:58</v>
       </c>
       <c r="H162" t="str">
-        <v>SPELLLING</v>
+        <v>Juanes</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L162" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>In Violet</v>
+        <v>World Change Me</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-29</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:09</v>
+        <v>3:03</v>
       </c>
       <c r="H163" t="str">
-        <v>Searows</v>
+        <v>Max McNown</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L163" t="str">
-        <v>In Violet - Searows</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Baby Run</v>
+        <v>Exclusive</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-29</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Baby Run - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>4:47</v>
+        <v>3:20</v>
       </c>
       <c r="H164" t="str">
-        <v>Jimi Jules</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L164" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>What If We Don't</v>
+        <v>Say Less</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-29</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:06</v>
+        <v>2:18</v>
       </c>
       <c r="H165" t="str">
-        <v>Ashley McBryde</v>
+        <v>JYT</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L165" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Hagamos Que</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-29</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G166" t="str">
-        <v>2:58</v>
+        <v>3:52</v>
       </c>
       <c r="H166" t="str">
-        <v>Juanes</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L166" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>World Change Me</v>
+        <v>Over You</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-29</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>World Change Me - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G167" t="str">
-        <v>3:03</v>
+        <v>4:44</v>
       </c>
       <c r="H167" t="str">
-        <v>Max McNown</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L167" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Exclusive</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-29</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Exclusive - EP</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:20</v>
+        <v>2:42</v>
       </c>
       <c r="H168" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L168" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Say Less</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-29</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Say Less - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:18</v>
+        <v>3:06</v>
       </c>
       <c r="H169" t="str">
-        <v>JYT</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L169" t="str">
-        <v>Say Less - JYT</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Angels Cry</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-29</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:52</v>
+        <v>2:48</v>
       </c>
       <c r="H170" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>David Guetta</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L170" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Over You</v>
+        <v>Rejoice</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-29</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>A Love For Strangers</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>4:44</v>
+        <v>4:20</v>
       </c>
       <c r="H171" t="str">
-        <v>Chet Faker</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L171" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-29</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:42</v>
+        <v>2:58</v>
       </c>
       <c r="H172" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L172" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Odisea</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-29</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:06</v>
+        <v>3:56</v>
       </c>
       <c r="H173" t="str">
-        <v>Disco Lines</v>
+        <v>BASSYY</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L173" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-29</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G174" t="str">
-        <v>2:48</v>
+        <v>3:13</v>
       </c>
       <c r="H174" t="str">
-        <v>David Guetta</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L174" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rejoice</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-29</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Rejoice - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:20</v>
+        <v>4:00</v>
       </c>
       <c r="H175" t="str">
-        <v>Def Leppard</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L175" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Easy</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-29</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:58</v>
+        <v>4:30</v>
       </c>
       <c r="H176" t="str">
-        <v>Honey Dijon</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L176" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Odisea</v>
+        <v>Break Me In</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/odisea/1866927906</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-29</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Odisea - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:56</v>
+        <v>2:52</v>
       </c>
       <c r="H177" t="str">
-        <v>BASSYY</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/odisea/1866927904</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L177" t="str">
-        <v>Odisea - BASSYY</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Lucky Day</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-29</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Speed Kills</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:13</v>
+        <v>2:36</v>
       </c>
       <c r="H178" t="str">
-        <v>Ally Evenson</v>
+        <v>Sugar</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L178" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Breathe On It</v>
+        <v>Depressed</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-29</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G179" t="str">
-        <v>4:00</v>
+        <v>3:32</v>
       </c>
       <c r="H179" t="str">
-        <v>Tauren Wells</v>
+        <v>The Format</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L179" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Easy</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-29</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Easy - Single</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G180" t="str">
-        <v>4:30</v>
+        <v>3:09</v>
       </c>
       <c r="H180" t="str">
-        <v>lydi lynn</v>
+        <v>Poppy</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L180" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Break Me In</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-29</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Break Me In - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G181" t="str">
-        <v>2:52</v>
+        <v>3:45</v>
       </c>
       <c r="H181" t="str">
-        <v>Joyce Wrice</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L181" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Long Live Love</v>
+        <v>Angela</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-29</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:36</v>
+        <v>3:32</v>
       </c>
       <c r="H182" t="str">
-        <v>Sugar</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L182" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Depressed</v>
+        <v>Disappear</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-29</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Boycott Heaven</v>
+        <v>Greyhound</v>
       </c>
       <c r="G183" t="str">
-        <v>3:32</v>
+        <v>3:31</v>
       </c>
       <c r="H183" t="str">
-        <v>The Format</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L183" t="str">
-        <v>Depressed - The Format</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Empty Hands</v>
+        <v>Catapult</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-29</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Empty Hands</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H184" t="str">
-        <v>Poppy</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L184" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>The Long Surrender</v>
+        <v>Think Twice</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-29</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>The Long Surrender</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:45</v>
+        <v>2:22</v>
       </c>
       <c r="H185" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L185" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Angela</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-29</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Angela - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G186" t="str">
-        <v>3:32</v>
+        <v>3:33</v>
       </c>
       <c r="H186" t="str">
-        <v>Hayden Everett</v>
+        <v>Agnes</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L186" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Disappear</v>
+        <v>Down South</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-29</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Greyhound</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:31</v>
+        <v>2:19</v>
       </c>
       <c r="H187" t="str">
-        <v>Katie Tupper</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L187" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Catapult</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-29</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Catapult - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:57</v>
+        <v>2:16</v>
       </c>
       <c r="H188" t="str">
-        <v>Cape Francis</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L188" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Think Twice</v>
+        <v>Love Like This</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-29</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Think Twice - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:22</v>
+        <v>3:30</v>
       </c>
       <c r="H189" t="str">
-        <v>Leonie Biney</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L189" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>LOVESONGS</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D190" t="str">
         <v>2026-01-29</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>La Locura, Vol. 1</v>
       </c>
       <c r="G190" t="str">
-        <v>3:33</v>
+        <v>3:10</v>
       </c>
       <c r="H190" t="str">
-        <v>Agnes</v>
+        <v>Funky</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L190" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Down South</v>
+        <v>double edged sword</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D191" t="str">
         <v>2026-01-29</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Down South - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:19</v>
+        <v>3:28</v>
       </c>
       <c r="H191" t="str">
-        <v>Trap Dickey</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L191" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D192" t="str">
         <v>2026-01-29</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:16</v>
+        <v>3:27</v>
       </c>
       <c r="H192" t="str">
-        <v>SALIMATA</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L192" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Love Like This</v>
+        <v>The Decay</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D193" t="str">
         <v>2026-01-29</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Love Like This - Single</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G193" t="str">
-        <v>3:30</v>
+        <v>3:20</v>
       </c>
       <c r="H193" t="str">
-        <v>Jacob Banks</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L193" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plan Plan</v>
+        <v>3111</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D194" t="str">
         <v>2026-01-29</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>La Locura, Vol. 1</v>
+        <v>Goliath</v>
       </c>
       <c r="G194" t="str">
-        <v>3:10</v>
+        <v>4:08</v>
       </c>
       <c r="H194" t="str">
-        <v>Funky</v>
+        <v>Exodus</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L194" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>double edged sword</v>
+        <v>Touch My Love And Die</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D195" t="str">
         <v>2026-01-29</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>double edged sword - Single</v>
+        <v>Touch My Love And Die - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:28</v>
+        <v>2:57</v>
       </c>
       <c r="H195" t="str">
-        <v>Hailey Picardi</v>
+        <v>Myrkur</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
       </c>
       <c r="L195" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Touch My Love And Die - Myrkur</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>Bomb To A Knife Fight</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D196" t="str">
         <v>2026-01-29</v>
@@ -7823,182 +7823,30 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>Bomb To A Knife Fight - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:27</v>
+        <v>2:41</v>
       </c>
       <c r="H196" t="str">
-        <v>Matt Hansen</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
       <c r="L196" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>The Decay</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>What Remains (Midnight Edition)</v>
-      </c>
-      <c r="G197" t="str">
-        <v>3:20</v>
-      </c>
-      <c r="H197" t="str">
-        <v>Pop Evil</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
-      </c>
-      <c r="L197" t="str">
-        <v>The Decay - Pop Evil</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>3111</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>Goliath</v>
-      </c>
-      <c r="G198" t="str">
-        <v>4:08</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Exodus</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
-      </c>
-      <c r="L198" t="str">
-        <v>3111 - Exodus</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Touch My Love And Die</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Touch My Love And Die - Single</v>
-      </c>
-      <c r="G199" t="str">
-        <v>2:57</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Myrkur</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Bomb To A Knife Fight</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Bomb To A Knife Fight - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>2:41</v>
-      </c>
-      <c r="H200" t="str">
-        <v>The Barbarians of California</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
-      </c>
-      <c r="L200" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B2" t="str">
         <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -454,10 +454,10 @@
         <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H2" t="str">
-        <v>Teddy Swims</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B3" t="str">
         <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -492,10 +492,10 @@
         <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:14</v>
+        <v>3:16</v>
       </c>
       <c r="H3" t="str">
-        <v>Beck</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H4" t="str">
-        <v>The Offspring</v>
+        <v>Beck</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:10</v>
+        <v>2:57</v>
       </c>
       <c r="H5" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:10</v>
+        <v>4:10</v>
       </c>
       <c r="H6" t="str">
-        <v>Jason Derulo</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:52</v>
+        <v>2:10</v>
       </c>
       <c r="H7" t="str">
-        <v>lights</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H8" t="str">
-        <v>Telenova</v>
+        <v>lights</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>When I Did "How Music Works" LIVE To 1500 People</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>5:32</v>
+        <v>3:50</v>
       </c>
       <c r="H9" t="str">
-        <v>Marcin</v>
+        <v>Telenova</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>When I Did "How Music Works" LIVE To 1500 People - Marcin</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>When I Did "How Music Works" LIVE To 1500 People</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:27</v>
+        <v>5:32</v>
       </c>
       <c r="H10" t="str">
-        <v>We Three</v>
+        <v>Marcin</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>When I Did "How Music Works" LIVE To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H11" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H12" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H13" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H14" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -948,10 +948,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H15" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B16" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -986,10 +986,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H16" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B17" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1024,10 +1024,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H17" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B18" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1062,10 +1062,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H18" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1100,10 +1100,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H19" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1138,10 +1138,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H20" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B21" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1176,10 +1176,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H21" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1214,10 +1214,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:37</v>
+        <v>3:46</v>
       </c>
       <c r="H22" t="str">
-        <v>Bella White</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B23" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1252,10 +1252,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H23" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1290,10 +1290,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H24" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1328,10 +1328,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H25" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B26" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1366,10 +1366,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H26" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H27" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>2:56</v>
       </c>
       <c r="H28" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1480,10 +1480,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H29" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1518,10 +1518,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H30" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H31" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1594,10 +1594,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H32" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H33" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1673,7 +1673,7 @@
         <v>3:13</v>
       </c>
       <c r="H34" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H35" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H36" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H37" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1822,10 +1822,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H38" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H39" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1898,10 +1898,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H40" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H41" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B42" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1974,10 +1974,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H42" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B43" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2012,10 +2012,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H43" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B44" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2050,10 +2050,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H44" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B45" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2088,10 +2088,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H45" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H46" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B47" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H47" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B48" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2202,10 +2202,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H48" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H49" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H50" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B51" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2316,10 +2316,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H51" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B52" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2354,10 +2354,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H52" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2392,10 +2392,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H53" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2430,10 +2430,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H54" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2468,10 +2468,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H55" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2506,10 +2506,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H56" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2544,10 +2544,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H57" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B58" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2582,10 +2582,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H58" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2620,10 +2620,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H59" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2658,10 +2658,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H60" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2696,10 +2696,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H61" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H62" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H63" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H64" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H65" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H66" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H67" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H68" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H69" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:11</v>
+        <v>3:11</v>
       </c>
       <c r="H70" t="str">
-        <v>Ocean Alley</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:31</v>
+        <v>4:11</v>
       </c>
       <c r="H71" t="str">
-        <v>OneRepublic</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="H72" t="str">
-        <v>Ty Myers</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:42</v>
+        <v>4:16</v>
       </c>
       <c r="H73" t="str">
-        <v>JavaJazzFest</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:47</v>
+        <v>4:42</v>
       </c>
       <c r="H74" t="str">
-        <v>Teo Glacier</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:59</v>
+        <v>2:47</v>
       </c>
       <c r="H75" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:09</v>
+        <v>3:59</v>
       </c>
       <c r="H76" t="str">
-        <v>Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="H77" t="str">
-        <v>ella jane</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H78" t="str">
-        <v>Johnny Orlando</v>
+        <v>ella jane</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="H79" t="str">
-        <v>Kungs</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:15</v>
+        <v>3:32</v>
       </c>
       <c r="H80" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kungs</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:03</v>
+        <v>3:15</v>
       </c>
       <c r="H81" t="str">
-        <v>NathanEvanss</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H82" t="str">
-        <v>Stephen Sanchez</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:33</v>
+        <v>3:04</v>
       </c>
       <c r="H83" t="str">
-        <v>Bruno Mars</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="H84" t="str">
-        <v>MAX</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:11</v>
+        <v>2:53</v>
       </c>
       <c r="H85" t="str">
-        <v>Jessie J</v>
+        <v>MAX</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:45</v>
+        <v>4:11</v>
       </c>
       <c r="H86" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jessie J</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:00</v>
+        <v>2:45</v>
       </c>
       <c r="H87" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:27</v>
+        <v>4:00</v>
       </c>
       <c r="H88" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H89" t="str">
-        <v>Olivia Dean</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:34</v>
+        <v>3:25</v>
       </c>
       <c r="H90" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:25</v>
+        <v>3:34</v>
       </c>
       <c r="H91" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:26</v>
+        <v>2:25</v>
       </c>
       <c r="H92" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:46</v>
+        <v>3:26</v>
       </c>
       <c r="H93" t="str">
-        <v>Keith Urban</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3950,7 +3950,7 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:24</v>
+        <v>4:46</v>
       </c>
       <c r="H94" t="str">
         <v>Keith Urban</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-29</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H95" t="str">
-        <v>Madonna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-29</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:06</v>
+        <v>2:52</v>
       </c>
       <c r="H96" t="str">
-        <v>Estás Tonné</v>
+        <v>Madonna</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-29</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:09</v>
+        <v>2:06</v>
       </c>
       <c r="H97" t="str">
-        <v>Anna Graves</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-29</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>5:11</v>
+        <v>3:09</v>
       </c>
       <c r="H98" t="str">
-        <v>Ocean Alley</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-29</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:40</v>
+        <v>5:11</v>
       </c>
       <c r="H99" t="str">
-        <v>Zara Larsson</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-29</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:49</v>
+        <v>3:40</v>
       </c>
       <c r="H100" t="str">
-        <v>Lauren Watkins</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-29</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:42</v>
+        <v>3:49</v>
       </c>
       <c r="H101" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="102">

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:05</v>
@@ -477,7 +477,7 @@
         <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:16</v>
@@ -515,7 +515,7 @@
         <v>Beck - Love (Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:14</v>
@@ -857,7 +857,7 @@
         <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:20</v>

--- a/data/global/2026-01-week05/titles.xlsx
+++ b/data/global/2026-01-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L210"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24412&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-29</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>22:45</v>
       </c>
       <c r="G2" t="str">
-        <v>4:05</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Demi Lovato</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>שלמה גרוניך - תודה אהבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>חנן בן ארי - לא המשוגע היחידי</v>
       </c>
       <c r="B3" t="str">
-        <v>5 hours ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24440&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-29</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 hours ago</v>
+        <v>15:38</v>
       </c>
       <c r="G3" t="str">
-        <v>3:16</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Teddy Swims</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>חנן בן ארי - לא המשוגע היחידי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
       <c r="B4" t="str">
-        <v>6 hours ago</v>
+        <v>2026-01-21</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-29</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 hours ago</v>
+        <v>11:10</v>
       </c>
       <c r="G4" t="str">
-        <v>3:14</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Beck</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
+        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-17</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24316&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-29</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>11:47</v>
       </c>
       <c r="G5" t="str">
-        <v>2:57</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>The Offspring</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
+        <v>חנן בן ארי - לייב מופע הינדיקים 2024</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>תומר יוסף - 360</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-14</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24437&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-29</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>08:40</v>
       </c>
       <c r="G6" t="str">
-        <v>4:10</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>תומר יוסף - 360</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-01</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24435&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-29</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>22:40</v>
       </c>
       <c r="G7" t="str">
-        <v>2:10</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Jason Derulo</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>מחפש את השיר-היכן אהובי-של דורית ולהקת אז אולי-אבל נקי ללא רעשים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2025-12-31</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24398&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-29</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>02:17</v>
       </c>
       <c r="G8" t="str">
-        <v>3:52</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>lights</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>עמיר בניון - לא נוגע בקרקע</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>אברהם טל - חי</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2025-12-31</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24399&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-29</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>02:16</v>
       </c>
       <c r="G9" t="str">
-        <v>3:50</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Telenova</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>אברהם טל - חי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>When I Did "How Music Works" LIVE To 1500 People</v>
+        <v>פיטר רוט - 50</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2025-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-29</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>02:13</v>
       </c>
       <c r="G10" t="str">
-        <v>5:32</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Marcin</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>When I Did "How Music Works" LIVE To 1500 People - Marcin</v>
+        <v>פיטר רוט - 50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2025-12-31</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-29</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>02:11</v>
       </c>
       <c r="G11" t="str">
-        <v>4:27</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>We Three</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>אגם בוחבוט - עשרים ואחת</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>2025-12-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-29</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>02:09</v>
       </c>
       <c r="G12" t="str">
-        <v>3:01</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>Timebelle Official</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>רבקה זוהר - רסיסים של אור</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>2025-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24410&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-29</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>02:06</v>
       </c>
       <c r="G13" t="str">
-        <v>3:20</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>חוה אלברשטיין - חמישה שירים</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>2025-12-31</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24409&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-29</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>02:05</v>
       </c>
       <c r="G14" t="str">
-        <v>3:34</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>Clinton Kane</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>הפרויקט של עידן רייכל - עד סוף העולם</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>סטטיק - קעקועים</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>2025-12-31</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24419&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-29</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>02:03</v>
       </c>
       <c r="G15" t="str">
-        <v>4:01</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>סטטיק - קעקועים</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-29</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:24</v>
+        <v>4:05</v>
       </c>
       <c r="H16" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-29</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G17" t="str">
-        <v>5:52</v>
+        <v>3:16</v>
       </c>
       <c r="H17" t="str">
-        <v>Harry Styles</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-29</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G18" t="str">
-        <v>5:01</v>
+        <v>3:14</v>
       </c>
       <c r="H18" t="str">
-        <v>Neal Francis</v>
+        <v>Beck</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-29</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:12</v>
+        <v>2:57</v>
       </c>
       <c r="H19" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>The Offspring</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-29</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:59</v>
+        <v>4:10</v>
       </c>
       <c r="H20" t="str">
-        <v>Holly Humberstone</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-29</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:56</v>
+        <v>2:10</v>
       </c>
       <c r="H21" t="str">
-        <v>Cliff Richard</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-29</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:46</v>
+        <v>3:52</v>
       </c>
       <c r="H22" t="str">
-        <v>Jessie Ware</v>
+        <v>lights</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-29</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:37</v>
+        <v>3:50</v>
       </c>
       <c r="H23" t="str">
-        <v>Bella White</v>
+        <v>Telenova</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>When I Did "How Music Works" LIVE To 1500 People</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-29</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:06</v>
+        <v>5:32</v>
       </c>
       <c r="H24" t="str">
-        <v>Ryan Wright</v>
+        <v>Marcin</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>When I Did "How Music Works" LIVE To 1500 People - Marcin</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-29</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:54</v>
+        <v>4:27</v>
       </c>
       <c r="H25" t="str">
-        <v>Dove Cameron</v>
+        <v>We Three</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-29</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:10</v>
+        <v>3:01</v>
       </c>
       <c r="H26" t="str">
-        <v>Parker McCollum</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-29</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:26</v>
+        <v>3:20</v>
       </c>
       <c r="H27" t="str">
-        <v>Matt Hansen</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-29</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:56</v>
+        <v>3:34</v>
       </c>
       <c r="H28" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-29</v>
@@ -1480,10 +1480,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H29" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-29</v>
@@ -1518,10 +1518,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:01</v>
+        <v>3:24</v>
       </c>
       <c r="H30" t="str">
-        <v>Tauren Wells</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-29</v>
@@ -1556,10 +1556,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:05</v>
+        <v>5:52</v>
       </c>
       <c r="H31" t="str">
-        <v>Maiah Manser</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B32" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-29</v>
@@ -1594,10 +1594,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:27</v>
+        <v>5:01</v>
       </c>
       <c r="H32" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992</v>
       </c>
       <c r="B33" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-29</v>
@@ -1632,10 +1632,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:34</v>
+        <v>4:12</v>
       </c>
       <c r="H33" t="str">
-        <v>Chelsea Cutler</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Extreme Perform More Than Words &amp; Hole Hearted | Brit Awards 1992 - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-29</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:13</v>
+        <v>3:59</v>
       </c>
       <c r="H34" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-29</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H35" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-29</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:08</v>
+        <v>3:46</v>
       </c>
       <c r="H36" t="str">
-        <v>CAIN</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-29</v>
@@ -1784,10 +1784,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>5:14</v>
+        <v>4:37</v>
       </c>
       <c r="H37" t="str">
-        <v>Harry Styles</v>
+        <v>Bella White</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-29</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:59</v>
+        <v>4:06</v>
       </c>
       <c r="H38" t="str">
-        <v>Lana Lubany</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-29</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:21</v>
+        <v>3:54</v>
       </c>
       <c r="H39" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-29</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:09</v>
+        <v>4:10</v>
       </c>
       <c r="H40" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-29</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:34</v>
+        <v>3:26</v>
       </c>
       <c r="H41" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-29</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:10</v>
+        <v>2:56</v>
       </c>
       <c r="H42" t="str">
-        <v>Olivia Dean</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-29</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H43" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-29</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:06</v>
+        <v>4:01</v>
       </c>
       <c r="H44" t="str">
-        <v>The Avett Brothers</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-29</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:21</v>
+        <v>3:05</v>
       </c>
       <c r="H45" t="str">
-        <v>Jordana Bryant</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-29</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>7:21</v>
+        <v>2:27</v>
       </c>
       <c r="H46" t="str">
-        <v>Katy Perry</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-29</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="H47" t="str">
-        <v>Lauren Watkins</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-29</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:45</v>
+        <v>3:13</v>
       </c>
       <c r="H48" t="str">
-        <v>Tones And I</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-29</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:57</v>
+        <v>3:13</v>
       </c>
       <c r="H49" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-29</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:03</v>
+        <v>3:08</v>
       </c>
       <c r="H50" t="str">
-        <v>Charlie Puth</v>
+        <v>CAIN</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-29</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:27</v>
+        <v>5:14</v>
       </c>
       <c r="H51" t="str">
-        <v>Chappell Roan</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-29</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:34</v>
+        <v>2:59</v>
       </c>
       <c r="H52" t="str">
-        <v>Armik</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-29</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:54</v>
+        <v>4:21</v>
       </c>
       <c r="H53" t="str">
-        <v>LØLØ</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-29</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H54" t="str">
-        <v>Tenille Townes</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-29</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:01</v>
+        <v>2:34</v>
       </c>
       <c r="H55" t="str">
-        <v>Alan Walker</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-29</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:25</v>
+        <v>3:10</v>
       </c>
       <c r="H56" t="str">
-        <v>Charli xcx</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-29</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>1:14</v>
+        <v>3:21</v>
       </c>
       <c r="H57" t="str">
-        <v>Labrinth</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-29</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H58" t="str">
-        <v>Charlie Puth</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-29</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:29</v>
+        <v>3:21</v>
       </c>
       <c r="H59" t="str">
-        <v>Girl Tones</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-29</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:34</v>
+        <v>7:21</v>
       </c>
       <c r="H60" t="str">
-        <v>Jagwar Twin</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-29</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:48</v>
+        <v>3:17</v>
       </c>
       <c r="H61" t="str">
-        <v>Caroline Jones</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-29</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:32</v>
+        <v>3:45</v>
       </c>
       <c r="H62" t="str">
-        <v>The Beaches</v>
+        <v>Tones And I</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-29</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:49</v>
+        <v>3:57</v>
       </c>
       <c r="H63" t="str">
-        <v>Dolly Parton</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-29</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:28</v>
+        <v>3:03</v>
       </c>
       <c r="H64" t="str">
-        <v>Madison Beer</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-29</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:37</v>
+        <v>4:27</v>
       </c>
       <c r="H65" t="str">
-        <v>Ty Myers</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-29</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:35</v>
+        <v>4:34</v>
       </c>
       <c r="H66" t="str">
-        <v>Megan Moroney</v>
+        <v>Armik</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-29</v>
@@ -2924,10 +2924,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:31</v>
+        <v>2:54</v>
       </c>
       <c r="H67" t="str">
-        <v>Julia Cole Music</v>
+        <v>LØLØ</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-29</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:21</v>
+        <v>3:25</v>
       </c>
       <c r="H68" t="str">
-        <v>Lily Allen</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-29</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>5:24</v>
+        <v>2:01</v>
       </c>
       <c r="H69" t="str">
-        <v>Nickless</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-29</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:11</v>
+        <v>2:25</v>
       </c>
       <c r="H70" t="str">
-        <v>Peach PRC</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-29</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:11</v>
+        <v>1:14</v>
       </c>
       <c r="H71" t="str">
-        <v>Ocean Alley</v>
+        <v>Labrinth</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-29</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:31</v>
+        <v>2:59</v>
       </c>
       <c r="H72" t="str">
-        <v>OneRepublic</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-29</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:16</v>
+        <v>2:29</v>
       </c>
       <c r="H73" t="str">
-        <v>Ty Myers</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-29</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:42</v>
+        <v>2:34</v>
       </c>
       <c r="H74" t="str">
-        <v>JavaJazzFest</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-29</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:47</v>
+        <v>3:48</v>
       </c>
       <c r="H75" t="str">
-        <v>Teo Glacier</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-29</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:59</v>
+        <v>3:32</v>
       </c>
       <c r="H76" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>The Beaches</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-29</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:09</v>
+        <v>3:49</v>
       </c>
       <c r="H77" t="str">
-        <v>Louie TheSinger</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-29</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:24</v>
+        <v>4:28</v>
       </c>
       <c r="H78" t="str">
-        <v>ella jane</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-29</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:14</v>
+        <v>3:37</v>
       </c>
       <c r="H79" t="str">
-        <v>Johnny Orlando</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-29</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:32</v>
+        <v>3:35</v>
       </c>
       <c r="H80" t="str">
-        <v>Kungs</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-29</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:15</v>
+        <v>2:31</v>
       </c>
       <c r="H81" t="str">
-        <v>Billy Raffoul</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-29</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H82" t="str">
-        <v>NathanEvanss</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-29</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:04</v>
+        <v>5:24</v>
       </c>
       <c r="H83" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Nickless</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-29</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:33</v>
+        <v>3:11</v>
       </c>
       <c r="H84" t="str">
-        <v>Bruno Mars</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-29</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:53</v>
+        <v>4:11</v>
       </c>
       <c r="H85" t="str">
-        <v>MAX</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-29</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:11</v>
+        <v>3:31</v>
       </c>
       <c r="H86" t="str">
-        <v>Jessie J</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-29</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:45</v>
+        <v>4:16</v>
       </c>
       <c r="H87" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-29</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:00</v>
+        <v>4:42</v>
       </c>
       <c r="H88" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-29</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:27</v>
+        <v>2:47</v>
       </c>
       <c r="H89" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-29</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:25</v>
+        <v>3:59</v>
       </c>
       <c r="H90" t="str">
-        <v>Olivia Dean</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-29</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:34</v>
+        <v>4:09</v>
       </c>
       <c r="H91" t="str">
-        <v>Demi Lovato</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-29</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:25</v>
+        <v>3:24</v>
       </c>
       <c r="H92" t="str">
-        <v>Joseph</v>
+        <v>ella jane</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-29</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H93" t="str">
-        <v>Demi Lovato</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-29</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:46</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Keith Urban</v>
+        <v>Kungs</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-29</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H95" t="str">
-        <v>Keith Urban</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-29</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:52</v>
+        <v>3:03</v>
       </c>
       <c r="H96" t="str">
-        <v>Madonna</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-29</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:06</v>
+        <v>3:04</v>
       </c>
       <c r="H97" t="str">
-        <v>Estás Tonné</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-29</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:09</v>
+        <v>3:33</v>
       </c>
       <c r="H98" t="str">
-        <v>Anna Graves</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-29</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>5:11</v>
+        <v>2:53</v>
       </c>
       <c r="H99" t="str">
-        <v>Ocean Alley</v>
+        <v>MAX</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-29</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:40</v>
+        <v>4:11</v>
       </c>
       <c r="H100" t="str">
-        <v>Zara Larsson</v>
+        <v>Jessie J</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-29</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:49</v>
+        <v>2:45</v>
       </c>
       <c r="H101" t="str">
-        <v>Lauren Watkins</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>I Did This To Myself</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-29</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Distracted</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:30</v>
+        <v>4:00</v>
       </c>
       <c r="H102" t="str">
-        <v>Thundercat</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>I Did This To Myself - Thundercat</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Aperture</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-29</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>5:11</v>
+        <v>3:27</v>
       </c>
       <c r="H103" t="str">
-        <v>Harry Styles</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Opening Night</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-29</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>HELP(2)</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>4:19</v>
+        <v>3:25</v>
       </c>
       <c r="H104" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>For Hire</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-29</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>For Hire - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:44</v>
+        <v>3:34</v>
       </c>
       <c r="H105" t="str">
-        <v>People I’ve Met</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>For Hire - People I’ve Met</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-29</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Don't Be Dumb</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:20</v>
+        <v>2:25</v>
       </c>
       <c r="H106" t="str">
-        <v>A$AP Rocky</v>
+        <v>Joseph</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-29</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:01</v>
+        <v>3:26</v>
       </c>
       <c r="H107" t="str">
-        <v>Luis Fonsi</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-29</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Piss In The Wind</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:29</v>
+        <v>4:46</v>
       </c>
       <c r="H108" t="str">
-        <v>Joji</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>High Key</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-29</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Vacancy</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G109" t="str">
-        <v>2:12</v>
+        <v>3:24</v>
       </c>
       <c r="H109" t="str">
-        <v>Ari Lennox</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>scared</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-29</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>scared - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:46</v>
+        <v>2:52</v>
       </c>
       <c r="H110" t="str">
-        <v>Fred again..</v>
+        <v>Madonna</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>scared - Fred again..</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Death of Love</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-29</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Trying Times</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:26</v>
+        <v>2:06</v>
       </c>
       <c r="H111" t="str">
-        <v>James Blake</v>
+        <v>Estás Tonné</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estás Tonné</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-29</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G112" t="str">
-        <v>4:03</v>
+        <v>3:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Parker McCollum</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ATM</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/atm/1871258339</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-29</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>OCTANE</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G113" t="str">
-        <v>3:00</v>
+        <v>5:11</v>
       </c>
       <c r="H113" t="str">
-        <v>Don Toliver</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/don-toliver/1237012992</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/atm/1871258329</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>ATM - Don Toliver</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Flo Jackson</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-29</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G114" t="str">
-        <v>2:23</v>
+        <v>3:40</v>
       </c>
       <c r="H114" t="str">
-        <v>Flo Milli</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-29</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Creature of Habit</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G115" t="str">
-        <v>2:46</v>
+        <v>3:49</v>
       </c>
       <c r="H115" t="str">
-        <v>Courtney Barnett</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Puppet Parade</v>
+        <v>I Did This To Myself</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/i-did-this-to-myself/1861531672</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-29</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Megadeth</v>
+        <v>Distracted</v>
       </c>
       <c r="G116" t="str">
-        <v>4:40</v>
+        <v>2:30</v>
       </c>
       <c r="H116" t="str">
-        <v>Megadeth</v>
+        <v>Thundercat</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/i-did-this-to-myself/1861531667</v>
       </c>
       <c r="L116" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>I Did This To Myself - Thundercat</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>To Love Somebody</v>
+        <v>Aperture</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-29</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Cruel World</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G117" t="str">
-        <v>3:57</v>
+        <v>5:11</v>
       </c>
       <c r="H117" t="str">
-        <v>Holly Humberstone</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L117" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>Opening Night</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-29</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G118" t="str">
-        <v>4:14</v>
+        <v>4:19</v>
       </c>
       <c r="H118" t="str">
-        <v>Cleo Sol</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L118" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>HYPNOTIZE</v>
+        <v>For Hire</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/for-hire/1870722567</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-29</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>THE CORE - 核</v>
+        <v>For Hire - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:50</v>
+        <v>3:44</v>
       </c>
       <c r="H119" t="str">
-        <v>XG</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/for-hire/1870722565</v>
       </c>
       <c r="L119" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>For Hire - People I’ve Met</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Dead End</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-29</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Ricochet</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G120" t="str">
-        <v>4:05</v>
+        <v>2:20</v>
       </c>
       <c r="H120" t="str">
-        <v>Snail Mail</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L120" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-29</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:52</v>
+        <v>3:01</v>
       </c>
       <c r="H121" t="str">
-        <v>Dove Cameron</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L121" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-29</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G122" t="str">
-        <v>3:02</v>
+        <v>2:29</v>
       </c>
       <c r="H122" t="str">
-        <v>Kenia Os</v>
+        <v>Joji</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704<